--- a/Others/Quant模型设计.xlsx
+++ b/Others/Quant模型设计.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Quant\Backtrader_PJ1\Quant\Others\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" tabRatio="743"/>
+    <workbookView windowWidth="23040" windowHeight="10620" tabRatio="743" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="T00" sheetId="1" r:id="rId1"/>
@@ -37,8 +42,8 @@
     <definedName name="ods_trading_days_insight">Tinsight!$G$5</definedName>
     <definedName name="ods_stock_code_daily_insight">Tinsight!$B$5</definedName>
     <definedName name="ods_stock_chouma_insight">Tinsight!$G$28</definedName>
-    <definedName name="ods_shareholder_num">Tinsight!$B$41</definedName>
-    <definedName name="ods_north_bound_daily">Tinsight!$B$54</definedName>
+    <definedName name="ods_shareholder_num">Tinsight!$B$44</definedName>
+    <definedName name="ods_north_bound_daily">Tinsight!$B$58</definedName>
     <definedName name="ods_stock_exchange_market">Tcal!$H$9</definedName>
     <definedName name="ods_tdx_stock_pepb_info">TDX!$C$28</definedName>
     <definedName name="ods_stock_kline_daily_insight">Tinsight!$B$14</definedName>
@@ -111,7 +116,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1839" uniqueCount="770">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1843" uniqueCount="774">
   <si>
     <t>序号</t>
   </si>
@@ -896,16 +901,34 @@
     <t>流通股加权平均持仓成本</t>
   </si>
   <si>
+    <t>max_cost</t>
+  </si>
+  <si>
+    <t>流通股最大持仓成本</t>
+  </si>
+  <si>
+    <t>min_cost</t>
+  </si>
+  <si>
+    <t>流通股最小持仓成本</t>
+  </si>
+  <si>
+    <t>winner_rate</t>
+  </si>
+  <si>
+    <t>流通股获利胜率</t>
+  </si>
+  <si>
     <t>total_sh</t>
   </si>
   <si>
     <t>总股东数</t>
   </si>
   <si>
-    <t>max_cost</t>
-  </si>
-  <si>
-    <t>流通股最大持仓成本</t>
+    <t>diversity</t>
+  </si>
+  <si>
+    <t>流通股筹码分散程度百分比</t>
   </si>
   <si>
     <t>avg_share</t>
@@ -914,10 +937,10 @@
     <t>每个股东平均持股数</t>
   </si>
   <si>
-    <t>min_cost</t>
-  </si>
-  <si>
-    <t>流通股最小持仓成本</t>
+    <t>pre_winner_rate</t>
+  </si>
+  <si>
+    <t>流通股昨日获利胜率</t>
   </si>
   <si>
     <t>pct_of_total_sh</t>
@@ -926,10 +949,10 @@
     <t>股东数较上期环比波动百分比</t>
   </si>
   <si>
-    <t>winner_rate</t>
-  </si>
-  <si>
-    <t>流通股获利胜率</t>
+    <t>restricted_avg_cost</t>
+  </si>
+  <si>
+    <t>限售股平均持仓成本</t>
   </si>
   <si>
     <t>pct_of_avg_sh</t>
@@ -938,70 +961,64 @@
     <t>每个股东平均持股数较上期环比波动百分比</t>
   </si>
   <si>
-    <t>diversity</t>
-  </si>
-  <si>
-    <t>流通股筹码分散程度百分比</t>
-  </si>
-  <si>
-    <t>pre_winner_rate</t>
-  </si>
-  <si>
-    <t>流通股昨日获利胜率</t>
-  </si>
-  <si>
-    <t>restricted_avg_cost</t>
-  </si>
-  <si>
-    <t>限售股平均持仓成本</t>
-  </si>
-  <si>
     <t>restricted_max_cost</t>
   </si>
   <si>
     <t>限售股最大持仓成本</t>
   </si>
   <si>
+    <t>load_time</t>
+  </si>
+  <si>
+    <t>记录首次写入时间</t>
+  </si>
+  <si>
+    <t>restricted_min_cost</t>
+  </si>
+  <si>
+    <t>限售股最小持仓成本</t>
+  </si>
+  <si>
+    <t>ann_date</t>
+  </si>
+  <si>
+    <t>公告日期/可知日</t>
+  </si>
+  <si>
+    <t>large_shareholders_avg_cost</t>
+  </si>
+  <si>
+    <t>大流通股股东持股平均持仓成本</t>
+  </si>
+  <si>
+    <t>large_shareholders_total_share</t>
+  </si>
+  <si>
+    <t>大流通股股东持股总数</t>
+  </si>
+  <si>
+    <t>large_shareholders_total_share_pct</t>
+  </si>
+  <si>
+    <t>大流通股股东持股占总股本的比例</t>
+  </si>
+  <si>
     <t>北向持仓数据</t>
   </si>
   <si>
-    <t>restricted_min_cost</t>
-  </si>
-  <si>
-    <t>限售股最小持仓成本</t>
-  </si>
-  <si>
     <t>ods_north_bound_daily</t>
   </si>
   <si>
-    <t>large_shareholders_avg_cost</t>
-  </si>
-  <si>
-    <t>大流通股股东持股平均持仓成本</t>
-  </si>
-  <si>
-    <t>large_shareholders_total_share</t>
-  </si>
-  <si>
-    <t>大流通股股东持股总数</t>
-  </si>
-  <si>
-    <t>large_shareholders_total_share_pct</t>
-  </si>
-  <si>
-    <t>大流通股股东持股占总股本的比例</t>
+    <t>北向资金持有股票数</t>
+  </si>
+  <si>
+    <t>北向资金持有股票占比</t>
   </si>
   <si>
     <t>sh_hkshare_hold</t>
   </si>
   <si>
-    <t>北向资金持有股票数</t>
-  </si>
-  <si>
     <t>pct_total_share</t>
-  </si>
-  <si>
-    <t>北向资金持有股票占比</t>
   </si>
   <si>
     <t>股票基本面数据</t>
@@ -4984,13 +5001,13 @@
   <sheetData>
     <row r="1" spans="2:6">
       <c r="B1" s="1" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
     </row>
     <row r="2" spans="2:6">
@@ -5043,7 +5060,7 @@
     </row>
     <row r="6" spans="2:6">
       <c r="B6" s="2" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>152</v>
@@ -5067,7 +5084,7 @@
     </row>
     <row r="8" spans="2:6">
       <c r="B8" s="2" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="E8" t="s">
         <v>118</v>
@@ -5103,7 +5120,7 @@
     </row>
     <row r="11" spans="2:6">
       <c r="B11" s="2" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="E11" t="s">
         <v>142</v>
@@ -5130,7 +5147,7 @@
         <v>42</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="F13" t="e">
         <f t="shared" si="0"/>
@@ -5154,7 +5171,7 @@
         <v>50</v>
       </c>
       <c r="E15" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="F15" t="str">
         <f t="shared" si="0"/>
@@ -5166,7 +5183,7 @@
         <v>53</v>
       </c>
       <c r="E16" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="F16" t="str">
         <f t="shared" si="0"/>
@@ -5190,7 +5207,7 @@
         <v>61</v>
       </c>
       <c r="E18" t="s">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="F18" t="str">
         <f t="shared" si="0"/>
@@ -5202,7 +5219,7 @@
         <v>64</v>
       </c>
       <c r="E19" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="F19" t="str">
         <f t="shared" si="0"/>
@@ -5211,10 +5228,10 @@
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="2" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="E20" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="F20" t="str">
         <f t="shared" si="0"/>
@@ -5223,7 +5240,7 @@
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="E21" t="s">
         <v>29</v>
@@ -5235,7 +5252,7 @@
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="2" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="E22" t="s">
         <v>37</v>
@@ -5247,7 +5264,7 @@
     </row>
     <row r="23" spans="2:6">
       <c r="B23" s="2" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="E23" t="s">
         <v>42</v>
@@ -5274,7 +5291,7 @@
         <v>73</v>
       </c>
       <c r="E25" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="F25" t="str">
         <f t="shared" si="0"/>
@@ -5331,7 +5348,7 @@
     </row>
     <row r="30" spans="2:6">
       <c r="B30" s="2" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="E30" t="s">
         <v>53</v>
@@ -5343,10 +5360,10 @@
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="2" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="F31" t="e">
         <f t="shared" si="0"/>
@@ -5355,7 +5372,7 @@
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="2" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="E32" t="s">
         <v>50</v>
@@ -5370,7 +5387,7 @@
         <v>97</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="F33" t="e">
         <f t="shared" si="0"/>
@@ -5382,7 +5399,7 @@
         <v>100</v>
       </c>
       <c r="E34" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="F34" t="str">
         <f t="shared" si="0"/>
@@ -5394,7 +5411,7 @@
         <v>106</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="F35" t="e">
         <f t="shared" ref="F35:F60" si="1">VLOOKUP(E35,B:B,1,FALSE)</f>
@@ -5418,7 +5435,7 @@
         <v>113</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="F37" t="e">
         <f t="shared" si="1"/>
@@ -5475,10 +5492,10 @@
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="2" t="s">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="F42" t="e">
         <f t="shared" si="1"/>
@@ -5514,7 +5531,7 @@
         <v>137</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="F45" t="e">
         <f t="shared" si="1"/>
@@ -5574,7 +5591,7 @@
         <v>159</v>
       </c>
       <c r="E50" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="F50" t="str">
         <f t="shared" si="1"/>
@@ -5622,7 +5639,7 @@
     </row>
     <row r="55" spans="2:6">
       <c r="E55" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="F55" t="str">
         <f t="shared" si="1"/>
@@ -5640,7 +5657,7 @@
     </row>
     <row r="57" spans="2:6">
       <c r="E57" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="F57" t="str">
         <f t="shared" si="1"/>
@@ -5658,7 +5675,7 @@
     </row>
     <row r="59" spans="2:6">
       <c r="E59" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="F59" t="str">
         <f t="shared" si="1"/>
@@ -5746,7 +5763,7 @@
   <sheetData>
     <row r="2" spans="2:2">
       <c r="B2" t="s">
-        <v>767</v>
+        <v>771</v>
       </c>
     </row>
   </sheetData>
@@ -5758,7 +5775,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A4:R60"/>
+  <dimension ref="A4:R63"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="19.95" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="8.22222222222222" style="6" customWidth="1"/>
@@ -6586,9 +6603,6 @@
       </c>
     </row>
     <row r="40" customHeight="1" spans="1:18">
-      <c r="B40" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="F40" s="6">
         <v>11</v>
       </c>
@@ -6609,9 +6623,6 @@
       </c>
     </row>
     <row r="41" customHeight="1" spans="1:18">
-      <c r="B41" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="F41" s="6">
         <v>12</v>
       </c>
@@ -6623,15 +6634,6 @@
       </c>
     </row>
     <row r="42" customHeight="1" spans="1:18">
-      <c r="A42" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>167</v>
-      </c>
       <c r="F42" s="6">
         <v>13</v>
       </c>
@@ -6643,14 +6645,8 @@
       </c>
     </row>
     <row r="43" customHeight="1" spans="1:18">
-      <c r="A43" s="6">
-        <v>1</v>
-      </c>
-      <c r="B43" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="C43" t="s">
-        <v>171</v>
+      <c r="B43" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="F43" s="6">
         <v>14</v>
@@ -6663,14 +6659,8 @@
       </c>
     </row>
     <row r="44" customHeight="1" spans="1:18">
-      <c r="A44" s="6">
-        <v>2</v>
-      </c>
-      <c r="B44" t="s">
-        <v>174</v>
-      </c>
-      <c r="C44" t="s">
-        <v>213</v>
+      <c r="B44" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="F44" s="6">
         <v>15</v>
@@ -6683,14 +6673,14 @@
       </c>
     </row>
     <row r="45" customHeight="1" spans="1:18">
-      <c r="A45" s="6">
-        <v>3</v>
-      </c>
-      <c r="B45" s="14" t="s">
-        <v>168</v>
-      </c>
-      <c r="C45" t="s">
-        <v>169</v>
+      <c r="A45" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>167</v>
       </c>
       <c r="F45" s="6">
         <v>16</v>
@@ -6704,107 +6694,134 @@
     </row>
     <row r="46" customHeight="1" spans="1:18">
       <c r="A46" s="6">
-        <v>4</v>
-      </c>
-      <c r="B46" t="s">
-        <v>258</v>
+        <v>1</v>
+      </c>
+      <c r="B46" s="14" t="s">
+        <v>170</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>171</v>
       </c>
       <c r="F46" s="6">
         <v>17</v>
       </c>
       <c r="G46" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="H46" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="1:18">
       <c r="A47" s="6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B47" t="s">
-        <v>262</v>
+        <v>174</v>
       </c>
       <c r="C47" t="s">
-        <v>263</v>
+        <v>213</v>
       </c>
       <c r="F47" s="6">
         <v>18</v>
       </c>
       <c r="G47" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="H47" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="1:18">
       <c r="A48" s="6">
-        <v>6</v>
-      </c>
-      <c r="B48" t="s">
-        <v>266</v>
+        <v>3</v>
+      </c>
+      <c r="B48" s="14" t="s">
+        <v>168</v>
       </c>
       <c r="C48" t="s">
-        <v>267</v>
+        <v>169</v>
       </c>
       <c r="F48" s="6">
         <v>19</v>
       </c>
       <c r="G48" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="H48" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="1:8">
       <c r="A49" s="6">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B49" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="C49" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="F49" s="6">
         <v>20</v>
       </c>
       <c r="G49" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="H49" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="1:8">
+      <c r="A50" s="6">
+        <v>5</v>
+      </c>
+      <c r="B50" t="s">
+        <v>268</v>
+      </c>
+      <c r="C50" t="s">
+        <v>269</v>
+      </c>
       <c r="F50" s="6">
         <v>21</v>
       </c>
       <c r="G50" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="H50" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="1:8">
+      <c r="A51" s="6">
+        <v>6</v>
+      </c>
+      <c r="B51" t="s">
+        <v>272</v>
+      </c>
+      <c r="C51" t="s">
+        <v>273</v>
+      </c>
       <c r="F51" s="6">
         <v>22</v>
       </c>
       <c r="G51" t="s">
+        <v>274</v>
+      </c>
+      <c r="H51" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="52" customHeight="1" spans="1:8">
+      <c r="A52" s="6">
+        <v>7</v>
+      </c>
+      <c r="B52" t="s">
         <v>276</v>
       </c>
-      <c r="H51" t="s">
+      <c r="C52" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="52" customHeight="1" spans="1:8">
       <c r="F52" s="6">
         <v>23</v>
       </c>
@@ -6816,111 +6833,129 @@
       </c>
     </row>
     <row r="53" customHeight="1" spans="1:8">
-      <c r="B53" s="1" t="s">
+      <c r="B53" t="s">
         <v>280</v>
+      </c>
+      <c r="C53" t="s">
+        <v>281</v>
       </c>
       <c r="F53" s="6">
         <v>24</v>
       </c>
       <c r="G53" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H53" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="1:8">
-      <c r="B54" s="1" t="s">
-        <v>283</v>
+      <c r="B54" t="s">
+        <v>284</v>
+      </c>
+      <c r="C54" t="s">
+        <v>285</v>
       </c>
       <c r="F54" s="6">
         <v>25</v>
       </c>
       <c r="G54" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="H54" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="1:8">
-      <c r="A55" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>167</v>
-      </c>
       <c r="F55" s="6">
         <v>26</v>
       </c>
       <c r="G55" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="H55" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="1:8">
-      <c r="A56" s="6">
-        <v>1</v>
-      </c>
-      <c r="B56" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="C56" t="s">
-        <v>171</v>
-      </c>
       <c r="F56" s="6">
         <v>27</v>
       </c>
       <c r="G56" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="H56" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="1:8">
-      <c r="A57" s="6">
-        <v>2</v>
-      </c>
-      <c r="B57" s="14" t="s">
-        <v>168</v>
-      </c>
-      <c r="C57" t="s">
-        <v>169</v>
+      <c r="A57" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>167</v>
       </c>
       <c r="F57" s="6"/>
     </row>
     <row r="58" customHeight="1" spans="1:8">
       <c r="A58" s="6">
-        <v>3</v>
-      </c>
-      <c r="B58" t="s">
-        <v>290</v>
+        <v>1</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>293</v>
       </c>
       <c r="C58" t="s">
-        <v>291</v>
+        <v>171</v>
       </c>
       <c r="F58" s="6"/>
     </row>
     <row r="59" customHeight="1" spans="1:8">
       <c r="A59" s="6">
+        <v>2</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C59" t="s">
+        <v>169</v>
+      </c>
+      <c r="F59" s="6"/>
+    </row>
+    <row r="60" customHeight="1" spans="1:8">
+      <c r="A60" s="6">
+        <v>3</v>
+      </c>
+      <c r="B60" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="C60" t="s">
+        <v>294</v>
+      </c>
+      <c r="F60" s="6"/>
+    </row>
+    <row r="61" customHeight="1" spans="1:8">
+      <c r="A61" s="6">
         <v>4</v>
       </c>
-      <c r="B59" t="s">
-        <v>292</v>
-      </c>
-      <c r="C59" t="s">
-        <v>293</v>
-      </c>
-      <c r="F59" s="6"/>
-    </row>
-    <row r="60" customHeight="1" spans="1:8">
-      <c r="F60" s="6"/>
+      <c r="B61" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="C61" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="62" customHeight="1" spans="1:8">
+      <c r="B62" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="63" customHeight="1" spans="1:8">
+      <c r="B63" t="s">
+        <v>297</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6949,7 +6984,7 @@
   <sheetData>
     <row r="3" customHeight="1" spans="1:14">
       <c r="A3" s="15" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -6988,7 +7023,7 @@
       </c>
       <c r="L6" s="6"/>
       <c r="M6" s="1" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:14">
@@ -7000,7 +7035,7 @@
       </c>
       <c r="L7" s="6"/>
       <c r="M7" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:14">
@@ -7040,7 +7075,7 @@
         <v>168</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="G9" s="6">
         <v>1</v>
@@ -7049,7 +7084,7 @@
         <v>168</v>
       </c>
       <c r="I9" s="16" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="L9" s="6">
         <v>1</v>
@@ -7098,7 +7133,7 @@
         <v>187</v>
       </c>
       <c r="D11" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="G11" s="6">
         <v>3</v>
@@ -7124,28 +7159,28 @@
         <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="D12" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="G12" s="6">
         <v>4</v>
       </c>
       <c r="H12" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="I12" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="L12" s="6">
         <v>4</v>
       </c>
       <c r="M12" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="N12" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:14">
@@ -7153,19 +7188,19 @@
         <v>5</v>
       </c>
       <c r="C13" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="D13" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="G13" s="6">
         <v>5</v>
       </c>
       <c r="H13" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="I13" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="L13" s="6">
         <v>5</v>
@@ -7174,7 +7209,7 @@
         <v>256</v>
       </c>
       <c r="N13" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:14">
@@ -7182,28 +7217,28 @@
         <v>6</v>
       </c>
       <c r="C14" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="D14" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="G14" s="6">
         <v>6</v>
       </c>
       <c r="H14" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="I14" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="L14" s="6">
         <v>6</v>
       </c>
       <c r="M14" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="N14" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:14">
@@ -7211,28 +7246,28 @@
         <v>7</v>
       </c>
       <c r="C15" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="D15" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="G15" s="6">
         <v>7</v>
       </c>
       <c r="H15" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="I15" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="L15" s="6">
         <v>7</v>
       </c>
       <c r="M15" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="N15" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:14">
@@ -7240,28 +7275,28 @@
         <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="D16" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="G16" s="6">
         <v>8</v>
       </c>
       <c r="H16" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="I16" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="L16" s="6">
         <v>8</v>
       </c>
       <c r="M16" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="N16" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="2:14">
@@ -7269,28 +7304,28 @@
         <v>9</v>
       </c>
       <c r="C17" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="D17" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="G17" s="6">
         <v>9</v>
       </c>
       <c r="H17" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="I17" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="L17" s="6">
         <v>9</v>
       </c>
       <c r="M17" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="N17" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="2:14">
@@ -7298,28 +7333,28 @@
         <v>10</v>
       </c>
       <c r="C18" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="D18" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="G18" s="6">
         <v>10</v>
       </c>
       <c r="H18" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="I18" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="L18" s="6">
         <v>10</v>
       </c>
       <c r="M18" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="N18" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="2:14">
@@ -7327,28 +7362,28 @@
         <v>11</v>
       </c>
       <c r="C19" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="D19" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="G19" s="6">
         <v>11</v>
       </c>
       <c r="H19" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="I19" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="L19" s="6">
         <v>11</v>
       </c>
       <c r="M19" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="N19" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="2:14">
@@ -7356,19 +7391,19 @@
         <v>12</v>
       </c>
       <c r="C20" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D20" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="G20" s="6">
         <v>12</v>
       </c>
       <c r="H20" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="I20" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="2:14">
@@ -7376,19 +7411,19 @@
         <v>13</v>
       </c>
       <c r="C21" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="D21" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="G21" s="6">
         <v>13</v>
       </c>
       <c r="H21" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="I21" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="2:14">
@@ -7396,19 +7431,19 @@
         <v>14</v>
       </c>
       <c r="C22" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="D22" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="G22" s="6">
         <v>14</v>
       </c>
       <c r="H22" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="I22" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="2:14">
@@ -7416,10 +7451,10 @@
         <v>15</v>
       </c>
       <c r="H23" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="I23" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="2:14">
@@ -7481,7 +7516,7 @@
         <v>168</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="G29" s="6">
         <v>1</v>
@@ -7490,7 +7525,7 @@
         <v>168</v>
       </c>
       <c r="I29" s="16" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="L29" s="6">
         <v>1</v>
@@ -7507,7 +7542,7 @@
         <v>2</v>
       </c>
       <c r="C30" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="D30" t="s">
         <v>0</v>
@@ -7516,7 +7551,7 @@
         <v>2</v>
       </c>
       <c r="H30" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="I30" t="s">
         <v>0</v>
@@ -7525,10 +7560,10 @@
         <v>2</v>
       </c>
       <c r="M30" s="16" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="N30" s="16" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="2:14">
@@ -7557,7 +7592,7 @@
         <v>187</v>
       </c>
       <c r="N31" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="2:14">
@@ -7568,7 +7603,7 @@
         <v>174</v>
       </c>
       <c r="D32" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="G32" s="6">
         <v>4</v>
@@ -7577,16 +7612,16 @@
         <v>174</v>
       </c>
       <c r="I32" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="L32" s="6">
         <v>4</v>
       </c>
       <c r="M32" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="N32" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="2:14">
@@ -7594,28 +7629,28 @@
         <v>5</v>
       </c>
       <c r="C33" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="D33" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="G33" s="6">
         <v>5</v>
       </c>
       <c r="H33" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="I33" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="L33" s="6">
         <v>5</v>
       </c>
       <c r="M33" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="N33" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="2:14">
@@ -7623,28 +7658,28 @@
         <v>6</v>
       </c>
       <c r="C34" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="D34" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="G34" s="6">
         <v>6</v>
       </c>
       <c r="H34" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="I34" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="L34" s="6">
         <v>6</v>
       </c>
       <c r="M34" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="N34" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="2:14">
@@ -7652,28 +7687,28 @@
         <v>7</v>
       </c>
       <c r="C35" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="D35" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="G35" s="6">
         <v>7</v>
       </c>
       <c r="H35" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="I35" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="L35" s="6">
         <v>7</v>
       </c>
       <c r="M35" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="N35" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="2:14">
@@ -7681,28 +7716,28 @@
         <v>8</v>
       </c>
       <c r="C36" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="D36" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="G36" s="6">
         <v>8</v>
       </c>
       <c r="H36" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="I36" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="L36" s="6">
         <v>8</v>
       </c>
       <c r="M36" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="N36" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="2:14">
@@ -7710,28 +7745,28 @@
         <v>9</v>
       </c>
       <c r="C37" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="D37" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="G37" s="6">
         <v>9</v>
       </c>
       <c r="H37" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="I37" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="L37" s="6">
         <v>9</v>
       </c>
       <c r="M37" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="N37" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="2:14">
@@ -7739,19 +7774,19 @@
         <v>10</v>
       </c>
       <c r="C38" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D38" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="G38" s="6">
         <v>10</v>
       </c>
       <c r="H38" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="I38" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="2:14">
@@ -7759,19 +7794,19 @@
         <v>11</v>
       </c>
       <c r="C39" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="D39" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="G39" s="6">
         <v>11</v>
       </c>
       <c r="H39" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="I39" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="2:14">
@@ -7779,10 +7814,10 @@
         <v>12</v>
       </c>
       <c r="C40" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="D40" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="2:14">
@@ -7790,10 +7825,10 @@
         <v>13</v>
       </c>
       <c r="C41" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="D41" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="2:14">
@@ -7801,10 +7836,10 @@
         <v>14</v>
       </c>
       <c r="C42" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="D42" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="2:14">
@@ -7812,10 +7847,10 @@
         <v>15</v>
       </c>
       <c r="C43" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="D43" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="2:14">
@@ -7823,10 +7858,10 @@
         <v>16</v>
       </c>
       <c r="C44" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="D44" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="2:14">
@@ -7834,10 +7869,10 @@
         <v>17</v>
       </c>
       <c r="C45" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="D45" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="2:14">
@@ -7845,47 +7880,47 @@
         <v>18</v>
       </c>
       <c r="C46" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="D46" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="2:20">
       <c r="B51" s="9" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="2:20">
       <c r="C52" s="1" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="L52" s="6"/>
       <c r="M52" s="1" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="R52" s="6"/>
       <c r="S52" s="1" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="2:20">
       <c r="C53" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="H53" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="L53" s="6"/>
       <c r="M53" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="R53" s="6"/>
       <c r="S53" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="2:20">
@@ -7934,7 +7969,7 @@
         <v>168</v>
       </c>
       <c r="D55" s="16" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="G55" s="6">
         <v>1</v>
@@ -7943,7 +7978,7 @@
         <v>168</v>
       </c>
       <c r="I55" s="16" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="L55" s="6">
         <v>1</v>
@@ -7952,7 +7987,7 @@
         <v>168</v>
       </c>
       <c r="N55" s="16" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="R55" s="6">
         <v>1</v>
@@ -7961,7 +7996,7 @@
         <v>168</v>
       </c>
       <c r="T55" s="16" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="2:20">
@@ -7969,7 +8004,7 @@
         <v>2</v>
       </c>
       <c r="C56" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="D56" t="s">
         <v>0</v>
@@ -7978,28 +8013,28 @@
         <v>2</v>
       </c>
       <c r="H56" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="I56" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="L56" s="6">
         <v>2</v>
       </c>
       <c r="M56" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="N56" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="R56" s="6">
         <v>2</v>
       </c>
       <c r="S56" s="16" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="T56" s="16" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="2:20">
@@ -8010,25 +8045,25 @@
         <v>170</v>
       </c>
       <c r="D57" s="16" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="G57" s="6">
         <v>3</v>
       </c>
       <c r="H57" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="I57" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="L57" s="6">
         <v>3</v>
       </c>
       <c r="M57" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="N57" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="R57" s="6">
         <v>3</v>
@@ -8037,7 +8072,7 @@
         <v>183</v>
       </c>
       <c r="T57" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="2:20">
@@ -8048,22 +8083,22 @@
         <v>174</v>
       </c>
       <c r="D58" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="G58" s="6">
         <v>4</v>
       </c>
       <c r="H58" s="16" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="I58" s="16" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="L58" s="6">
         <v>4</v>
       </c>
       <c r="M58" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="N58" t="s">
         <v>0</v>
@@ -8075,7 +8110,7 @@
         <v>187</v>
       </c>
       <c r="T58" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="2:20">
@@ -8095,7 +8130,7 @@
         <v>187</v>
       </c>
       <c r="I59" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="L59" s="6">
         <v>5</v>
@@ -8104,7 +8139,7 @@
         <v>170</v>
       </c>
       <c r="N59" s="16" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="R59" s="6">
         <v>5</v>
@@ -8113,7 +8148,7 @@
         <v>191</v>
       </c>
       <c r="T59" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="2:20">
@@ -8121,19 +8156,19 @@
         <v>6</v>
       </c>
       <c r="C60" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="D60" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="G60" s="6">
         <v>6</v>
       </c>
       <c r="H60" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="I60" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="L60" s="6">
         <v>6</v>
@@ -8142,7 +8177,7 @@
         <v>174</v>
       </c>
       <c r="N60" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="R60" s="6">
         <v>6</v>
@@ -8151,7 +8186,7 @@
         <v>195</v>
       </c>
       <c r="T60" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="2:20">
@@ -8159,19 +8194,19 @@
         <v>7</v>
       </c>
       <c r="C61" s="13" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="D61" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="G61" s="6">
         <v>7</v>
       </c>
       <c r="H61" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="I61" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="L61" s="6">
         <v>7</v>
@@ -8180,16 +8215,16 @@
         <v>187</v>
       </c>
       <c r="N61" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="R61" s="6">
         <v>7</v>
       </c>
       <c r="S61" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="T61" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="2:20">
@@ -8197,37 +8232,37 @@
         <v>8</v>
       </c>
       <c r="C62" s="13" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="D62" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="G62" s="6">
         <v>8</v>
       </c>
       <c r="H62" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="I62" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="L62" s="6">
         <v>8</v>
       </c>
       <c r="M62" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="N62" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="R62" s="6">
         <v>8</v>
       </c>
       <c r="S62" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="T62" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="2:20">
@@ -8235,34 +8270,34 @@
         <v>9</v>
       </c>
       <c r="C63" s="13" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="D63" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="G63" s="6">
         <v>9</v>
       </c>
       <c r="H63" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="I63" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="L63" s="6">
         <v>9</v>
       </c>
       <c r="M63" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="N63" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="R63" s="6">
         <v>9</v>
       </c>
       <c r="S63" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="T63" t="s">
         <v>204</v>
@@ -8273,37 +8308,37 @@
         <v>10</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="D64" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="G64" s="6">
         <v>10</v>
       </c>
       <c r="H64" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="I64" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="L64" s="6">
         <v>10</v>
       </c>
       <c r="M64" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="N64" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="R64" s="6">
         <v>10</v>
       </c>
       <c r="S64" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="T64" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="2:20">
@@ -8314,34 +8349,34 @@
         <v>191</v>
       </c>
       <c r="D65" s="13" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="G65" s="6">
         <v>11</v>
       </c>
       <c r="H65" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="I65" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="L65" s="6">
         <v>11</v>
       </c>
       <c r="M65" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="N65" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="R65" s="6">
         <v>11</v>
       </c>
       <c r="S65" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="T65" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="2:20">
@@ -8352,34 +8387,34 @@
         <v>195</v>
       </c>
       <c r="D66" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="G66" s="6">
         <v>12</v>
       </c>
       <c r="H66" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="I66" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="L66" s="6">
         <v>12</v>
       </c>
       <c r="M66" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="N66" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="R66" s="6">
         <v>12</v>
       </c>
       <c r="S66" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="T66" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="2:20">
@@ -8390,16 +8425,16 @@
         <v>183</v>
       </c>
       <c r="D67" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="G67" s="6">
         <v>13</v>
       </c>
       <c r="H67" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="I67" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="L67" s="6">
         <v>13</v>
@@ -8408,7 +8443,7 @@
         <v>191</v>
       </c>
       <c r="N67" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="2:20">
@@ -8419,7 +8454,7 @@
         <v>218</v>
       </c>
       <c r="D68" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="L68" s="6">
         <v>14</v>
@@ -8428,7 +8463,7 @@
         <v>195</v>
       </c>
       <c r="N68" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="2:20">
@@ -8436,10 +8471,10 @@
         <v>15</v>
       </c>
       <c r="C69" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="D69" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="L69" s="6">
         <v>15</v>
@@ -8448,7 +8483,7 @@
         <v>183</v>
       </c>
       <c r="N69" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="2:20">
@@ -8456,10 +8491,10 @@
         <v>16</v>
       </c>
       <c r="C70" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="D70" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="L70" s="6">
         <v>16</v>
@@ -8468,7 +8503,7 @@
         <v>218</v>
       </c>
       <c r="N70" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="2:20">
@@ -8476,19 +8511,19 @@
         <v>17</v>
       </c>
       <c r="C71" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="D71" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="L71" s="6">
         <v>17</v>
       </c>
       <c r="M71" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="N71" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="2:20">
@@ -8496,19 +8531,19 @@
         <v>18</v>
       </c>
       <c r="C72" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="D72" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="L72" s="6">
         <v>18</v>
       </c>
       <c r="M72" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="N72" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="2:20">
@@ -8516,19 +8551,19 @@
         <v>19</v>
       </c>
       <c r="C73" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="D73" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="L73" s="6">
         <v>19</v>
       </c>
       <c r="M73" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="N73" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="2:20">
@@ -8536,10 +8571,10 @@
         <v>20</v>
       </c>
       <c r="C74" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="D74" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="2:20">
@@ -8547,10 +8582,10 @@
         <v>21</v>
       </c>
       <c r="C75" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="D75" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="2:20">
@@ -8558,10 +8593,10 @@
         <v>22</v>
       </c>
       <c r="C76" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="D76" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="2:20">
@@ -8569,10 +8604,10 @@
         <v>23</v>
       </c>
       <c r="C77" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="D77" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="2:20">
@@ -8580,15 +8615,15 @@
         <v>24</v>
       </c>
       <c r="C78" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="D78" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="2:9">
       <c r="B82" s="9" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="2:9">
@@ -8635,7 +8670,7 @@
         <v>168</v>
       </c>
       <c r="D86" s="16" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="G86" s="6">
         <v>1</v>
@@ -8644,7 +8679,7 @@
         <v>168</v>
       </c>
       <c r="I86" s="16" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="87" customHeight="1" spans="2:9">
@@ -8652,19 +8687,19 @@
         <v>2</v>
       </c>
       <c r="C87" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="D87" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="G87" s="6">
         <v>2</v>
       </c>
       <c r="H87" s="17" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="I87" s="17" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="88" customHeight="1" spans="2:9">
@@ -8672,19 +8707,19 @@
         <v>3</v>
       </c>
       <c r="C88" s="16" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="D88" s="16" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="G88" s="6">
         <v>3</v>
       </c>
       <c r="H88" s="16" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="I88" s="16" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="89" customHeight="1" spans="2:9">
@@ -8695,7 +8730,7 @@
         <v>183</v>
       </c>
       <c r="I89" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
     </row>
     <row r="90" customHeight="1" spans="2:9">
@@ -8706,7 +8741,7 @@
         <v>191</v>
       </c>
       <c r="I90" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="91" customHeight="1" spans="2:9">
@@ -8717,7 +8752,7 @@
         <v>195</v>
       </c>
       <c r="I91" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="92" customHeight="1" spans="2:9">
@@ -8728,7 +8763,7 @@
         <v>187</v>
       </c>
       <c r="I92" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="93" customHeight="1" spans="2:9">
@@ -8736,10 +8771,10 @@
         <v>8</v>
       </c>
       <c r="H93" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="I93" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="94" customHeight="1" spans="2:9">
@@ -8747,10 +8782,10 @@
         <v>9</v>
       </c>
       <c r="H94" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="I94" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
     </row>
   </sheetData>
@@ -8782,7 +8817,7 @@
   <sheetData>
     <row r="3" customHeight="1" spans="1:14">
       <c r="A3" s="15" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -8817,11 +8852,11 @@
         <v>79</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="L6" s="6"/>
       <c r="M6" s="1" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:14">
@@ -8829,11 +8864,11 @@
         <v>78</v>
       </c>
       <c r="H7" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="L7" s="6"/>
       <c r="M7" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:14">
@@ -8980,10 +9015,10 @@
         <v>7</v>
       </c>
       <c r="C15" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="D15" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="G15" s="6">
         <v>7</v>
@@ -9000,7 +9035,7 @@
         <v>203</v>
       </c>
       <c r="D16" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="G16" s="6">
         <v>8</v>
@@ -9014,10 +9049,10 @@
         <v>9</v>
       </c>
       <c r="C17" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="D17" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="G17" s="6">
         <v>9</v>
@@ -9031,10 +9066,10 @@
         <v>10</v>
       </c>
       <c r="C18" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="D18" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="G18" s="6">
         <v>10</v>
@@ -9048,10 +9083,10 @@
         <v>11</v>
       </c>
       <c r="C19" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="D19" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="G19" s="6">
         <v>11</v>
@@ -9082,7 +9117,7 @@
     </row>
     <row r="26" customHeight="1" spans="1:14">
       <c r="A26" s="15" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="B26" s="12"/>
       <c r="C26" s="12"/>
@@ -9173,7 +9208,7 @@
         <v>168</v>
       </c>
       <c r="D33" s="16" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="G33" s="6">
         <v>1</v>
@@ -9191,7 +9226,7 @@
         <v>168</v>
       </c>
       <c r="N33" s="16" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="2:14">
@@ -9199,28 +9234,28 @@
         <v>2</v>
       </c>
       <c r="C34" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="D34" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="G34" s="6">
         <v>2</v>
       </c>
       <c r="H34" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="I34" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="L34" s="6">
         <v>2</v>
       </c>
       <c r="M34" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="N34" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="2:14">
@@ -9228,28 +9263,28 @@
         <v>3</v>
       </c>
       <c r="C35" s="16" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="D35" s="16" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="G35" s="6">
         <v>3</v>
       </c>
       <c r="H35" s="16" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="I35" s="16" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="L35" s="6">
         <v>3</v>
       </c>
       <c r="M35" s="16" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="N35" s="16" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="2:14">
@@ -9257,10 +9292,10 @@
         <v>4</v>
       </c>
       <c r="C36" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="D36" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="G36" s="6">
         <v>4</v>
@@ -9269,7 +9304,7 @@
         <v>183</v>
       </c>
       <c r="I36" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="L36" s="6">
         <v>4</v>
@@ -9286,7 +9321,7 @@
         <v>5</v>
       </c>
       <c r="C37" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D37" t="s">
         <v>210</v>
@@ -9298,7 +9333,7 @@
         <v>191</v>
       </c>
       <c r="I37" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="L37" s="6">
         <v>5</v>
@@ -9315,10 +9350,10 @@
         <v>6</v>
       </c>
       <c r="C38" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="D38" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="G38" s="6">
         <v>6</v>
@@ -9327,16 +9362,16 @@
         <v>195</v>
       </c>
       <c r="I38" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="L38" s="6">
         <v>6</v>
       </c>
       <c r="M38" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="N38" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="2:14">
@@ -9344,10 +9379,10 @@
         <v>7</v>
       </c>
       <c r="C39" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="D39" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="G39" s="6">
         <v>7</v>
@@ -9356,16 +9391,16 @@
         <v>187</v>
       </c>
       <c r="I39" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="L39" s="6">
         <v>7</v>
       </c>
       <c r="M39" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="N39" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="2:14">
@@ -9376,16 +9411,16 @@
         <v>218</v>
       </c>
       <c r="I40" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="L40" s="6">
         <v>8</v>
       </c>
       <c r="M40" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="N40" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="2:14">
@@ -9393,19 +9428,19 @@
         <v>9</v>
       </c>
       <c r="H41" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="I41" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="L41" s="6">
         <v>9</v>
       </c>
       <c r="M41" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="N41" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="2:14">
@@ -9413,10 +9448,10 @@
         <v>10</v>
       </c>
       <c r="H42" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="I42" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="L42" s="6"/>
     </row>
@@ -9425,10 +9460,10 @@
         <v>11</v>
       </c>
       <c r="H43" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="I43" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="2:14">
@@ -9436,7 +9471,7 @@
         <v>12</v>
       </c>
       <c r="H44" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="I44" t="s">
         <v>204</v>
@@ -9447,10 +9482,10 @@
         <v>13</v>
       </c>
       <c r="H45" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="I45" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="2:14">
@@ -9458,10 +9493,10 @@
         <v>14</v>
       </c>
       <c r="H46" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="I46" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="2:14">
@@ -9469,34 +9504,34 @@
         <v>15</v>
       </c>
       <c r="H47" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="I47" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="2:15">
       <c r="C50" s="1" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="L50" s="6"/>
       <c r="M50" s="1" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="2:15">
       <c r="C51" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="H51" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="L51" s="6"/>
       <c r="M51" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="2:15">
@@ -9536,7 +9571,7 @@
         <v>168</v>
       </c>
       <c r="D53" s="16" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="G53" s="6">
         <v>1</v>
@@ -9554,7 +9589,7 @@
         <v>168</v>
       </c>
       <c r="N53" s="16" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="O53" s="16"/>
     </row>
@@ -9563,28 +9598,28 @@
         <v>2</v>
       </c>
       <c r="C54" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="D54" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="G54" s="6">
         <v>2</v>
       </c>
       <c r="H54" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="I54" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="L54" s="6">
         <v>2</v>
       </c>
       <c r="M54" s="16" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="N54" s="16" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="O54" s="16"/>
     </row>
@@ -9593,28 +9628,28 @@
         <v>3</v>
       </c>
       <c r="C55" s="16" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="D55" s="16" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="G55" s="6">
         <v>3</v>
       </c>
       <c r="H55" s="16" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="I55" s="16" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="L55" s="6">
         <v>3</v>
       </c>
       <c r="M55" s="16" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="N55" s="16" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="O55" s="16"/>
     </row>
@@ -9623,10 +9658,10 @@
         <v>4</v>
       </c>
       <c r="C56" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="D56" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="G56" s="6">
         <v>4</v>
@@ -9635,7 +9670,7 @@
         <v>183</v>
       </c>
       <c r="I56" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="L56" s="6">
         <v>4</v>
@@ -9644,7 +9679,7 @@
         <v>170</v>
       </c>
       <c r="N56" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="2:15">
@@ -9652,10 +9687,10 @@
         <v>5</v>
       </c>
       <c r="C57" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="D57" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="G57" s="6">
         <v>5</v>
@@ -9664,7 +9699,7 @@
         <v>191</v>
       </c>
       <c r="I57" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="L57" s="6">
         <v>5</v>
@@ -9673,7 +9708,7 @@
         <v>174</v>
       </c>
       <c r="N57" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="2:15">
@@ -9681,10 +9716,10 @@
         <v>6</v>
       </c>
       <c r="C58" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="D58" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="G58" s="6">
         <v>6</v>
@@ -9693,7 +9728,7 @@
         <v>195</v>
       </c>
       <c r="I58" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="2:15">
@@ -9701,10 +9736,10 @@
         <v>7</v>
       </c>
       <c r="C59" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="D59" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="G59" s="6">
         <v>7</v>
@@ -9713,7 +9748,7 @@
         <v>187</v>
       </c>
       <c r="I59" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="2:15">
@@ -9721,19 +9756,19 @@
         <v>8</v>
       </c>
       <c r="C60" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="D60" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="G60" s="6">
         <v>8</v>
       </c>
       <c r="H60" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="I60" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="2:15">
@@ -9741,19 +9776,19 @@
         <v>9</v>
       </c>
       <c r="C61" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="D61" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="G61" s="6">
         <v>9</v>
       </c>
       <c r="H61" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="I61" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="2:15">
@@ -9761,19 +9796,19 @@
         <v>10</v>
       </c>
       <c r="C62" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="D62" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="G62" s="6">
         <v>10</v>
       </c>
       <c r="H62" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="I62" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="2:15">
@@ -9781,19 +9816,19 @@
         <v>11</v>
       </c>
       <c r="C63" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="D63" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="G63" s="6">
         <v>11</v>
       </c>
       <c r="H63" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="I63" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="2:15">
@@ -9801,10 +9836,10 @@
         <v>12</v>
       </c>
       <c r="H64" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="I64" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="7:9">
@@ -9812,10 +9847,10 @@
         <v>13</v>
       </c>
       <c r="H65" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="I65" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="7:9">
@@ -9823,10 +9858,10 @@
         <v>14</v>
       </c>
       <c r="H66" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="I66" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
     </row>
   </sheetData>
@@ -9859,7 +9894,7 @@
   <sheetData>
     <row r="3" customHeight="1" spans="1:13">
       <c r="A3" s="15" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -9891,7 +9926,7 @@
     </row>
     <row r="7" customHeight="1" spans="1:13">
       <c r="B7" s="9" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:13">
@@ -9955,10 +9990,10 @@
         <v>2</v>
       </c>
       <c r="C12" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="D12" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="G12" s="6">
         <v>2</v>
@@ -9967,7 +10002,7 @@
         <v>170</v>
       </c>
       <c r="I12" s="16" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:13">
@@ -9978,7 +10013,7 @@
         <v>170</v>
       </c>
       <c r="D13" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="G13" s="6">
         <v>3</v>
@@ -9987,7 +10022,7 @@
         <v>174</v>
       </c>
       <c r="I13" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:13">
@@ -9998,16 +10033,16 @@
         <v>174</v>
       </c>
       <c r="D14" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="G14" s="6">
         <v>4</v>
       </c>
       <c r="H14" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="I14" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:13">
@@ -10015,15 +10050,15 @@
         <v>5</v>
       </c>
       <c r="C15" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="D15" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:13">
       <c r="A22" s="15" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="B22" s="12"/>
       <c r="C22" s="12"/>
@@ -10102,10 +10137,10 @@
         <v>1</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="D7" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="2:4">
@@ -10113,7 +10148,7 @@
         <v>2</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="D8" t="s">
         <v>169</v>
@@ -10124,7 +10159,7 @@
         <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="D9" t="s">
         <v>184</v>
@@ -10135,7 +10170,7 @@
         <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="D10" t="s">
         <v>192</v>
@@ -10146,7 +10181,7 @@
         <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="D11" t="s">
         <v>196</v>
@@ -10157,7 +10192,7 @@
         <v>6</v>
       </c>
       <c r="C12" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="D12" t="s">
         <v>188</v>
@@ -10220,7 +10255,7 @@
         <v>181</v>
       </c>
       <c r="D21" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="G21" s="6">
         <v>1</v>
@@ -10249,7 +10284,7 @@
         <v>181</v>
       </c>
       <c r="I22" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="2:9">
@@ -10325,7 +10360,7 @@
   <sheetData>
     <row r="3" customHeight="1" spans="1:14">
       <c r="A3" s="12" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -10413,7 +10448,7 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="D9" t="s">
         <v>178</v>
@@ -10422,7 +10457,7 @@
         <v>1</v>
       </c>
       <c r="H9" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="I9" t="s">
         <v>178</v>
@@ -10431,7 +10466,7 @@
         <v>1</v>
       </c>
       <c r="M9" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="N9" t="s">
         <v>178</v>
@@ -10442,19 +10477,19 @@
         <v>2</v>
       </c>
       <c r="C10" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="D10" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="G10" s="6">
         <v>2</v>
       </c>
       <c r="H10" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="I10" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="L10" s="6">
         <v>2</v>
@@ -10463,7 +10498,7 @@
         <v>216</v>
       </c>
       <c r="N10" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:14">
@@ -10471,19 +10506,19 @@
         <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="D11" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="G11" s="6">
         <v>3</v>
       </c>
       <c r="H11" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="I11" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="L11" s="6">
         <v>3</v>
@@ -10492,7 +10527,7 @@
         <v>211</v>
       </c>
       <c r="N11" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:14">
@@ -10500,7 +10535,7 @@
         <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="D12" t="s">
         <v>171</v>
@@ -10509,7 +10544,7 @@
         <v>4</v>
       </c>
       <c r="H12" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="I12" t="s">
         <v>171</v>
@@ -10518,7 +10553,7 @@
         <v>4</v>
       </c>
       <c r="M12" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="N12" t="s">
         <v>171</v>
@@ -10529,7 +10564,7 @@
         <v>5</v>
       </c>
       <c r="C13" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="D13" t="s">
         <v>213</v>
@@ -10538,7 +10573,7 @@
         <v>5</v>
       </c>
       <c r="H13" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="I13" t="s">
         <v>213</v>
@@ -10547,7 +10582,7 @@
         <v>5</v>
       </c>
       <c r="M13" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="N13" t="s">
         <v>213</v>
@@ -10594,7 +10629,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="D19" t="s">
         <v>178</v>
@@ -10603,7 +10638,7 @@
         <v>1</v>
       </c>
       <c r="H19" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="I19" t="s">
         <v>178</v>
@@ -10614,10 +10649,10 @@
         <v>2</v>
       </c>
       <c r="C20" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="D20" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="G20" s="6">
         <v>2</v>
@@ -10626,7 +10661,7 @@
         <v>176</v>
       </c>
       <c r="I20" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="2:9">
@@ -10634,10 +10669,10 @@
         <v>3</v>
       </c>
       <c r="C21" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="D21" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="G21" s="6">
         <v>3</v>
@@ -10646,7 +10681,7 @@
         <v>179</v>
       </c>
       <c r="I21" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="2:9">
@@ -10691,12 +10726,12 @@
     </row>
     <row r="27" customHeight="1" spans="2:9">
       <c r="C27" s="1" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="2:9">
       <c r="C28" s="13" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="2:9">
@@ -10729,7 +10764,7 @@
         <v>170</v>
       </c>
       <c r="D31" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="2:9">
@@ -10740,7 +10775,7 @@
         <v>174</v>
       </c>
       <c r="D32" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="2:4">
@@ -10748,10 +10783,10 @@
         <v>4</v>
       </c>
       <c r="C33" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="D33" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="2:4">
@@ -10759,10 +10794,10 @@
         <v>5</v>
       </c>
       <c r="C34" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="D34" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="2:4">
@@ -10770,10 +10805,10 @@
         <v>6</v>
       </c>
       <c r="C35" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="D35" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="2:4">
@@ -10781,10 +10816,10 @@
         <v>7</v>
       </c>
       <c r="C36" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="D36" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="2:4">
@@ -10792,10 +10827,10 @@
         <v>8</v>
       </c>
       <c r="C37" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="D37" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="2:4">
@@ -10803,10 +10838,10 @@
         <v>9</v>
       </c>
       <c r="C38" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="D38" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="2:4">
@@ -10814,10 +10849,10 @@
         <v>10</v>
       </c>
       <c r="C39" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="D39" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="2:4">
@@ -10825,10 +10860,10 @@
         <v>11</v>
       </c>
       <c r="C40" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="D40" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="2:4">
@@ -10836,10 +10871,10 @@
         <v>12</v>
       </c>
       <c r="C41" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="D41" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
     </row>
   </sheetData>
@@ -10869,7 +10904,7 @@
   <sheetData>
     <row r="2" customHeight="1" spans="1:14">
       <c r="A2" s="7" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
@@ -10904,7 +10939,7 @@
     </row>
     <row r="15" customHeight="1" spans="1:14">
       <c r="A15" s="10" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
@@ -11029,7 +11064,7 @@
         <v>170</v>
       </c>
       <c r="D22" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="G22" s="6">
         <v>2</v>
@@ -11044,10 +11079,10 @@
         <v>2</v>
       </c>
       <c r="M22" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="N22" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="2:14">
@@ -11058,7 +11093,7 @@
         <v>174</v>
       </c>
       <c r="D23" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="G23" s="6">
         <v>3</v>
@@ -11073,10 +11108,10 @@
         <v>3</v>
       </c>
       <c r="M23" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="N23" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="2:14">
@@ -11087,16 +11122,16 @@
         <v>187</v>
       </c>
       <c r="D24" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="G24" s="6">
         <v>4</v>
       </c>
       <c r="H24" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="I24" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="L24" s="6">
         <v>4</v>
@@ -11105,7 +11140,7 @@
         <v>170</v>
       </c>
       <c r="N24" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="2:14">
@@ -11113,19 +11148,19 @@
         <v>5</v>
       </c>
       <c r="C25" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="D25" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="G25" s="6">
         <v>5</v>
       </c>
       <c r="H25" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="I25" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="L25" s="6">
         <v>5</v>
@@ -11134,7 +11169,7 @@
         <v>174</v>
       </c>
       <c r="N25" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="2:14">
@@ -11151,19 +11186,19 @@
         <v>6</v>
       </c>
       <c r="H26" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="I26" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="L26" s="6">
         <v>6</v>
       </c>
       <c r="M26" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="N26" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="2:14">
@@ -11171,28 +11206,28 @@
         <v>7</v>
       </c>
       <c r="C27" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="D27" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="G27" s="6">
         <v>7</v>
       </c>
       <c r="H27" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="I27" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="L27" s="6">
         <v>7</v>
       </c>
       <c r="M27" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="N27" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="2:14">
@@ -11200,10 +11235,10 @@
         <v>8</v>
       </c>
       <c r="C28" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="D28" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="2:14">
@@ -11211,10 +11246,10 @@
         <v>9</v>
       </c>
       <c r="C29" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="D29" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="2:14">
@@ -11222,10 +11257,10 @@
         <v>10</v>
       </c>
       <c r="C30" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="D30" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="2:14">
@@ -11233,10 +11268,10 @@
         <v>11</v>
       </c>
       <c r="C31" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="D31" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="H31" s="1"/>
     </row>
@@ -11245,10 +11280,10 @@
         <v>12</v>
       </c>
       <c r="C32" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="D32" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="H32" s="1"/>
     </row>
@@ -11257,10 +11292,10 @@
         <v>13</v>
       </c>
       <c r="C33" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D33" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="G33" s="9"/>
       <c r="H33" s="1"/>
@@ -11271,10 +11306,10 @@
         <v>14</v>
       </c>
       <c r="C34" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="D34" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="2:14">
@@ -11282,10 +11317,10 @@
         <v>15</v>
       </c>
       <c r="C35" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="D35" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="2:14">
@@ -11293,10 +11328,10 @@
         <v>16</v>
       </c>
       <c r="C36" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D36" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="2:14">
@@ -11304,10 +11339,10 @@
         <v>17</v>
       </c>
       <c r="C37" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="D37" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="2:14">
@@ -11455,19 +11490,19 @@
         <v>4</v>
       </c>
       <c r="C48" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="D48" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="G48" s="6">
         <v>4</v>
       </c>
       <c r="H48" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="I48" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="L48" s="6">
         <v>4</v>
@@ -11513,28 +11548,28 @@
         <v>6</v>
       </c>
       <c r="C50" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="D50" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="G50" s="6">
         <v>6</v>
       </c>
       <c r="H50" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="I50" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="L50" s="6">
         <v>6</v>
       </c>
       <c r="M50" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="N50" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="2:14">
@@ -11542,28 +11577,28 @@
         <v>7</v>
       </c>
       <c r="C51" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="D51" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="G51" s="6">
         <v>7</v>
       </c>
       <c r="H51" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="I51" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="L51" s="6">
         <v>7</v>
       </c>
       <c r="M51" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="N51" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="2:14">
@@ -11571,28 +11606,28 @@
         <v>8</v>
       </c>
       <c r="C52" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="D52" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="G52" s="6">
         <v>8</v>
       </c>
       <c r="H52" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="I52" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="L52" s="6">
         <v>8</v>
       </c>
       <c r="M52" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="N52" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="2:14">
@@ -11600,28 +11635,28 @@
         <v>9</v>
       </c>
       <c r="C53" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="D53" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="G53" s="6">
         <v>9</v>
       </c>
       <c r="H53" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="I53" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="L53" s="6">
         <v>9</v>
       </c>
       <c r="M53" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="N53" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="2:14">
@@ -11629,28 +11664,28 @@
         <v>10</v>
       </c>
       <c r="C54" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="D54" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="G54" s="6">
         <v>10</v>
       </c>
       <c r="H54" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="I54" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="L54" s="6">
         <v>10</v>
       </c>
       <c r="M54" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="N54" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="2:14">
@@ -11658,28 +11693,28 @@
         <v>11</v>
       </c>
       <c r="C55" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="D55" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="G55" s="6">
         <v>11</v>
       </c>
       <c r="H55" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="I55" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="L55" s="6">
         <v>11</v>
       </c>
       <c r="M55" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="N55" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="2:14">
@@ -11687,28 +11722,28 @@
         <v>12</v>
       </c>
       <c r="C56" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="D56" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="G56" s="6">
         <v>12</v>
       </c>
       <c r="H56" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="I56" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="L56" s="6">
         <v>12</v>
       </c>
       <c r="M56" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="N56" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="2:14">
@@ -11716,28 +11751,28 @@
         <v>13</v>
       </c>
       <c r="C57" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="D57" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="G57" s="6">
         <v>13</v>
       </c>
       <c r="H57" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="I57" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="L57" s="6">
         <v>13</v>
       </c>
       <c r="M57" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="N57" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="2:14">
@@ -11745,28 +11780,28 @@
         <v>14</v>
       </c>
       <c r="C58" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="D58" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="G58" s="6">
         <v>14</v>
       </c>
       <c r="H58" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="I58" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="L58" s="6">
         <v>14</v>
       </c>
       <c r="M58" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="N58" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="2:14">
@@ -11774,28 +11809,28 @@
         <v>15</v>
       </c>
       <c r="C59" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="D59" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="G59" s="6">
         <v>15</v>
       </c>
       <c r="H59" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="I59" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="L59" s="6">
         <v>15</v>
       </c>
       <c r="M59" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="N59" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="2:14">
@@ -11803,28 +11838,28 @@
         <v>16</v>
       </c>
       <c r="C60" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D60" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="G60" s="6">
         <v>16</v>
       </c>
       <c r="H60" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="I60" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="L60" s="6">
         <v>16</v>
       </c>
       <c r="M60" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="N60" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="2:14">
@@ -11832,28 +11867,28 @@
         <v>17</v>
       </c>
       <c r="C61" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="D61" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="G61" s="6">
         <v>17</v>
       </c>
       <c r="H61" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="I61" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="L61" s="6">
         <v>17</v>
       </c>
       <c r="M61" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="N61" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="2:14">
@@ -11861,10 +11896,10 @@
         <v>18</v>
       </c>
       <c r="M62" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="N62" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="2:14">
@@ -11872,10 +11907,10 @@
         <v>19</v>
       </c>
       <c r="M63" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="N63" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="2:14">
@@ -11883,30 +11918,30 @@
         <v>20</v>
       </c>
       <c r="M64" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="N64" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="1:14">
       <c r="B65" s="6" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="C65" t="s">
         <v>17</v>
       </c>
       <c r="D65" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="L65" s="6">
         <v>21</v>
       </c>
       <c r="M65" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="N65" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="1:14">
@@ -11914,20 +11949,20 @@
         <v>22</v>
       </c>
       <c r="M66" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="N66" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="1:14">
       <c r="C67" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="1:14">
       <c r="A70" s="10" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="B70" s="10"/>
       <c r="C70" s="10"/>
@@ -12069,10 +12104,10 @@
         <v>4</v>
       </c>
       <c r="H79" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="I79" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="1:14">
@@ -12089,10 +12124,10 @@
         <v>5</v>
       </c>
       <c r="H80" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="I80" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="1:9">
@@ -12100,19 +12135,19 @@
         <v>6</v>
       </c>
       <c r="C81" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="D81" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="G81" s="6">
         <v>6</v>
       </c>
       <c r="H81" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="I81" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="1:9">
@@ -12120,19 +12155,19 @@
         <v>7</v>
       </c>
       <c r="C82" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="D82" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="G82" s="6">
         <v>7</v>
       </c>
       <c r="H82" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="I82" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="1:9">
@@ -12140,19 +12175,19 @@
         <v>8</v>
       </c>
       <c r="C83" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="D83" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="G83" s="6">
         <v>8</v>
       </c>
       <c r="H83" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="I83" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
     </row>
     <row r="84" customHeight="1" spans="1:9">
@@ -12160,19 +12195,19 @@
         <v>9</v>
       </c>
       <c r="C84" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="D84" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="G84" s="6">
         <v>9</v>
       </c>
       <c r="H84" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="I84" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
     </row>
     <row r="85" customHeight="1" spans="1:9">
@@ -12180,19 +12215,19 @@
         <v>10</v>
       </c>
       <c r="C85" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="D85" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="G85" s="6">
         <v>10</v>
       </c>
       <c r="H85" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="I85" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
     </row>
     <row r="86" customHeight="1" spans="1:9">
@@ -12200,10 +12235,10 @@
         <v>11</v>
       </c>
       <c r="C86" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="D86" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
     </row>
     <row r="87" customHeight="1" spans="1:9">
@@ -12211,10 +12246,10 @@
         <v>12</v>
       </c>
       <c r="C87" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="D87" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
     </row>
     <row r="88" customHeight="1" spans="1:9">
@@ -12222,10 +12257,10 @@
         <v>13</v>
       </c>
       <c r="C88" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="D88" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
     </row>
     <row r="89" customHeight="1" spans="1:9">
@@ -12233,10 +12268,10 @@
         <v>14</v>
       </c>
       <c r="C89" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="D89" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
     </row>
     <row r="90" customHeight="1" spans="1:9">
@@ -12244,10 +12279,10 @@
         <v>15</v>
       </c>
       <c r="C90" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="D90" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
     </row>
     <row r="91" customHeight="1" spans="1:9">
@@ -12255,15 +12290,15 @@
         <v>16</v>
       </c>
       <c r="C91" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="D91" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
     </row>
     <row r="95" customHeight="1" spans="1:9">
       <c r="A95" s="10" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="B95" s="10"/>
       <c r="C95" s="10"/>
@@ -12287,10 +12322,10 @@
     </row>
     <row r="99" customHeight="1" spans="2:9">
       <c r="C99" s="1" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
     </row>
     <row r="100" customHeight="1" spans="2:9">
@@ -12386,19 +12421,19 @@
         <v>4</v>
       </c>
       <c r="C105" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="D105" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="G105" s="6">
         <v>4</v>
       </c>
       <c r="H105" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="I105" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
     </row>
     <row r="106" customHeight="1" spans="2:9">
@@ -12406,19 +12441,19 @@
         <v>5</v>
       </c>
       <c r="C106" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="D106" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="G106" s="6">
         <v>5</v>
       </c>
       <c r="H106" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="I106" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
     </row>
     <row r="107" customHeight="1" spans="2:9">
@@ -12426,19 +12461,19 @@
         <v>6</v>
       </c>
       <c r="C107" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="D107" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="G107" s="6">
         <v>6</v>
       </c>
       <c r="H107" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="I107" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
     </row>
     <row r="108" customHeight="1" spans="2:9">
@@ -12446,19 +12481,19 @@
         <v>7</v>
       </c>
       <c r="C108" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="D108" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="G108" s="6">
         <v>7</v>
       </c>
       <c r="H108" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="I108" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
     </row>
     <row r="109" customHeight="1" spans="2:9">
@@ -12466,19 +12501,19 @@
         <v>8</v>
       </c>
       <c r="C109" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="D109" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="G109" s="6">
         <v>8</v>
       </c>
       <c r="H109" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="I109" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
     </row>
   </sheetData>
@@ -12509,29 +12544,29 @@
   <sheetData>
     <row r="5" spans="3:9">
       <c r="C5" s="1" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
     </row>
     <row r="7" spans="3:9">
       <c r="F7" s="1" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
     </row>
     <row r="8" spans="3:9">
       <c r="D8" s="1" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>17</v>
@@ -12539,89 +12574,89 @@
     </row>
     <row r="9" spans="3:9">
       <c r="I9" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
     </row>
     <row r="13" spans="3:9">
       <c r="H13" s="1" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
     </row>
     <row r="14" spans="3:9">
       <c r="H14" s="1" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
     </row>
     <row r="15" spans="3:9">
       <c r="I15" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
     </row>
     <row r="19" spans="8:9">
       <c r="H19" s="1" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
     </row>
     <row r="20" spans="8:9">
       <c r="H20" s="1" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
     </row>
     <row r="21" spans="8:9">
       <c r="I21" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
     </row>
     <row r="25" spans="8:9">
       <c r="H25" s="1" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
     </row>
     <row r="26" spans="8:9">
       <c r="H26" s="1" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
     </row>
     <row r="27" spans="8:9">
       <c r="I27" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
     </row>
     <row r="31" spans="8:9">
       <c r="H31" s="1" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
     </row>
     <row r="32" spans="8:9">
       <c r="H32" s="1" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
     </row>
     <row r="33" spans="8:9">
       <c r="I33" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
     </row>
     <row r="37" spans="8:9">
       <c r="H37" s="1" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
     </row>
     <row r="38" spans="8:9">
       <c r="H38" s="1" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="I38" s="1" t="s">
         <v>21</v>
@@ -12629,12 +12664,12 @@
     </row>
     <row r="43" spans="8:9">
       <c r="H43" s="1" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
     </row>
     <row r="44" spans="8:9">
       <c r="H44" s="1" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="I44" s="1" t="s">
         <v>106</v>
@@ -12642,17 +12677,17 @@
     </row>
     <row r="45" spans="8:9">
       <c r="I45" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
     </row>
     <row r="49" ht="13" customHeight="1" spans="6:9">
       <c r="H49" s="1" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
     </row>
     <row r="50" spans="6:9">
       <c r="H50" s="1" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="I50" s="5" t="s">
         <v>109</v>
@@ -12660,41 +12695,41 @@
     </row>
     <row r="51" spans="6:9">
       <c r="I51" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
     </row>
     <row r="55" spans="6:9">
       <c r="H55" s="1" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
     </row>
     <row r="56" spans="6:9">
       <c r="H56" s="1" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="I56" s="5" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
     </row>
     <row r="57" spans="6:9">
       <c r="I57" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
     </row>
     <row r="61" spans="6:9">
       <c r="F61" s="1" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
     </row>
     <row r="62" spans="6:9">
       <c r="F62" s="1" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="I62" s="1" t="s">
         <v>46</v>
@@ -12702,17 +12737,17 @@
     </row>
     <row r="63" spans="6:9">
       <c r="I63" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
     </row>
     <row r="65" spans="8:9">
       <c r="H65" s="1" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
     </row>
     <row r="66" spans="8:9">
       <c r="H66" s="1" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="I66" s="1" t="s">
         <v>50</v>
@@ -12720,17 +12755,17 @@
     </row>
     <row r="67" spans="8:9">
       <c r="I67" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
     </row>
     <row r="69" spans="8:9">
       <c r="H69" s="1" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
     </row>
     <row r="70" spans="8:9">
       <c r="H70" s="1" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="I70" s="1" t="s">
         <v>97</v>
@@ -12738,35 +12773,35 @@
     </row>
     <row r="71" spans="8:9">
       <c r="I71" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
     </row>
     <row r="73" spans="8:9">
       <c r="H73" s="1" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="74" spans="8:9">
       <c r="H74" s="1" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="I74" s="5" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
     </row>
     <row r="75" spans="8:9">
       <c r="I75" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
     </row>
     <row r="77" spans="8:9">
       <c r="H77" s="1" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
     </row>
     <row r="78" spans="8:9">
       <c r="H78" s="1" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="I78" s="1" t="s">
         <v>24</v>
@@ -12774,59 +12809,59 @@
     </row>
     <row r="79" spans="8:9">
       <c r="I79" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
     </row>
     <row r="81" spans="6:9">
       <c r="H81" s="1" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
     </row>
     <row r="82" spans="6:9">
       <c r="H82" s="1" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
     </row>
     <row r="83" spans="6:9">
       <c r="I83" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
     </row>
     <row r="87" spans="6:9">
       <c r="F87" s="1" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
     </row>
     <row r="88" spans="6:9">
       <c r="F88" s="1" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
     </row>
     <row r="89" spans="6:9">
       <c r="I89" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
     </row>
     <row r="92" spans="6:9">
       <c r="H92" s="1" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
     </row>
     <row r="93" spans="6:9">
       <c r="H93" s="1" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="I93" s="1" t="s">
         <v>135</v>
@@ -12834,17 +12869,17 @@
     </row>
     <row r="94" spans="6:9">
       <c r="I94" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
     </row>
     <row r="97" spans="6:9">
       <c r="H97" s="1" t="s">
-        <v>738</v>
+        <v>742</v>
       </c>
     </row>
     <row r="98" spans="6:9">
       <c r="H98" s="1" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="I98" s="1" t="s">
         <v>139</v>
@@ -12852,17 +12887,17 @@
     </row>
     <row r="99" spans="6:9">
       <c r="I99" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
     </row>
     <row r="101" spans="6:9">
       <c r="H101" s="1" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
     </row>
     <row r="102" spans="6:9">
       <c r="H102" s="1" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="I102" s="1" t="s">
         <v>142</v>
@@ -12870,7 +12905,7 @@
     </row>
     <row r="103" spans="6:9">
       <c r="I103" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
     </row>
     <row r="105" spans="6:9">
@@ -12880,23 +12915,23 @@
     </row>
     <row r="106" spans="6:9">
       <c r="I106" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
     </row>
     <row r="109" spans="6:9">
       <c r="F109" s="1" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
     </row>
     <row r="110" spans="6:9">
       <c r="F110" s="1" t="s">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="I110" s="1" t="s">
         <v>159</v>
@@ -12904,17 +12939,17 @@
     </row>
     <row r="111" spans="6:9">
       <c r="I111" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="114" spans="6:9">
       <c r="H114" s="1" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
     </row>
     <row r="115" spans="6:9">
       <c r="H115" s="1" t="s">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="I115" s="1" t="s">
         <v>163</v>
@@ -12922,23 +12957,23 @@
     </row>
     <row r="116" spans="6:9">
       <c r="I116" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="120" spans="6:9">
       <c r="F120" s="1" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
     </row>
     <row r="121" spans="6:9">
       <c r="F121" s="1" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="I121" s="1" t="s">
         <v>46</v>
@@ -12946,12 +12981,12 @@
     </row>
     <row r="124" spans="6:9">
       <c r="H124" s="1" t="s">
-        <v>755</v>
+        <v>759</v>
       </c>
     </row>
     <row r="125" spans="6:9">
       <c r="H125" s="1" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="I125" s="1" t="s">
         <v>50</v>
@@ -12959,12 +12994,12 @@
     </row>
     <row r="128" spans="6:9">
       <c r="H128" s="1" t="s">
-        <v>757</v>
+        <v>761</v>
       </c>
     </row>
     <row r="129" spans="8:9">
       <c r="H129" s="1" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="I129" s="1" t="s">
         <v>97</v>
@@ -12972,12 +13007,12 @@
     </row>
     <row r="132" spans="8:9">
       <c r="H132" s="1" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="133" spans="8:9">
       <c r="H133" s="1" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="I133" s="1" t="s">
         <v>53</v>
@@ -12985,12 +13020,12 @@
     </row>
     <row r="136" spans="8:9">
       <c r="H136" s="1" t="s">
-        <v>761</v>
+        <v>765</v>
       </c>
     </row>
     <row r="137" spans="8:9">
       <c r="H137" s="1" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="I137" s="1" t="s">
         <v>24</v>
@@ -12998,12 +13033,12 @@
     </row>
     <row r="141" spans="8:9">
       <c r="I141" s="1" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
     </row>
     <row r="158" spans="6:6">
       <c r="F158" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
     </row>
   </sheetData>

--- a/Others/Quant模型设计.xlsx
+++ b/Others/Quant模型设计.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Quant\Backtrader_PJ1\Quant\Others\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Quant\Backtrader_PJ1\Others\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="10620" tabRatio="743" activeTab="1"/>
+    <workbookView windowWidth="22188" windowHeight="9180" tabRatio="743" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="T00" sheetId="1" r:id="rId1"/>
@@ -6833,6 +6833,9 @@
       </c>
     </row>
     <row r="53" customHeight="1" spans="1:8">
+      <c r="A53" s="6">
+        <v>8</v>
+      </c>
       <c r="B53" t="s">
         <v>280</v>
       </c>
@@ -6850,6 +6853,9 @@
       </c>
     </row>
     <row r="54" customHeight="1" spans="1:8">
+      <c r="A54" s="6">
+        <v>9</v>
+      </c>
       <c r="B54" t="s">
         <v>284</v>
       </c>

--- a/Others/Quant模型设计.xlsx
+++ b/Others/Quant模型设计.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" tabRatio="743" activeTab="7"/>
+    <workbookView windowWidth="22188" windowHeight="9180" tabRatio="743" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="T00" sheetId="1" r:id="rId1"/>
@@ -463,7 +463,7 @@
     <t>通达信概念板块数据</t>
   </si>
   <si>
-    <t>手动更新，目前跟新至 20250130</t>
+    <t>已废弃，目前跟新至 20250130</t>
   </si>
   <si>
     <t>ods_tdx_stock_region_plate</t>
@@ -3460,7 +3460,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14317345" y="8901430"/>
+          <a:off x="15013305" y="8901430"/>
           <a:ext cx="1118870" cy="1765935"/>
         </a:xfrm>
         <a:prstGeom prst="rightBrace">
@@ -3755,7 +3755,7 @@
     <col min="5" max="5" width="20.5740740740741" customWidth="1"/>
     <col min="6" max="6" width="46.8518518518519" customWidth="1"/>
     <col min="7" max="7" width="35.4444444444444" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="26.2777777777778" customWidth="1"/>
+    <col min="8" max="8" width="36.4259259259259" customWidth="1"/>
     <col min="9" max="9" width="46.1759259259259" customWidth="1"/>
     <col min="10" max="10" width="18.2592592592593" customWidth="1"/>
     <col min="11" max="11" width="26.5555555555556" customWidth="1"/>

--- a/Others/Quant模型设计.xlsx
+++ b/Others/Quant模型设计.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" tabRatio="743"/>
+    <workbookView windowWidth="22188" windowHeight="9180" tabRatio="743" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="T00" sheetId="1" r:id="rId1"/>
@@ -1648,16 +1648,7 @@
     <t>美元指数</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>行业标签数据</t>
-    </r>
+    <t>行业标签数据</t>
   </si>
   <si>
     <r>
@@ -3166,7 +3157,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3194,6 +3185,9 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3203,14 +3197,8 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3631,7 +3619,7 @@
   <dimension ref="A1:J79"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9" style="15"/>
+    <col min="1" max="1" width="9" style="14"/>
     <col min="2" max="2" width="9" style="3"/>
     <col min="3" max="3" width="12.1111111111111" style="3" customWidth="1"/>
     <col min="4" max="4" width="12.1759259259259" customWidth="1"/>
@@ -3646,7 +3634,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="19.95" customHeight="1" spans="1:10">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
@@ -3678,7 +3666,7 @@
       </c>
     </row>
     <row r="2" ht="19.95" customHeight="1" spans="1:10">
-      <c r="A2" s="17">
+      <c r="A2" s="16">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -3693,19 +3681,19 @@
       <c r="E2" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="17" t="s">
         <v>13</v>
       </c>
       <c r="G2" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="19" t="s">
+      <c r="H2" s="18" t="s">
         <v>15</v>
       </c>
       <c r="I2" s="1"/>
     </row>
     <row r="3" ht="19.95" customHeight="1" spans="1:10">
-      <c r="A3" s="17">
+      <c r="A3" s="16">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
@@ -3720,18 +3708,18 @@
       <c r="E3" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="18" t="s">
+      <c r="F3" s="17" t="s">
         <v>17</v>
       </c>
       <c r="G3" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="20" t="s">
+      <c r="H3" s="19" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="4" ht="19.95" customHeight="1" spans="1:10">
-      <c r="A4" s="17">
+      <c r="A4" s="16">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
@@ -3746,18 +3734,18 @@
       <c r="E4" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="18" t="s">
+      <c r="F4" s="17" t="s">
         <v>21</v>
       </c>
       <c r="G4" t="s">
         <v>22</v>
       </c>
-      <c r="H4" s="20" t="s">
+      <c r="H4" s="19" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="5" ht="19.95" customHeight="1" spans="1:10">
-      <c r="A5" s="17">
+      <c r="A5" s="16">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
@@ -3772,7 +3760,7 @@
       <c r="E5" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="18" t="s">
+      <c r="F5" s="17" t="s">
         <v>24</v>
       </c>
       <c r="G5" t="s">
@@ -3783,7 +3771,7 @@
       </c>
     </row>
     <row r="6" ht="19.95" customHeight="1" spans="1:10">
-      <c r="A6" s="17">
+      <c r="A6" s="16">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
@@ -3798,18 +3786,18 @@
       <c r="E6" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="18" t="s">
+      <c r="F6" s="17" t="s">
         <v>29</v>
       </c>
       <c r="G6" t="s">
         <v>30</v>
       </c>
-      <c r="H6" s="21" t="s">
+      <c r="H6" s="20" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="7" ht="19.95" customHeight="1" spans="1:10">
-      <c r="A7" s="17">
+      <c r="A7" s="16">
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
@@ -3824,18 +3812,18 @@
       <c r="E7" t="s">
         <v>32</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="F7" s="17" t="s">
         <v>33</v>
       </c>
       <c r="G7" t="s">
         <v>34</v>
       </c>
-      <c r="H7" s="21" t="s">
+      <c r="H7" s="20" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="8" ht="19.95" customHeight="1" spans="1:10">
-      <c r="A8" s="17">
+      <c r="A8" s="16">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
@@ -3850,18 +3838,18 @@
       <c r="E8" t="s">
         <v>35</v>
       </c>
-      <c r="F8" s="18" t="s">
+      <c r="F8" s="17" t="s">
         <v>36</v>
       </c>
       <c r="G8" t="s">
         <v>37</v>
       </c>
-      <c r="H8" s="20" t="s">
+      <c r="H8" s="19" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="9" ht="19.95" customHeight="1" spans="1:10">
-      <c r="A9" s="17">
+      <c r="A9" s="16">
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
@@ -3876,25 +3864,25 @@
       <c r="E9" t="s">
         <v>38</v>
       </c>
-      <c r="F9" s="18" t="s">
+      <c r="F9" s="17" t="s">
         <v>39</v>
       </c>
       <c r="G9" t="s">
         <v>40</v>
       </c>
-      <c r="H9" s="20" t="s">
+      <c r="H9" s="19" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:10">
-      <c r="G10" s="18"/>
+      <c r="G10" s="17"/>
     </row>
     <row r="11" ht="19.95" customHeight="1" spans="1:10">
-      <c r="G11" s="18"/>
+      <c r="G11" s="17"/>
     </row>
     <row r="12" ht="19.95" customHeight="1"/>
     <row r="13" ht="19.95" customHeight="1" spans="1:10">
-      <c r="A13" s="15">
+      <c r="A13" s="14">
         <v>1</v>
       </c>
       <c r="B13" s="3" t="s">
@@ -3909,18 +3897,18 @@
       <c r="E13" t="s">
         <v>42</v>
       </c>
-      <c r="F13" s="18" t="s">
+      <c r="F13" s="17" t="s">
         <v>43</v>
       </c>
       <c r="G13" t="s">
         <v>44</v>
       </c>
-      <c r="H13" s="22" t="s">
+      <c r="H13" s="21" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="14" ht="19.95" customHeight="1" spans="1:10">
-      <c r="A14" s="15">
+      <c r="A14" s="14">
         <v>2</v>
       </c>
       <c r="B14" s="3" t="s">
@@ -3935,7 +3923,7 @@
       <c r="E14" t="s">
         <v>46</v>
       </c>
-      <c r="F14" s="18" t="s">
+      <c r="F14" s="17" t="s">
         <v>47</v>
       </c>
       <c r="G14" t="s">
@@ -3946,7 +3934,7 @@
       </c>
     </row>
     <row r="15" ht="19.95" customHeight="1" spans="1:10">
-      <c r="A15" s="15">
+      <c r="A15" s="14">
         <v>3</v>
       </c>
       <c r="B15" s="3" t="s">
@@ -3961,7 +3949,7 @@
       <c r="E15" t="s">
         <v>49</v>
       </c>
-      <c r="F15" s="18" t="s">
+      <c r="F15" s="17" t="s">
         <v>50</v>
       </c>
       <c r="G15" t="s">
@@ -3972,7 +3960,7 @@
       </c>
     </row>
     <row r="16" ht="19.95" customHeight="1" spans="1:10">
-      <c r="A16" s="15">
+      <c r="A16" s="14">
         <v>4</v>
       </c>
       <c r="B16" s="3" t="s">
@@ -3987,18 +3975,18 @@
       <c r="E16" t="s">
         <v>53</v>
       </c>
-      <c r="F16" s="18" t="s">
+      <c r="F16" s="17" t="s">
         <v>54</v>
       </c>
       <c r="G16" t="s">
         <v>55</v>
       </c>
-      <c r="H16" s="22" t="s">
+      <c r="H16" s="21" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="17" ht="19.95" customHeight="1" spans="1:8">
-      <c r="A17" s="15">
+      <c r="A17" s="14">
         <v>5</v>
       </c>
       <c r="B17" s="3" t="s">
@@ -4013,18 +4001,18 @@
       <c r="E17" t="s">
         <v>57</v>
       </c>
-      <c r="F17" s="18" t="s">
+      <c r="F17" s="17" t="s">
         <v>58</v>
       </c>
       <c r="G17" t="s">
         <v>59</v>
       </c>
-      <c r="H17" s="22" t="s">
+      <c r="H17" s="21" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="18" ht="19.95" customHeight="1" spans="1:8">
-      <c r="A18" s="15">
+      <c r="A18" s="14">
         <v>6</v>
       </c>
       <c r="B18" s="3" t="s">
@@ -4039,18 +4027,18 @@
       <c r="E18" t="s">
         <v>60</v>
       </c>
-      <c r="F18" s="18" t="s">
+      <c r="F18" s="17" t="s">
         <v>61</v>
       </c>
       <c r="G18" t="s">
         <v>62</v>
       </c>
-      <c r="H18" s="22" t="s">
+      <c r="H18" s="21" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="19" ht="19.95" customHeight="1" spans="1:8">
-      <c r="A19" s="15">
+      <c r="A19" s="14">
         <v>9</v>
       </c>
       <c r="B19" s="3" t="s">
@@ -4065,31 +4053,31 @@
       <c r="E19" t="s">
         <v>65</v>
       </c>
-      <c r="F19" s="18" t="s">
+      <c r="F19" s="17" t="s">
         <v>66</v>
       </c>
       <c r="G19" t="s">
         <v>67</v>
       </c>
-      <c r="H19" s="20" t="s">
+      <c r="H19" s="19" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="20" ht="19.95" customHeight="1" spans="1:8">
-      <c r="F20" s="18"/>
-      <c r="H20" s="23"/>
+      <c r="F20" s="17"/>
+      <c r="H20" s="22"/>
     </row>
     <row r="21" ht="19.95" customHeight="1" spans="1:8">
-      <c r="E21" s="24"/>
-      <c r="F21" s="18"/>
-      <c r="H21" s="23"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="17"/>
+      <c r="H21" s="22"/>
     </row>
     <row r="22" ht="19.95" customHeight="1" spans="1:8">
-      <c r="F22" s="18"/>
-      <c r="H22" s="23"/>
+      <c r="F22" s="17"/>
+      <c r="H22" s="22"/>
     </row>
     <row r="23" ht="19.95" customHeight="1" spans="1:8">
-      <c r="A23" s="15">
+      <c r="A23" s="14">
         <v>1</v>
       </c>
       <c r="B23" s="3" t="s">
@@ -4104,18 +4092,18 @@
       <c r="E23" t="s">
         <v>70</v>
       </c>
-      <c r="F23" s="18" t="s">
+      <c r="F23" s="17" t="s">
         <v>71</v>
       </c>
       <c r="G23" t="s">
         <v>72</v>
       </c>
-      <c r="H23" s="20" t="s">
+      <c r="H23" s="19" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="24" ht="19.95" customHeight="1" spans="1:8">
-      <c r="A24" s="15">
+      <c r="A24" s="14">
         <v>2</v>
       </c>
       <c r="B24" s="3" t="s">
@@ -4130,15 +4118,15 @@
       <c r="E24" t="s">
         <v>73</v>
       </c>
-      <c r="F24" s="18" t="s">
+      <c r="F24" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="H24" s="20" t="s">
+      <c r="H24" s="19" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="25" ht="19.95" customHeight="1" spans="1:8">
-      <c r="A25" s="15">
+      <c r="A25" s="14">
         <v>3</v>
       </c>
       <c r="B25" s="3" t="s">
@@ -4153,17 +4141,17 @@
       <c r="E25" t="s">
         <v>75</v>
       </c>
-      <c r="F25" s="18" t="s">
+      <c r="F25" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="H25" s="20" t="s">
+      <c r="H25" s="19" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="26" ht="19.95" customHeight="1"/>
     <row r="27" ht="19.95" customHeight="1"/>
     <row r="28" ht="19.95" customHeight="1" spans="1:8">
-      <c r="A28" s="15">
+      <c r="A28" s="14">
         <v>1</v>
       </c>
       <c r="B28" s="3" t="s">
@@ -4178,18 +4166,18 @@
       <c r="E28" t="s">
         <v>78</v>
       </c>
-      <c r="F28" s="18" t="s">
+      <c r="F28" s="17" t="s">
         <v>79</v>
       </c>
       <c r="G28" t="s">
         <v>80</v>
       </c>
-      <c r="H28" s="20" t="s">
+      <c r="H28" s="19" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="29" ht="19.95" customHeight="1" spans="1:8">
-      <c r="A29" s="15">
+      <c r="A29" s="14">
         <v>2</v>
       </c>
       <c r="B29" s="3" t="s">
@@ -4204,20 +4192,20 @@
       <c r="E29" t="s">
         <v>81</v>
       </c>
-      <c r="F29" s="18" t="s">
+      <c r="F29" s="17" t="s">
         <v>82</v>
       </c>
       <c r="G29" t="s">
         <v>83</v>
       </c>
-      <c r="H29" s="20" t="s">
+      <c r="H29" s="19" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="30" ht="19.95" customHeight="1"/>
     <row r="31" ht="19.95" customHeight="1"/>
     <row r="32" ht="19.95" customHeight="1" spans="1:8">
-      <c r="A32" s="15">
+      <c r="A32" s="14">
         <v>1</v>
       </c>
       <c r="B32" s="3" t="s">
@@ -4232,18 +4220,18 @@
       <c r="E32" t="s">
         <v>85</v>
       </c>
-      <c r="F32" s="18" t="s">
+      <c r="F32" s="17" t="s">
         <v>86</v>
       </c>
       <c r="G32" t="s">
         <v>87</v>
       </c>
-      <c r="H32" s="20" t="s">
+      <c r="H32" s="19" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="33" ht="19.95" customHeight="1" spans="1:9">
-      <c r="A33" s="15">
+      <c r="A33" s="14">
         <v>2</v>
       </c>
       <c r="B33" s="3" t="s">
@@ -4258,18 +4246,18 @@
       <c r="E33" t="s">
         <v>88</v>
       </c>
-      <c r="F33" s="18" t="s">
+      <c r="F33" s="17" t="s">
         <v>89</v>
       </c>
       <c r="G33" t="s">
         <v>90</v>
       </c>
-      <c r="H33" s="20" t="s">
+      <c r="H33" s="19" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="34" ht="19.95" customHeight="1" spans="1:9">
-      <c r="A34" s="15">
+      <c r="A34" s="14">
         <v>8</v>
       </c>
       <c r="B34" s="3" t="s">
@@ -4281,33 +4269,33 @@
       <c r="D34" t="s">
         <v>92</v>
       </c>
-      <c r="F34" s="18" t="s">
+      <c r="F34" s="17" t="s">
         <v>93</v>
       </c>
       <c r="G34" t="s">
         <v>94</v>
       </c>
-      <c r="H34" s="25" t="s">
+      <c r="H34" s="24" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="35" ht="19.95" customHeight="1"/>
     <row r="36" ht="19.95" customHeight="1"/>
     <row r="37" ht="19.95" customHeight="1" spans="1:9">
-      <c r="A37" s="26" t="s">
+      <c r="A37" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="B37" s="26"/>
-      <c r="C37" s="26"/>
-      <c r="D37" s="26"/>
-      <c r="E37" s="26"/>
-      <c r="F37" s="26"/>
-      <c r="G37" s="26"/>
-      <c r="H37" s="26"/>
-      <c r="I37" s="26"/>
+      <c r="B37" s="25"/>
+      <c r="C37" s="25"/>
+      <c r="D37" s="25"/>
+      <c r="E37" s="25"/>
+      <c r="F37" s="25"/>
+      <c r="G37" s="25"/>
+      <c r="H37" s="25"/>
+      <c r="I37" s="25"/>
     </row>
     <row r="38" ht="124" customHeight="1" spans="1:9">
-      <c r="A38" s="15">
+      <c r="A38" s="14">
         <v>1</v>
       </c>
       <c r="B38" s="3" t="s">
@@ -4316,21 +4304,21 @@
       <c r="C38" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="F38" s="18" t="s">
+      <c r="F38" s="17" t="s">
         <v>98</v>
       </c>
       <c r="G38" t="s">
         <v>99</v>
       </c>
-      <c r="H38" s="27" t="s">
+      <c r="H38" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="I38" s="28" t="s">
+      <c r="I38" s="27" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="39" ht="31" customHeight="1" spans="1:9">
-      <c r="A39" s="17">
+      <c r="A39" s="16">
         <v>2</v>
       </c>
       <c r="B39" s="3" t="s">
@@ -4339,25 +4327,25 @@
       <c r="C39" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D39" s="10"/>
-      <c r="E39" s="10" t="s">
+      <c r="D39" s="11"/>
+      <c r="E39" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="F39" s="29" t="s">
+      <c r="F39" s="28" t="s">
         <v>102</v>
       </c>
       <c r="G39" t="s">
         <v>103</v>
       </c>
-      <c r="H39" s="20" t="s">
+      <c r="H39" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="I39" s="28" t="s">
+      <c r="I39" s="27" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="40" ht="31" customHeight="1" spans="1:9">
-      <c r="A40" s="15">
+      <c r="A40" s="14">
         <v>3</v>
       </c>
       <c r="B40" s="3" t="s">
@@ -4366,22 +4354,22 @@
       <c r="C40" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D40" s="10"/>
-      <c r="E40" s="10" t="s">
+      <c r="D40" s="11"/>
+      <c r="E40" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="F40" s="29" t="s">
+      <c r="F40" s="28" t="s">
         <v>105</v>
       </c>
-      <c r="H40" s="20" t="s">
+      <c r="H40" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="I40" s="28" t="s">
+      <c r="I40" s="27" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="41" ht="31" customHeight="1" spans="1:9">
-      <c r="A41" s="17">
+      <c r="A41" s="16">
         <v>4</v>
       </c>
       <c r="B41" s="3" t="s">
@@ -4390,22 +4378,22 @@
       <c r="C41" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D41" s="10"/>
-      <c r="E41" s="10" t="s">
+      <c r="D41" s="11"/>
+      <c r="E41" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="F41" s="29" t="s">
+      <c r="F41" s="28" t="s">
         <v>107</v>
       </c>
-      <c r="H41" s="20" t="s">
+      <c r="H41" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="I41" s="28" t="s">
+      <c r="I41" s="27" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="42" ht="98" customHeight="1" spans="1:9">
-      <c r="A42" s="15">
+      <c r="A42" s="14">
         <v>5</v>
       </c>
       <c r="B42" s="3" t="s">
@@ -4417,21 +4405,21 @@
       <c r="E42" t="s">
         <v>108</v>
       </c>
-      <c r="F42" s="18" t="s">
+      <c r="F42" s="17" t="s">
         <v>109</v>
       </c>
       <c r="G42" t="s">
         <v>110</v>
       </c>
-      <c r="H42" s="20" t="s">
+      <c r="H42" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="I42" s="28" t="s">
+      <c r="I42" s="27" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="43" ht="40" customHeight="1" spans="1:9">
-      <c r="A43" s="17">
+      <c r="A43" s="16">
         <v>6</v>
       </c>
       <c r="B43" s="3" t="s">
@@ -4443,21 +4431,21 @@
       <c r="E43" t="s">
         <v>112</v>
       </c>
-      <c r="F43" s="18" t="s">
+      <c r="F43" s="17" t="s">
         <v>113</v>
       </c>
       <c r="G43" t="s">
         <v>114</v>
       </c>
-      <c r="H43" s="20" t="s">
+      <c r="H43" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="I43" s="28" t="s">
+      <c r="I43" s="27" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="44" ht="36" customHeight="1" spans="1:9">
-      <c r="A44" s="15">
+      <c r="A44" s="14">
         <v>7</v>
       </c>
       <c r="B44" s="3" t="s">
@@ -4469,21 +4457,21 @@
       <c r="E44" t="s">
         <v>116</v>
       </c>
-      <c r="F44" s="18" t="s">
+      <c r="F44" s="17" t="s">
         <v>117</v>
       </c>
       <c r="G44" t="s">
         <v>118</v>
       </c>
-      <c r="H44" s="20" t="s">
+      <c r="H44" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="I44" s="28" t="s">
+      <c r="I44" s="27" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="45" ht="26" customHeight="1" spans="1:9">
-      <c r="A45" s="17">
+      <c r="A45" s="16">
         <v>8</v>
       </c>
       <c r="B45" s="3" t="s">
@@ -4495,38 +4483,38 @@
       <c r="E45" t="s">
         <v>120</v>
       </c>
-      <c r="F45" s="18" t="s">
+      <c r="F45" s="17" t="s">
         <v>121</v>
       </c>
       <c r="G45" t="s">
         <v>122</v>
       </c>
-      <c r="H45" s="20" t="s">
+      <c r="H45" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="I45" s="28" t="s">
+      <c r="I45" s="27" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="46" ht="19.95" customHeight="1" spans="1:9">
-      <c r="F46" s="18" t="s">
+      <c r="F46" s="17" t="s">
         <v>123</v>
       </c>
       <c r="G46" t="s">
         <v>124</v>
       </c>
-      <c r="H46" s="30" t="s">
+      <c r="H46" s="29" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="47" ht="19.95" customHeight="1" spans="1:9">
-      <c r="F47" s="18" t="s">
+      <c r="F47" s="17" t="s">
         <v>126</v>
       </c>
       <c r="G47" t="s">
         <v>127</v>
       </c>
-      <c r="H47" s="30" t="s">
+      <c r="H47" s="29" t="s">
         <v>125</v>
       </c>
     </row>
@@ -4534,17 +4522,17 @@
     <row r="49" ht="19.95" customHeight="1"/>
     <row r="50" ht="19.95" customHeight="1"/>
     <row r="51" ht="19.95" customHeight="1" spans="1:9">
-      <c r="A51" s="26" t="s">
+      <c r="A51" s="25" t="s">
         <v>128</v>
       </c>
-      <c r="B51" s="26"/>
-      <c r="C51" s="26"/>
-      <c r="D51" s="26"/>
-      <c r="E51" s="26"/>
-      <c r="F51" s="26"/>
-      <c r="G51" s="26"/>
-      <c r="H51" s="26"/>
-      <c r="I51" s="26"/>
+      <c r="B51" s="25"/>
+      <c r="C51" s="25"/>
+      <c r="D51" s="25"/>
+      <c r="E51" s="25"/>
+      <c r="F51" s="25"/>
+      <c r="G51" s="25"/>
+      <c r="H51" s="25"/>
+      <c r="I51" s="25"/>
     </row>
     <row r="52" ht="39" customHeight="1" spans="1:9">
       <c r="B52" s="3" t="s">
@@ -4553,7 +4541,7 @@
       <c r="C52" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="F52" s="18" t="s">
+      <c r="F52" s="17" t="s">
         <v>130</v>
       </c>
       <c r="G52" t="s">
@@ -4562,7 +4550,7 @@
       <c r="H52" t="s">
         <v>132</v>
       </c>
-      <c r="I52" s="28" t="s">
+      <c r="I52" s="27" t="s">
         <v>133</v>
       </c>
     </row>
@@ -4570,7 +4558,7 @@
       <c r="B53" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="F53" s="18" t="s">
+      <c r="F53" s="17" t="s">
         <v>134</v>
       </c>
       <c r="G53" t="s">
@@ -4721,7 +4709,7 @@
       <c r="A7" s="3">
         <v>1</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="12" t="s">
         <v>139</v>
       </c>
       <c r="C7" t="s">
@@ -4730,7 +4718,7 @@
       <c r="F7" s="3">
         <v>1</v>
       </c>
-      <c r="G7" s="11" t="s">
+      <c r="G7" s="12" t="s">
         <v>139</v>
       </c>
       <c r="H7" t="s">
@@ -4741,7 +4729,7 @@
       <c r="A8" s="3">
         <v>2</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="12" t="s">
         <v>141</v>
       </c>
       <c r="C8" t="s">
@@ -4750,7 +4738,7 @@
       <c r="F8" s="3">
         <v>2</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="G8" s="12" t="s">
         <v>143</v>
       </c>
       <c r="H8" t="s">
@@ -4836,7 +4824,7 @@
       <c r="A16" s="3">
         <v>1</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="12" t="s">
         <v>141</v>
       </c>
       <c r="C16" t="s">
@@ -4845,7 +4833,7 @@
       <c r="F16" s="3">
         <v>1</v>
       </c>
-      <c r="G16" s="11" t="s">
+      <c r="G16" s="12" t="s">
         <v>147</v>
       </c>
       <c r="H16" t="s">
@@ -4854,7 +4842,7 @@
       <c r="K16" s="3">
         <v>1</v>
       </c>
-      <c r="L16" s="11" t="s">
+      <c r="L16" s="12" t="s">
         <v>139</v>
       </c>
       <c r="M16" t="s">
@@ -4865,7 +4853,7 @@
       <c r="A17" s="3">
         <v>2</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="12" t="s">
         <v>139</v>
       </c>
       <c r="C17" t="s">
@@ -4883,7 +4871,7 @@
       <c r="K17" s="3">
         <v>2</v>
       </c>
-      <c r="L17" s="11" t="s">
+      <c r="L17" s="12" t="s">
         <v>152</v>
       </c>
       <c r="M17" t="s">
@@ -4903,7 +4891,7 @@
       <c r="F18" s="3">
         <v>3</v>
       </c>
-      <c r="G18" s="11" t="s">
+      <c r="G18" s="12" t="s">
         <v>139</v>
       </c>
       <c r="H18" t="s">
@@ -5125,7 +5113,7 @@
       <c r="A30" s="3">
         <v>1</v>
       </c>
-      <c r="B30" s="11" t="s">
+      <c r="B30" s="12" t="s">
         <v>141</v>
       </c>
       <c r="C30" t="s">
@@ -5134,7 +5122,7 @@
       <c r="F30" s="3">
         <v>1</v>
       </c>
-      <c r="G30" s="11" t="s">
+      <c r="G30" s="12" t="s">
         <v>141</v>
       </c>
       <c r="H30" t="s">
@@ -5143,7 +5131,7 @@
       <c r="K30" s="3">
         <v>1</v>
       </c>
-      <c r="L30" s="11" t="s">
+      <c r="L30" s="12" t="s">
         <v>139</v>
       </c>
       <c r="M30" t="s">
@@ -5152,7 +5140,7 @@
       <c r="P30" s="3">
         <v>1</v>
       </c>
-      <c r="Q30" s="11" t="s">
+      <c r="Q30" s="12" t="s">
         <v>139</v>
       </c>
       <c r="R30" t="s">
@@ -5163,7 +5151,7 @@
       <c r="A31" s="3">
         <v>2</v>
       </c>
-      <c r="B31" s="11" t="s">
+      <c r="B31" s="12" t="s">
         <v>139</v>
       </c>
       <c r="C31" t="s">
@@ -5172,7 +5160,7 @@
       <c r="F31" s="3">
         <v>2</v>
       </c>
-      <c r="G31" s="11" t="s">
+      <c r="G31" s="12" t="s">
         <v>139</v>
       </c>
       <c r="H31" t="s">
@@ -5190,7 +5178,7 @@
       <c r="P31" s="3">
         <v>2</v>
       </c>
-      <c r="Q31" s="11" t="s">
+      <c r="Q31" s="12" t="s">
         <v>141</v>
       </c>
       <c r="R31" t="s">
@@ -5257,7 +5245,7 @@
       <c r="K33" s="3">
         <v>4</v>
       </c>
-      <c r="L33" s="11" t="s">
+      <c r="L33" s="12" t="s">
         <v>187</v>
       </c>
       <c r="M33" t="s">
@@ -5586,7 +5574,7 @@
       <c r="A46" s="3">
         <v>1</v>
       </c>
-      <c r="B46" s="11" t="s">
+      <c r="B46" s="12" t="s">
         <v>141</v>
       </c>
       <c r="C46" t="s">
@@ -5626,7 +5614,7 @@
       <c r="A48" s="3">
         <v>3</v>
       </c>
-      <c r="B48" s="11" t="s">
+      <c r="B48" s="12" t="s">
         <v>139</v>
       </c>
       <c r="C48" t="s">
@@ -5824,7 +5812,7 @@
       <c r="A60" s="3">
         <v>3</v>
       </c>
-      <c r="B60" s="11" t="s">
+      <c r="B60" s="12" t="s">
         <v>141</v>
       </c>
       <c r="C60" t="s">
@@ -5836,7 +5824,7 @@
       <c r="A61" s="3">
         <v>4</v>
       </c>
-      <c r="B61" s="11" t="s">
+      <c r="B61" s="12" t="s">
         <v>139</v>
       </c>
       <c r="C61" t="s">
@@ -5879,36 +5867,36 @@
   </cols>
   <sheetData>
     <row r="3" customHeight="1" spans="1:14">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="9" t="s">
         <v>269</v>
       </c>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
     </row>
     <row r="4" customHeight="1" spans="1:14">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
     </row>
     <row r="6" customHeight="1" spans="1:14">
       <c r="C6" s="1" t="s">
@@ -7028,7 +7016,7 @@
       <c r="B61" s="3">
         <v>7</v>
       </c>
-      <c r="C61" s="10" t="s">
+      <c r="C61" s="11" t="s">
         <v>416</v>
       </c>
       <c r="D61" t="s">
@@ -7057,7 +7045,7 @@
       <c r="B62" s="3">
         <v>8</v>
       </c>
-      <c r="C62" s="10" t="s">
+      <c r="C62" s="11" t="s">
         <v>419</v>
       </c>
       <c r="D62" t="s">
@@ -7086,7 +7074,7 @@
       <c r="B63" s="3">
         <v>9</v>
       </c>
-      <c r="C63" s="10" t="s">
+      <c r="C63" s="11" t="s">
         <v>421</v>
       </c>
       <c r="D63" t="s">
@@ -7115,7 +7103,7 @@
       <c r="B64" s="3">
         <v>10</v>
       </c>
-      <c r="C64" s="10" t="s">
+      <c r="C64" s="11" t="s">
         <v>423</v>
       </c>
       <c r="D64" t="s">
@@ -7144,10 +7132,10 @@
       <c r="B65" s="3">
         <v>11</v>
       </c>
-      <c r="C65" s="10" t="s">
+      <c r="C65" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="D65" s="10" t="s">
+      <c r="D65" s="11" t="s">
         <v>413</v>
       </c>
       <c r="L65" s="3">
@@ -7173,7 +7161,7 @@
       <c r="B66" s="3">
         <v>12</v>
       </c>
-      <c r="C66" s="10" t="s">
+      <c r="C66" s="11" t="s">
         <v>166</v>
       </c>
       <c r="D66" t="s">
@@ -7421,36 +7409,36 @@
   </cols>
   <sheetData>
     <row r="3" customHeight="1" spans="1:14">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="9" t="s">
         <v>442</v>
       </c>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
     </row>
     <row r="4" customHeight="1" spans="1:14">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
     </row>
     <row r="6" customHeight="1" spans="1:14">
       <c r="C6" s="1" t="s">
@@ -7721,36 +7709,36 @@
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:14">
-      <c r="A26" s="12" t="s">
+      <c r="A26" s="9" t="s">
         <v>451</v>
       </c>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="9"/>
-      <c r="J26" s="9"/>
-      <c r="K26" s="9"/>
-      <c r="L26" s="9"/>
-      <c r="M26" s="9"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="10"/>
+      <c r="G26" s="10"/>
+      <c r="H26" s="10"/>
+      <c r="I26" s="10"/>
+      <c r="J26" s="10"/>
+      <c r="K26" s="10"/>
+      <c r="L26" s="10"/>
+      <c r="M26" s="10"/>
     </row>
     <row r="27" customHeight="1" spans="1:14">
-      <c r="A27" s="9"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="9"/>
-      <c r="J27" s="9"/>
-      <c r="K27" s="9"/>
-      <c r="L27" s="9"/>
-      <c r="M27" s="9"/>
+      <c r="A27" s="10"/>
+      <c r="B27" s="10"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="10"/>
+      <c r="F27" s="10"/>
+      <c r="G27" s="10"/>
+      <c r="H27" s="10"/>
+      <c r="I27" s="10"/>
+      <c r="J27" s="10"/>
+      <c r="K27" s="10"/>
+      <c r="L27" s="10"/>
+      <c r="M27" s="10"/>
     </row>
     <row r="30" customHeight="1" spans="1:14">
       <c r="C30" s="1" t="s">
@@ -7822,7 +7810,7 @@
       <c r="I33" s="13" t="s">
         <v>272</v>
       </c>
-      <c r="L33" s="14">
+      <c r="L33" s="3">
         <v>1</v>
       </c>
       <c r="M33" s="13" t="s">
@@ -7851,7 +7839,7 @@
       <c r="I34" t="s">
         <v>405</v>
       </c>
-      <c r="L34" s="14">
+      <c r="L34" s="3">
         <v>2</v>
       </c>
       <c r="M34" t="s">
@@ -7880,7 +7868,7 @@
       <c r="I35" s="13" t="s">
         <v>409</v>
       </c>
-      <c r="L35" s="14">
+      <c r="L35" s="3">
         <v>3</v>
       </c>
       <c r="M35" s="13" t="s">
@@ -7909,7 +7897,7 @@
       <c r="I36" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="L36" s="14">
+      <c r="L36" s="3">
         <v>4</v>
       </c>
       <c r="M36" t="s">
@@ -7938,7 +7926,7 @@
       <c r="I37" t="s">
         <v>184</v>
       </c>
-      <c r="L37" s="14">
+      <c r="L37" s="3">
         <v>5</v>
       </c>
       <c r="M37" t="s">
@@ -7967,7 +7955,7 @@
       <c r="I38" t="s">
         <v>459</v>
       </c>
-      <c r="L38" s="14">
+      <c r="L38" s="3">
         <v>6</v>
       </c>
       <c r="M38" t="s">
@@ -7987,7 +7975,7 @@
       <c r="I39" t="s">
         <v>461</v>
       </c>
-      <c r="L39" s="14">
+      <c r="L39" s="3">
         <v>7</v>
       </c>
       <c r="M39" t="s">
@@ -8007,7 +7995,7 @@
       <c r="I40" t="s">
         <v>463</v>
       </c>
-      <c r="L40" s="14">
+      <c r="L40" s="3">
         <v>8</v>
       </c>
       <c r="M40" t="s">
@@ -8027,7 +8015,7 @@
       <c r="I41" t="s">
         <v>465</v>
       </c>
-      <c r="L41" s="14">
+      <c r="L41" s="3">
         <v>9</v>
       </c>
       <c r="M41" t="s">
@@ -8423,36 +8411,36 @@
   </cols>
   <sheetData>
     <row r="3" customHeight="1" spans="1:13">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="9" t="s">
         <v>494</v>
       </c>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
     </row>
     <row r="4" customHeight="1" spans="1:13">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
     </row>
     <row r="7" customHeight="1" spans="1:13">
       <c r="B7" s="6" t="s">
@@ -8587,36 +8575,36 @@
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:13">
-      <c r="A22" s="12" t="s">
+      <c r="A22" s="9" t="s">
         <v>502</v>
       </c>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="9"/>
-      <c r="J22" s="9"/>
-      <c r="K22" s="9"/>
-      <c r="L22" s="9"/>
-      <c r="M22" s="9"/>
+      <c r="B22" s="10"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="10"/>
+      <c r="I22" s="10"/>
+      <c r="J22" s="10"/>
+      <c r="K22" s="10"/>
+      <c r="L22" s="10"/>
+      <c r="M22" s="10"/>
     </row>
     <row r="23" customHeight="1" spans="1:13">
-      <c r="A23" s="9"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="9"/>
-      <c r="J23" s="9"/>
-      <c r="K23" s="9"/>
-      <c r="L23" s="9"/>
-      <c r="M23" s="9"/>
+      <c r="A23" s="10"/>
+      <c r="B23" s="10"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="10"/>
+      <c r="I23" s="10"/>
+      <c r="J23" s="10"/>
+      <c r="K23" s="10"/>
+      <c r="L23" s="10"/>
+      <c r="M23" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -8666,7 +8654,7 @@
       <c r="B7" s="3">
         <v>1</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="12" t="s">
         <v>503</v>
       </c>
       <c r="D7" t="s">
@@ -8677,7 +8665,7 @@
       <c r="B8" s="3">
         <v>2</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="12" t="s">
         <v>504</v>
       </c>
       <c r="D8" t="s">
@@ -8781,7 +8769,7 @@
       <c r="B21" s="3">
         <v>1</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="12" t="s">
         <v>152</v>
       </c>
       <c r="D21" t="s">
@@ -8790,7 +8778,7 @@
       <c r="G21" s="3">
         <v>1</v>
       </c>
-      <c r="H21" s="11" t="s">
+      <c r="H21" s="12" t="s">
         <v>139</v>
       </c>
       <c r="I21" t="s">
@@ -8801,7 +8789,7 @@
       <c r="B22" s="3">
         <v>2</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="C22" s="12" t="s">
         <v>139</v>
       </c>
       <c r="D22" t="s">
@@ -8810,7 +8798,7 @@
       <c r="G22" s="3">
         <v>2</v>
       </c>
-      <c r="H22" s="11" t="s">
+      <c r="H22" s="12" t="s">
         <v>152</v>
       </c>
       <c r="I22" t="s">
@@ -8892,39 +8880,39 @@
       <c r="A3" s="9" t="s">
         <v>511</v>
       </c>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
     </row>
     <row r="4" customHeight="1" spans="1:13">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
     </row>
     <row r="9" customHeight="1" spans="1:13">
       <c r="C9" s="1"/>
     </row>
     <row r="10" customHeight="1" spans="1:13">
-      <c r="C10" s="10"/>
+      <c r="C10" s="11"/>
     </row>
     <row r="11" customHeight="1" spans="1:13">
       <c r="B11" s="6"/>
@@ -9162,7 +9150,6 @@
       <c r="M22" t="s">
         <v>145</v>
       </c>
-      <c r="N22"/>
       <c r="Q22" s="3">
         <v>2</v>
       </c>

--- a/Others/Quant模型设计.xlsx
+++ b/Others/Quant模型设计.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Quant\Backtrader_PJ1\Others\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Quant\Backtrader_PJ1\Quant\Others\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" tabRatio="743" activeTab="7"/>
+    <workbookView windowWidth="23040" windowHeight="10620" tabRatio="743"/>
   </bookViews>
   <sheets>
     <sheet name="T00" sheetId="1" r:id="rId1"/>

--- a/Others/Quant模型设计.xlsx
+++ b/Others/Quant模型设计.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Quant\Backtrader_PJ1\Quant\Others\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Quant\Backtrader_PJ1\Others\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="10620" tabRatio="743"/>
+    <workbookView windowWidth="22188" windowHeight="9180" tabRatio="743" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="T00" sheetId="1" r:id="rId1"/>
@@ -57,8 +57,8 @@
     <definedName name="dwd_ashare_stock_base_info">ODS_DWD_DMART!$C$19</definedName>
     <definedName name="dwd_stock_ZT_list">ODS_DWD_DMART!$C$43</definedName>
     <definedName name="dwd_stock_DT_list">ODS_DWD_DMART!$H$43</definedName>
-    <definedName name="dmart_stock_zt_details">ODS_DWD_DMART!$C$100</definedName>
-    <definedName name="dmart_stock_zt_details_expanded">ODS_DWD_DMART!$H$100</definedName>
+    <definedName name="dmart_stock_zt_details">ODS_DWD_DMART!$C$111</definedName>
+    <definedName name="dmart_stock_zt_details_expanded">ODS_DWD_DMART!$H$111</definedName>
     <definedName name="ods_akshare_stock_board_concept_cons_em">Takshare!$M$53</definedName>
     <definedName name="ods_akshare_stock_board_concept_hist_em">Takshare!$S$53</definedName>
     <definedName name="ods_akshare_stock_value_em" localSheetId="3">Tushare!$C$7</definedName>
@@ -80,8 +80,8 @@
     <definedName name="ods_tushare_stock_board_concept_hist_em">Tushare!$H$51</definedName>
     <definedName name="ods_tushare_stock_board_concept_maps_em">Tushare!$M$51</definedName>
     <definedName name="dwd_stock_technical_indicators">ODS_DWD_DMART!$M$43</definedName>
-    <definedName name="dwd_factor_volume_shrinkage">ODS_DWD_DMART!$C$74</definedName>
-    <definedName name="dwd_factor_summary">ODS_DWD_DMART!$H$74</definedName>
+    <definedName name="dwd_factor_volume_shrinkage">ODS_DWD_DMART!$C$85</definedName>
+    <definedName name="dwd_factor_summary">ODS_DWD_DMART!$H$85</definedName>
     <definedName name="ods_tushare_stock_board_concept_index_ths">Tushare!$M$31</definedName>
     <definedName name="dwd_shareholder_num_event">ODS_DWD_DMART!$M$19</definedName>
     <definedName name="dwd_shareholder_num_daily">ODS_DWD_DMART!$R$19</definedName>
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1543" uniqueCount="741">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1561" uniqueCount="743">
   <si>
     <t>序号</t>
   </si>
@@ -1869,52 +1869,40 @@
     <t>plate_names</t>
   </si>
   <si>
+    <t>ma5</t>
+  </si>
+  <si>
+    <t>5日均线</t>
+  </si>
+  <si>
+    <t>ma10</t>
+  </si>
+  <si>
+    <t>10日均线</t>
+  </si>
+  <si>
+    <t>ma20</t>
+  </si>
+  <si>
+    <t>20日均线</t>
+  </si>
+  <si>
     <t>last_close</t>
   </si>
   <si>
     <t>昨日收盘价</t>
   </si>
   <si>
+    <t>ma60</t>
+  </si>
+  <si>
+    <t>60日均线</t>
+  </si>
+  <si>
     <t>rate</t>
   </si>
   <si>
-    <t>涨幅</t>
-  </si>
-  <si>
-    <t>ma5</t>
-  </si>
-  <si>
-    <t>5日均线</t>
-  </si>
-  <si>
-    <t>ma10</t>
-  </si>
-  <si>
-    <t>10日均线</t>
-  </si>
-  <si>
-    <t>ma20</t>
-  </si>
-  <si>
-    <t>20日均线</t>
-  </si>
-  <si>
-    <t>total_asset</t>
-  </si>
-  <si>
-    <t>总资产(亿)</t>
-  </si>
-  <si>
-    <t>ma60</t>
-  </si>
-  <si>
-    <t>60日均线</t>
-  </si>
-  <si>
-    <t>net_asset</t>
-  </si>
-  <si>
-    <t>净资产(亿)</t>
+    <t>涨跌幅（%）</t>
   </si>
   <si>
     <t>ma120</t>
@@ -1923,12 +1911,30 @@
     <t>120日均线（半年线）</t>
   </si>
   <si>
+    <t>zt_type</t>
+  </si>
+  <si>
+    <t>涨停类型：yizi/tzi/shiti/zha</t>
+  </si>
+  <si>
+    <t>zt_price</t>
+  </si>
+  <si>
+    <t>理论跌停价</t>
+  </si>
+  <si>
     <t>ma250</t>
   </si>
   <si>
     <t>250日均线（年线）</t>
   </si>
   <si>
+    <t>理论涨停价</t>
+  </si>
+  <si>
+    <t>换手率（%）</t>
+  </si>
+  <si>
     <t>vol_ma5</t>
   </si>
   <si>
@@ -1983,22 +1989,22 @@
     <t>价格/60日均线-1, 单位%</t>
   </si>
   <si>
+    <t>volume_vs_ma5</t>
+  </si>
+  <si>
+    <t>成交量/5日均量-1, 单位%</t>
+  </si>
+  <si>
+    <t>volume_vs_ma20</t>
+  </si>
+  <si>
+    <t>成交量/20日均量-1, 单位%</t>
+  </si>
+  <si>
     <t>对</t>
   </si>
   <si>
     <t>打上创业、主板、科创、北证等的标识，才能计算其是否满足涨停，因为其涨跌停限制不一样</t>
-  </si>
-  <si>
-    <t>volume_vs_ma5</t>
-  </si>
-  <si>
-    <t>成交量/5日均量-1, 单位%</t>
-  </si>
-  <si>
-    <t>volume_vs_ma20</t>
-  </si>
-  <si>
-    <t>成交量/20日均量-1, 单位%</t>
   </si>
   <si>
     <t>北证的数据呢？ 能不能找到北证的stock_code</t>
@@ -8931,7 +8937,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:S109"/>
+  <dimension ref="A2:S120"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="19.95" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="8.88888888888889" style="3"/>
@@ -9760,19 +9766,19 @@
         <v>4</v>
       </c>
       <c r="C48" t="s">
-        <v>572</v>
+        <v>154</v>
       </c>
       <c r="D48" t="s">
-        <v>573</v>
+        <v>155</v>
       </c>
       <c r="G48" s="3">
         <v>4</v>
       </c>
       <c r="H48" t="s">
-        <v>572</v>
+        <v>154</v>
       </c>
       <c r="I48" t="s">
-        <v>573</v>
+        <v>155</v>
       </c>
       <c r="L48" s="3">
         <v>4</v>
@@ -9789,19 +9795,19 @@
         <v>5</v>
       </c>
       <c r="C49" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="D49" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="G49" s="3">
         <v>5</v>
       </c>
       <c r="H49" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="I49" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="L49" s="3">
         <v>5</v>
@@ -9818,28 +9824,28 @@
         <v>6</v>
       </c>
       <c r="C50" t="s">
-        <v>574</v>
+        <v>166</v>
       </c>
       <c r="D50" t="s">
-        <v>575</v>
+        <v>167</v>
       </c>
       <c r="G50" s="3">
         <v>6</v>
       </c>
       <c r="H50" t="s">
-        <v>574</v>
+        <v>166</v>
       </c>
       <c r="I50" t="s">
-        <v>575</v>
+        <v>167</v>
       </c>
       <c r="L50" s="3">
         <v>6</v>
       </c>
       <c r="M50" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="N50" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="2:14">
@@ -9847,28 +9853,28 @@
         <v>7</v>
       </c>
       <c r="C51" t="s">
-        <v>533</v>
+        <v>158</v>
       </c>
       <c r="D51" t="s">
-        <v>534</v>
+        <v>159</v>
       </c>
       <c r="G51" s="3">
         <v>7</v>
       </c>
       <c r="H51" t="s">
-        <v>533</v>
+        <v>158</v>
       </c>
       <c r="I51" t="s">
-        <v>534</v>
+        <v>159</v>
       </c>
       <c r="L51" s="3">
         <v>7</v>
       </c>
       <c r="M51" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="N51" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="2:14">
@@ -9876,28 +9882,28 @@
         <v>8</v>
       </c>
       <c r="C52" t="s">
-        <v>539</v>
+        <v>174</v>
       </c>
       <c r="D52" t="s">
-        <v>540</v>
+        <v>445</v>
       </c>
       <c r="G52" s="3">
         <v>8</v>
       </c>
       <c r="H52" t="s">
-        <v>539</v>
+        <v>174</v>
       </c>
       <c r="I52" t="s">
-        <v>540</v>
+        <v>445</v>
       </c>
       <c r="L52" s="3">
         <v>8</v>
       </c>
       <c r="M52" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="N52" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="2:14">
@@ -9905,28 +9911,28 @@
         <v>9</v>
       </c>
       <c r="C53" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="D53" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="G53" s="3">
         <v>9</v>
       </c>
       <c r="H53" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="I53" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="L53" s="3">
         <v>9</v>
       </c>
       <c r="M53" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="N53" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="2:14">
@@ -9934,28 +9940,28 @@
         <v>10</v>
       </c>
       <c r="C54" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="D54" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="G54" s="3">
         <v>10</v>
       </c>
       <c r="H54" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="I54" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="L54" s="3">
         <v>10</v>
       </c>
       <c r="M54" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="N54" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="2:14">
@@ -9963,19 +9969,19 @@
         <v>11</v>
       </c>
       <c r="C55" t="s">
-        <v>545</v>
+        <v>586</v>
       </c>
       <c r="D55" t="s">
-        <v>546</v>
+        <v>587</v>
       </c>
       <c r="G55" s="3">
         <v>11</v>
       </c>
       <c r="H55" t="s">
-        <v>545</v>
+        <v>588</v>
       </c>
       <c r="I55" t="s">
-        <v>546</v>
+        <v>589</v>
       </c>
       <c r="L55" s="3">
         <v>11</v>
@@ -9992,28 +9998,28 @@
         <v>12</v>
       </c>
       <c r="C56" t="s">
-        <v>552</v>
+        <v>588</v>
       </c>
       <c r="D56" t="s">
-        <v>553</v>
+        <v>592</v>
       </c>
       <c r="G56" s="3">
         <v>12</v>
       </c>
       <c r="H56" t="s">
-        <v>552</v>
+        <v>426</v>
       </c>
       <c r="I56" t="s">
-        <v>553</v>
+        <v>593</v>
       </c>
       <c r="L56" s="3">
         <v>12</v>
       </c>
       <c r="M56" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="N56" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="2:14">
@@ -10021,28 +10027,28 @@
         <v>13</v>
       </c>
       <c r="C57" t="s">
-        <v>558</v>
+        <v>426</v>
       </c>
       <c r="D57" t="s">
-        <v>559</v>
+        <v>593</v>
       </c>
       <c r="G57" s="3">
         <v>13</v>
       </c>
       <c r="H57" t="s">
-        <v>558</v>
+        <v>533</v>
       </c>
       <c r="I57" t="s">
-        <v>559</v>
+        <v>534</v>
       </c>
       <c r="L57" s="3">
         <v>13</v>
       </c>
       <c r="M57" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="N57" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="2:14">
@@ -10050,28 +10056,28 @@
         <v>14</v>
       </c>
       <c r="C58" t="s">
-        <v>316</v>
+        <v>533</v>
       </c>
       <c r="D58" t="s">
-        <v>317</v>
+        <v>534</v>
       </c>
       <c r="G58" s="3">
         <v>14</v>
       </c>
       <c r="H58" t="s">
-        <v>316</v>
+        <v>539</v>
       </c>
       <c r="I58" t="s">
-        <v>317</v>
+        <v>540</v>
       </c>
       <c r="L58" s="3">
         <v>14</v>
       </c>
       <c r="M58" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="N58" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="2:14">
@@ -10079,28 +10085,28 @@
         <v>15</v>
       </c>
       <c r="C59" t="s">
-        <v>566</v>
+        <v>539</v>
       </c>
       <c r="D59" t="s">
-        <v>567</v>
+        <v>540</v>
       </c>
       <c r="G59" s="3">
         <v>15</v>
       </c>
       <c r="H59" t="s">
-        <v>566</v>
+        <v>545</v>
       </c>
       <c r="I59" t="s">
-        <v>567</v>
+        <v>546</v>
       </c>
       <c r="L59" s="3">
         <v>15</v>
       </c>
       <c r="M59" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="N59" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="2:14">
@@ -10108,28 +10114,28 @@
         <v>16</v>
       </c>
       <c r="C60" t="s">
-        <v>337</v>
+        <v>545</v>
       </c>
       <c r="D60" t="s">
-        <v>499</v>
+        <v>546</v>
       </c>
       <c r="G60" s="3">
         <v>16</v>
       </c>
       <c r="H60" t="s">
-        <v>337</v>
+        <v>552</v>
       </c>
       <c r="I60" t="s">
-        <v>499</v>
+        <v>553</v>
       </c>
       <c r="L60" s="3">
         <v>16</v>
       </c>
       <c r="M60" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="N60" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="2:14">
@@ -10137,72 +10143,135 @@
         <v>17</v>
       </c>
       <c r="C61" t="s">
-        <v>571</v>
+        <v>552</v>
       </c>
       <c r="D61" t="s">
-        <v>405</v>
+        <v>553</v>
       </c>
       <c r="G61" s="3">
         <v>17</v>
       </c>
       <c r="H61" t="s">
-        <v>571</v>
+        <v>558</v>
       </c>
       <c r="I61" t="s">
-        <v>405</v>
+        <v>559</v>
       </c>
       <c r="L61" s="3">
         <v>17</v>
       </c>
       <c r="M61" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="N61" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="2:14">
+      <c r="B62" s="3">
+        <v>18</v>
+      </c>
+      <c r="C62" t="s">
+        <v>558</v>
+      </c>
+      <c r="D62" t="s">
+        <v>559</v>
+      </c>
+      <c r="G62" s="3">
+        <v>18</v>
+      </c>
+      <c r="H62" t="s">
+        <v>316</v>
+      </c>
+      <c r="I62" t="s">
+        <v>317</v>
+      </c>
       <c r="L62" s="3">
         <v>18</v>
       </c>
       <c r="M62" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="N62" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="2:14">
+      <c r="B63" s="3">
+        <v>19</v>
+      </c>
+      <c r="C63" t="s">
+        <v>316</v>
+      </c>
+      <c r="D63" t="s">
+        <v>317</v>
+      </c>
+      <c r="G63" s="3">
+        <v>19</v>
+      </c>
+      <c r="H63" t="s">
+        <v>566</v>
+      </c>
+      <c r="I63" t="s">
+        <v>567</v>
+      </c>
       <c r="L63" s="3">
         <v>19</v>
       </c>
       <c r="M63" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="N63" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="2:14">
+      <c r="B64" s="3">
+        <v>20</v>
+      </c>
+      <c r="C64" t="s">
+        <v>566</v>
+      </c>
+      <c r="D64" t="s">
+        <v>567</v>
+      </c>
+      <c r="G64" s="3">
+        <v>20</v>
+      </c>
+      <c r="H64" t="s">
+        <v>337</v>
+      </c>
+      <c r="I64" t="s">
+        <v>499</v>
+      </c>
       <c r="L64" s="3">
         <v>20</v>
       </c>
       <c r="M64" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="N64" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="65" customHeight="1" spans="1:14">
-      <c r="B65" s="3" t="s">
-        <v>610</v>
+        <v>611</v>
+      </c>
+    </row>
+    <row r="65" customHeight="1" spans="2:14">
+      <c r="B65" s="3">
+        <v>21</v>
       </c>
       <c r="C65" t="s">
-        <v>17</v>
+        <v>337</v>
       </c>
       <c r="D65" t="s">
-        <v>611</v>
+        <v>499</v>
+      </c>
+      <c r="G65" s="3">
+        <v>21</v>
+      </c>
+      <c r="H65" t="s">
+        <v>571</v>
+      </c>
+      <c r="I65" t="s">
+        <v>405</v>
       </c>
       <c r="L65" s="3">
         <v>21</v>
@@ -10214,7 +10283,16 @@
         <v>613</v>
       </c>
     </row>
-    <row r="66" customHeight="1" spans="1:14">
+    <row r="66" customHeight="1" spans="2:14">
+      <c r="B66" s="3">
+        <v>22</v>
+      </c>
+      <c r="C66" t="s">
+        <v>571</v>
+      </c>
+      <c r="D66" t="s">
+        <v>405</v>
+      </c>
       <c r="L66" s="3">
         <v>22</v>
       </c>
@@ -10225,573 +10303,584 @@
         <v>615</v>
       </c>
     </row>
-    <row r="67" customHeight="1" spans="1:14">
-      <c r="C67" t="s">
+    <row r="77" customHeight="1" spans="2:14">
+      <c r="B77" s="3" t="s">
         <v>616</v>
       </c>
-    </row>
-    <row r="70" customHeight="1" spans="1:14">
-      <c r="A70" s="7" t="s">
+      <c r="C77" t="s">
+        <v>17</v>
+      </c>
+      <c r="D77" t="s">
         <v>617</v>
       </c>
-      <c r="B70" s="7"/>
-      <c r="C70" s="7"/>
-      <c r="D70" s="7"/>
-      <c r="E70" s="7"/>
-      <c r="F70" s="7"/>
-      <c r="G70" s="7"/>
-      <c r="H70" s="7"/>
-      <c r="I70" s="7"/>
-      <c r="J70" s="7"/>
-      <c r="K70" s="7"/>
-      <c r="L70" s="7"/>
-      <c r="M70" s="7"/>
-      <c r="N70" s="7"/>
-    </row>
-    <row r="71" customHeight="1" spans="1:14">
-      <c r="A71" s="7"/>
-      <c r="B71" s="7"/>
-      <c r="C71" s="7"/>
-      <c r="D71" s="7"/>
-      <c r="E71" s="7"/>
-      <c r="F71" s="7"/>
-      <c r="G71" s="7"/>
-      <c r="H71" s="7"/>
-      <c r="I71" s="7"/>
-      <c r="J71" s="7"/>
-      <c r="K71" s="7"/>
-      <c r="L71" s="7"/>
-      <c r="M71" s="7"/>
-      <c r="N71" s="7"/>
-    </row>
-    <row r="73" customHeight="1" spans="1:14">
-      <c r="C73" s="1" t="s">
+    </row>
+    <row r="79" customHeight="1" spans="2:14">
+      <c r="C79" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="81" customHeight="1" spans="1:14">
+      <c r="A81" s="7" t="s">
+        <v>619</v>
+      </c>
+      <c r="B81" s="7"/>
+      <c r="C81" s="7"/>
+      <c r="D81" s="7"/>
+      <c r="E81" s="7"/>
+      <c r="F81" s="7"/>
+      <c r="G81" s="7"/>
+      <c r="H81" s="7"/>
+      <c r="I81" s="7"/>
+      <c r="J81" s="7"/>
+      <c r="K81" s="7"/>
+      <c r="L81" s="7"/>
+      <c r="M81" s="7"/>
+      <c r="N81" s="7"/>
+    </row>
+    <row r="82" customHeight="1" spans="1:14">
+      <c r="A82" s="7"/>
+      <c r="B82" s="7"/>
+      <c r="C82" s="7"/>
+      <c r="D82" s="7"/>
+      <c r="E82" s="7"/>
+      <c r="F82" s="7"/>
+      <c r="G82" s="7"/>
+      <c r="H82" s="7"/>
+      <c r="I82" s="7"/>
+      <c r="J82" s="7"/>
+      <c r="K82" s="7"/>
+      <c r="L82" s="7"/>
+      <c r="M82" s="7"/>
+      <c r="N82" s="7"/>
+    </row>
+    <row r="84" customHeight="1" spans="1:14">
+      <c r="C84" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="H73" s="1" t="s">
+      <c r="H84" s="1" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="74" customHeight="1" spans="1:14">
-      <c r="C74" s="1" t="s">
+    <row r="85" customHeight="1" spans="1:14">
+      <c r="C85" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="H74" s="1" t="s">
+      <c r="H85" s="1" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="75" customHeight="1" spans="1:14">
-      <c r="B75" s="6" t="s">
+    <row r="86" customHeight="1" spans="1:14">
+      <c r="B86" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="C86" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="D75" s="1" t="s">
+      <c r="D86" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="G75" s="6" t="s">
+      <c r="G86" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="H75" s="1" t="s">
+      <c r="H86" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="I75" s="1" t="s">
+      <c r="I86" s="1" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="76" customHeight="1" spans="1:14">
-      <c r="B76" s="3">
+    <row r="87" customHeight="1" spans="1:14">
+      <c r="B87" s="3">
         <v>1</v>
       </c>
-      <c r="C76" t="s">
+      <c r="C87" t="s">
         <v>139</v>
       </c>
-      <c r="D76" t="s">
+      <c r="D87" t="s">
         <v>140</v>
       </c>
-      <c r="G76" s="3">
+      <c r="G87" s="3">
         <v>1</v>
       </c>
-      <c r="H76" t="s">
+      <c r="H87" t="s">
         <v>139</v>
       </c>
-      <c r="I76" t="s">
+      <c r="I87" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="77" customHeight="1" spans="1:14">
-      <c r="B77" s="3">
+    <row r="88" customHeight="1" spans="1:14">
+      <c r="B88" s="3">
         <v>2</v>
       </c>
-      <c r="C77" t="s">
+      <c r="C88" t="s">
         <v>141</v>
       </c>
-      <c r="D77" t="s">
+      <c r="D88" t="s">
         <v>142</v>
       </c>
-      <c r="G77" s="3">
+      <c r="G88" s="3">
         <v>2</v>
       </c>
-      <c r="H77" t="s">
+      <c r="H88" t="s">
         <v>141</v>
       </c>
-      <c r="I77" t="s">
+      <c r="I88" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="78" customHeight="1" spans="1:14">
-      <c r="B78" s="3">
+    <row r="89" customHeight="1" spans="1:14">
+      <c r="B89" s="3">
         <v>3</v>
       </c>
-      <c r="C78" t="s">
+      <c r="C89" t="s">
         <v>145</v>
       </c>
-      <c r="D78" t="s">
+      <c r="D89" t="s">
         <v>184</v>
       </c>
-      <c r="G78" s="3">
+      <c r="G89" s="3">
         <v>3</v>
       </c>
-      <c r="H78" t="s">
+      <c r="H89" t="s">
         <v>145</v>
       </c>
-      <c r="I78" t="s">
+      <c r="I89" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="79" customHeight="1" spans="1:14">
-      <c r="B79" s="3">
+    <row r="90" customHeight="1" spans="1:14">
+      <c r="B90" s="3">
         <v>4</v>
       </c>
-      <c r="C79" t="s">
+      <c r="C90" t="s">
         <v>158</v>
       </c>
-      <c r="D79" t="s">
+      <c r="D90" t="s">
         <v>159</v>
       </c>
-      <c r="G79" s="3">
+      <c r="G90" s="3">
         <v>4</v>
       </c>
-      <c r="H79" t="s">
-        <v>618</v>
-      </c>
-      <c r="I79" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="80" customHeight="1" spans="1:14">
-      <c r="B80" s="3">
+      <c r="H90" t="s">
+        <v>620</v>
+      </c>
+      <c r="I90" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="91" customHeight="1" spans="1:14">
+      <c r="B91" s="3">
         <v>5</v>
       </c>
-      <c r="C80" t="s">
+      <c r="C91" t="s">
         <v>174</v>
       </c>
-      <c r="D80" t="s">
+      <c r="D91" t="s">
         <v>175</v>
       </c>
-      <c r="G80" s="3">
+      <c r="G91" s="3">
         <v>5</v>
       </c>
-      <c r="H80" t="s">
-        <v>620</v>
-      </c>
-      <c r="I80" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="81" customHeight="1" spans="1:9">
-      <c r="B81" s="3">
+      <c r="H91" t="s">
+        <v>622</v>
+      </c>
+      <c r="I91" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="92" customHeight="1" spans="1:14">
+      <c r="B92" s="3">
         <v>6</v>
       </c>
-      <c r="C81" t="s">
-        <v>592</v>
-      </c>
-      <c r="D81" t="s">
-        <v>593</v>
-      </c>
-      <c r="G81" s="3">
+      <c r="C92" t="s">
+        <v>594</v>
+      </c>
+      <c r="D92" t="s">
+        <v>595</v>
+      </c>
+      <c r="G92" s="3">
         <v>6</v>
       </c>
-      <c r="H81" t="s">
-        <v>622</v>
-      </c>
-      <c r="I81" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="82" customHeight="1" spans="1:9">
-      <c r="B82" s="3">
+      <c r="H92" t="s">
+        <v>624</v>
+      </c>
+      <c r="I92" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="93" customHeight="1" spans="1:14">
+      <c r="B93" s="3">
         <v>7</v>
       </c>
-      <c r="C82" t="s">
-        <v>598</v>
-      </c>
-      <c r="D82" t="s">
-        <v>599</v>
-      </c>
-      <c r="G82" s="3">
+      <c r="C93" t="s">
+        <v>600</v>
+      </c>
+      <c r="D93" t="s">
+        <v>601</v>
+      </c>
+      <c r="G93" s="3">
         <v>7</v>
       </c>
-      <c r="H82" t="s">
-        <v>624</v>
-      </c>
-      <c r="I82" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="83" customHeight="1" spans="1:9">
-      <c r="B83" s="3">
+      <c r="H93" t="s">
+        <v>626</v>
+      </c>
+      <c r="I93" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="94" customHeight="1" spans="1:14">
+      <c r="B94" s="3">
         <v>8</v>
       </c>
-      <c r="C83" t="s">
+      <c r="C94" t="s">
         <v>612</v>
       </c>
-      <c r="D83" t="s">
+      <c r="D94" t="s">
         <v>613</v>
       </c>
-      <c r="G83" s="3">
+      <c r="G94" s="3">
         <v>8</v>
       </c>
-      <c r="H83" t="s">
+      <c r="H94" t="s">
+        <v>628</v>
+      </c>
+      <c r="I94" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="95" customHeight="1" spans="1:14">
+      <c r="B95" s="3">
+        <v>9</v>
+      </c>
+      <c r="C95" t="s">
+        <v>630</v>
+      </c>
+      <c r="D95" t="s">
+        <v>631</v>
+      </c>
+      <c r="G95" s="3">
+        <v>9</v>
+      </c>
+      <c r="H95" t="s">
+        <v>632</v>
+      </c>
+      <c r="I95" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="96" customHeight="1" spans="1:14">
+      <c r="B96" s="3">
+        <v>10</v>
+      </c>
+      <c r="C96" t="s">
+        <v>634</v>
+      </c>
+      <c r="D96" t="s">
+        <v>635</v>
+      </c>
+      <c r="G96" s="3">
+        <v>10</v>
+      </c>
+      <c r="H96" t="s">
+        <v>636</v>
+      </c>
+      <c r="I96" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="97" customHeight="1" spans="1:9">
+      <c r="B97" s="3">
+        <v>11</v>
+      </c>
+      <c r="C97" t="s">
+        <v>449</v>
+      </c>
+      <c r="D97" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="98" customHeight="1" spans="1:9">
+      <c r="B98" s="3">
+        <v>12</v>
+      </c>
+      <c r="C98" t="s">
+        <v>639</v>
+      </c>
+      <c r="D98" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="99" customHeight="1" spans="1:9">
+      <c r="B99" s="3">
+        <v>13</v>
+      </c>
+      <c r="C99" t="s">
         <v>626</v>
       </c>
-      <c r="I83" t="s">
+      <c r="D99" t="s">
         <v>627</v>
       </c>
     </row>
-    <row r="84" customHeight="1" spans="1:9">
-      <c r="B84" s="3">
-        <v>9</v>
-      </c>
-      <c r="C84" t="s">
+    <row r="100" customHeight="1" spans="1:9">
+      <c r="B100" s="3">
+        <v>14</v>
+      </c>
+      <c r="C100" t="s">
         <v>628</v>
       </c>
-      <c r="D84" t="s">
+      <c r="D100" t="s">
         <v>629</v>
       </c>
-      <c r="G84" s="3">
-        <v>9</v>
-      </c>
-      <c r="H84" t="s">
-        <v>630</v>
-      </c>
-      <c r="I84" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="85" customHeight="1" spans="1:9">
-      <c r="B85" s="3">
-        <v>10</v>
-      </c>
-      <c r="C85" t="s">
+    </row>
+    <row r="101" customHeight="1" spans="1:9">
+      <c r="B101" s="3">
+        <v>15</v>
+      </c>
+      <c r="C101" t="s">
         <v>632</v>
       </c>
-      <c r="D85" t="s">
+      <c r="D101" t="s">
         <v>633</v>
       </c>
-      <c r="G85" s="3">
-        <v>10</v>
-      </c>
-      <c r="H85" t="s">
-        <v>634</v>
-      </c>
-      <c r="I85" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="86" customHeight="1" spans="1:9">
-      <c r="B86" s="3">
-        <v>11</v>
-      </c>
-      <c r="C86" t="s">
-        <v>449</v>
-      </c>
-      <c r="D86" t="s">
+    </row>
+    <row r="102" customHeight="1" spans="1:9">
+      <c r="B102" s="3">
+        <v>16</v>
+      </c>
+      <c r="C102" t="s">
         <v>636</v>
       </c>
-    </row>
-    <row r="87" customHeight="1" spans="1:9">
-      <c r="B87" s="3">
-        <v>12</v>
-      </c>
-      <c r="C87" t="s">
-        <v>637</v>
-      </c>
-      <c r="D87" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="88" customHeight="1" spans="1:9">
-      <c r="B88" s="3">
-        <v>13</v>
-      </c>
-      <c r="C88" t="s">
-        <v>624</v>
-      </c>
-      <c r="D88" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="89" customHeight="1" spans="1:9">
-      <c r="B89" s="3">
-        <v>14</v>
-      </c>
-      <c r="C89" t="s">
-        <v>626</v>
-      </c>
-      <c r="D89" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="90" customHeight="1" spans="1:9">
-      <c r="B90" s="3">
-        <v>15</v>
-      </c>
-      <c r="C90" t="s">
-        <v>630</v>
-      </c>
-      <c r="D90" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="91" customHeight="1" spans="1:9">
-      <c r="B91" s="3">
-        <v>16</v>
-      </c>
-      <c r="C91" t="s">
-        <v>634</v>
-      </c>
-      <c r="D91" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="95" customHeight="1" spans="1:9">
-      <c r="A95" s="7" t="s">
-        <v>640</v>
-      </c>
-      <c r="B95" s="7"/>
-      <c r="C95" s="7"/>
-      <c r="D95" s="7"/>
-      <c r="E95" s="7"/>
-      <c r="F95" s="7"/>
-      <c r="G95" s="8"/>
-      <c r="H95" s="7"/>
-      <c r="I95" s="7"/>
-    </row>
-    <row r="96" customHeight="1" spans="1:9">
-      <c r="A96" s="7"/>
-      <c r="B96" s="7"/>
-      <c r="C96" s="7"/>
-      <c r="D96" s="7"/>
-      <c r="E96" s="7"/>
-      <c r="F96" s="7"/>
-      <c r="G96" s="8"/>
-      <c r="H96" s="7"/>
-      <c r="I96" s="7"/>
-    </row>
-    <row r="99" customHeight="1" spans="2:9">
-      <c r="C99" s="1" t="s">
+      <c r="D102" t="s">
         <v>641</v>
       </c>
-      <c r="H99" s="1" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="100" customHeight="1" spans="2:9">
-      <c r="C100" s="1" t="s">
+    </row>
+    <row r="106" customHeight="1" spans="1:9">
+      <c r="A106" s="7" t="s">
+        <v>642</v>
+      </c>
+      <c r="B106" s="7"/>
+      <c r="C106" s="7"/>
+      <c r="D106" s="7"/>
+      <c r="E106" s="7"/>
+      <c r="F106" s="7"/>
+      <c r="G106" s="8"/>
+      <c r="H106" s="7"/>
+      <c r="I106" s="7"/>
+    </row>
+    <row r="107" customHeight="1" spans="1:9">
+      <c r="A107" s="7"/>
+      <c r="B107" s="7"/>
+      <c r="C107" s="7"/>
+      <c r="D107" s="7"/>
+      <c r="E107" s="7"/>
+      <c r="F107" s="7"/>
+      <c r="G107" s="8"/>
+      <c r="H107" s="7"/>
+      <c r="I107" s="7"/>
+    </row>
+    <row r="110" customHeight="1" spans="1:9">
+      <c r="C110" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="H110" s="1" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="111" customHeight="1" spans="1:9">
+      <c r="C111" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="H100" s="1" t="s">
+      <c r="H111" s="1" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="101" customHeight="1" spans="2:9">
-      <c r="B101" s="6" t="s">
+    <row r="112" customHeight="1" spans="1:9">
+      <c r="B112" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C101" s="1" t="s">
+      <c r="C112" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="D101" s="1" t="s">
+      <c r="D112" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="G101" s="6" t="s">
+      <c r="G112" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="H101" s="1" t="s">
+      <c r="H112" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="I101" s="1" t="s">
+      <c r="I112" s="1" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="102" customHeight="1" spans="2:9">
-      <c r="B102" s="3">
+    <row r="113" customHeight="1" spans="2:9">
+      <c r="B113" s="3">
         <v>1</v>
       </c>
-      <c r="C102" t="s">
+      <c r="C113" t="s">
         <v>139</v>
       </c>
-      <c r="D102" t="s">
+      <c r="D113" t="s">
         <v>140</v>
       </c>
-      <c r="G102" s="3">
+      <c r="G113" s="3">
         <v>1</v>
       </c>
-      <c r="H102" t="s">
+      <c r="H113" t="s">
         <v>139</v>
       </c>
-      <c r="I102" t="s">
+      <c r="I113" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="103" customHeight="1" spans="2:9">
-      <c r="B103" s="3">
+    <row r="114" customHeight="1" spans="2:9">
+      <c r="B114" s="3">
         <v>2</v>
       </c>
-      <c r="C103" t="s">
+      <c r="C114" t="s">
         <v>141</v>
       </c>
-      <c r="D103" t="s">
+      <c r="D114" t="s">
         <v>142</v>
       </c>
-      <c r="G103" s="3">
+      <c r="G114" s="3">
         <v>2</v>
       </c>
-      <c r="H103" t="s">
+      <c r="H114" t="s">
         <v>141</v>
       </c>
-      <c r="I103" t="s">
+      <c r="I114" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="104" customHeight="1" spans="2:9">
-      <c r="B104" s="3">
+    <row r="115" customHeight="1" spans="2:9">
+      <c r="B115" s="3">
         <v>3</v>
       </c>
-      <c r="C104" t="s">
+      <c r="C115" t="s">
         <v>145</v>
       </c>
-      <c r="D104" t="s">
+      <c r="D115" t="s">
         <v>184</v>
       </c>
-      <c r="G104" s="3">
+      <c r="G115" s="3">
         <v>3</v>
       </c>
-      <c r="H104" t="s">
+      <c r="H115" t="s">
         <v>145</v>
       </c>
-      <c r="I104" t="s">
+      <c r="I115" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="105" customHeight="1" spans="2:9">
-      <c r="B105" s="3">
+    <row r="116" customHeight="1" spans="2:9">
+      <c r="B116" s="3">
         <v>4</v>
       </c>
-      <c r="C105" t="s">
-        <v>642</v>
-      </c>
-      <c r="D105" t="s">
-        <v>643</v>
-      </c>
-      <c r="G105" s="3">
+      <c r="C116" t="s">
+        <v>644</v>
+      </c>
+      <c r="D116" t="s">
+        <v>645</v>
+      </c>
+      <c r="G116" s="3">
         <v>4</v>
       </c>
-      <c r="H105" t="s">
-        <v>642</v>
-      </c>
-      <c r="I105" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="106" customHeight="1" spans="2:9">
-      <c r="B106" s="3">
+      <c r="H116" t="s">
+        <v>644</v>
+      </c>
+      <c r="I116" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="117" customHeight="1" spans="2:9">
+      <c r="B117" s="3">
         <v>5</v>
       </c>
-      <c r="C106" t="s">
-        <v>644</v>
-      </c>
-      <c r="D106" t="s">
-        <v>645</v>
-      </c>
-      <c r="G106" s="3">
+      <c r="C117" t="s">
+        <v>646</v>
+      </c>
+      <c r="D117" t="s">
+        <v>647</v>
+      </c>
+      <c r="G117" s="3">
         <v>5</v>
       </c>
-      <c r="H106" t="s">
-        <v>644</v>
-      </c>
-      <c r="I106" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="107" customHeight="1" spans="2:9">
-      <c r="B107" s="3">
+      <c r="H117" t="s">
+        <v>646</v>
+      </c>
+      <c r="I117" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="118" customHeight="1" spans="2:9">
+      <c r="B118" s="3">
         <v>6</v>
       </c>
-      <c r="C107" t="s">
-        <v>646</v>
-      </c>
-      <c r="D107" t="s">
-        <v>647</v>
-      </c>
-      <c r="G107" s="3">
+      <c r="C118" t="s">
+        <v>648</v>
+      </c>
+      <c r="D118" t="s">
+        <v>649</v>
+      </c>
+      <c r="G118" s="3">
         <v>6</v>
       </c>
-      <c r="H107" t="s">
-        <v>646</v>
-      </c>
-      <c r="I107" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="108" customHeight="1" spans="2:9">
-      <c r="B108" s="3">
+      <c r="H118" t="s">
+        <v>648</v>
+      </c>
+      <c r="I118" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="119" customHeight="1" spans="2:9">
+      <c r="B119" s="3">
         <v>7</v>
       </c>
-      <c r="C108" t="s">
-        <v>648</v>
-      </c>
-      <c r="D108" t="s">
-        <v>649</v>
-      </c>
-      <c r="G108" s="3">
+      <c r="C119" t="s">
+        <v>650</v>
+      </c>
+      <c r="D119" t="s">
+        <v>651</v>
+      </c>
+      <c r="G119" s="3">
         <v>7</v>
       </c>
-      <c r="H108" t="s">
-        <v>648</v>
-      </c>
-      <c r="I108" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="109" customHeight="1" spans="2:9">
-      <c r="B109" s="3">
+      <c r="H119" t="s">
+        <v>650</v>
+      </c>
+      <c r="I119" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="120" customHeight="1" spans="2:9">
+      <c r="B120" s="3">
         <v>8</v>
       </c>
-      <c r="C109" t="s">
-        <v>650</v>
-      </c>
-      <c r="D109" t="s">
-        <v>651</v>
-      </c>
-      <c r="G109" s="3">
+      <c r="C120" t="s">
+        <v>652</v>
+      </c>
+      <c r="D120" t="s">
+        <v>653</v>
+      </c>
+      <c r="G120" s="3">
         <v>8</v>
       </c>
-      <c r="H109" t="s">
-        <v>650</v>
-      </c>
-      <c r="I109" t="s">
-        <v>651</v>
+      <c r="H120" t="s">
+        <v>652</v>
+      </c>
+      <c r="I120" t="s">
+        <v>653</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A2:I3"/>
     <mergeCell ref="A15:N16"/>
-    <mergeCell ref="A70:N71"/>
-    <mergeCell ref="A95:I96"/>
+    <mergeCell ref="A81:N82"/>
+    <mergeCell ref="A106:I107"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -10814,29 +10903,29 @@
   <sheetData>
     <row r="5" spans="3:9">
       <c r="C5" s="1" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="7" spans="3:9">
       <c r="F7" s="1" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
     </row>
     <row r="8" spans="3:9">
       <c r="D8" s="1" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>17</v>
@@ -10844,89 +10933,89 @@
     </row>
     <row r="9" spans="3:9">
       <c r="I9" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="13" spans="3:9">
       <c r="H13" s="1" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="14" spans="3:9">
       <c r="H14" s="1" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="15" spans="3:9">
       <c r="I15" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="19" spans="8:9">
       <c r="H19" s="1" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="20" spans="8:9">
       <c r="H20" s="1" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="21" spans="8:9">
       <c r="I21" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="25" spans="8:9">
       <c r="H25" s="1" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="26" spans="8:9">
       <c r="H26" s="1" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="27" spans="8:9">
       <c r="I27" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="31" spans="8:9">
       <c r="H31" s="1" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="32" spans="8:9">
       <c r="H32" s="1" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="33" spans="8:9">
       <c r="I33" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="37" spans="8:9">
       <c r="H37" s="1" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="38" spans="8:9">
       <c r="H38" s="1" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="I38" s="1" t="s">
         <v>21</v>
@@ -10934,12 +11023,12 @@
     </row>
     <row r="43" spans="8:9">
       <c r="H43" s="1" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="44" spans="8:9">
       <c r="H44" s="1" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="I44" s="1" t="s">
         <v>86</v>
@@ -10947,17 +11036,17 @@
     </row>
     <row r="45" spans="8:9">
       <c r="I45" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
     </row>
     <row r="49" ht="13" customHeight="1" spans="6:9">
       <c r="H49" s="1" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="50" spans="6:9">
       <c r="H50" s="1" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>89</v>
@@ -10965,41 +11054,41 @@
     </row>
     <row r="51" spans="6:9">
       <c r="I51" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="55" spans="6:9">
       <c r="H55" s="1" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
     </row>
     <row r="56" spans="6:9">
       <c r="H56" s="1" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
     </row>
     <row r="57" spans="6:9">
       <c r="I57" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
     </row>
     <row r="61" spans="6:9">
       <c r="F61" s="1" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
     </row>
     <row r="62" spans="6:9">
       <c r="F62" s="1" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="I62" s="1" t="s">
         <v>43</v>
@@ -11007,17 +11096,17 @@
     </row>
     <row r="63" spans="6:9">
       <c r="I63" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="65" spans="8:9">
       <c r="H65" s="1" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
     </row>
     <row r="66" spans="8:9">
       <c r="H66" s="1" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="I66" s="1" t="s">
         <v>47</v>
@@ -11025,17 +11114,17 @@
     </row>
     <row r="67" spans="8:9">
       <c r="I67" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="69" spans="8:9">
       <c r="H69" s="1" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
     </row>
     <row r="70" spans="8:9">
       <c r="H70" s="1" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="I70" s="1" t="s">
         <v>79</v>
@@ -11043,35 +11132,35 @@
     </row>
     <row r="71" spans="8:9">
       <c r="I71" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="73" spans="8:9">
       <c r="H73" s="1" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
     </row>
     <row r="74" spans="8:9">
       <c r="H74" s="1" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
     </row>
     <row r="75" spans="8:9">
       <c r="I75" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
     </row>
     <row r="77" spans="8:9">
       <c r="H77" s="1" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
     </row>
     <row r="78" spans="8:9">
       <c r="H78" s="1" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="I78" s="1" t="s">
         <v>24</v>
@@ -11079,17 +11168,17 @@
     </row>
     <row r="79" spans="8:9">
       <c r="I79" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
     </row>
     <row r="81" spans="6:9">
       <c r="H81" s="1" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="82" spans="6:9">
       <c r="H82" s="1" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="I82" s="1" t="s">
         <v>264</v>
@@ -11097,41 +11186,41 @@
     </row>
     <row r="83" spans="6:9">
       <c r="I83" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
     </row>
     <row r="87" spans="6:9">
       <c r="F87" s="1" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
     </row>
     <row r="88" spans="6:9">
       <c r="F88" s="1" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
     </row>
     <row r="89" spans="6:9">
       <c r="I89" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
     </row>
     <row r="92" spans="6:9">
       <c r="H92" s="1" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
     </row>
     <row r="93" spans="6:9">
       <c r="H93" s="1" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="I93" s="1" t="s">
         <v>102</v>
@@ -11139,17 +11228,17 @@
     </row>
     <row r="94" spans="6:9">
       <c r="I94" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
     </row>
     <row r="97" spans="6:9">
       <c r="H97" s="1" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
     </row>
     <row r="98" spans="6:9">
       <c r="H98" s="1" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="I98" s="1" t="s">
         <v>109</v>
@@ -11157,17 +11246,17 @@
     </row>
     <row r="99" spans="6:9">
       <c r="I99" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
     </row>
     <row r="101" spans="6:9">
       <c r="H101" s="1" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
     </row>
     <row r="102" spans="6:9">
       <c r="H102" s="1" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="I102" s="1" t="s">
         <v>113</v>
@@ -11175,7 +11264,7 @@
     </row>
     <row r="103" spans="6:9">
       <c r="I103" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
     </row>
     <row r="105" spans="6:9">
@@ -11185,23 +11274,23 @@
     </row>
     <row r="106" spans="6:9">
       <c r="I106" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
     </row>
     <row r="109" spans="6:9">
       <c r="F109" s="1" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
     </row>
     <row r="110" spans="6:9">
       <c r="F110" s="1" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="I110" s="1" t="s">
         <v>130</v>
@@ -11209,17 +11298,17 @@
     </row>
     <row r="111" spans="6:9">
       <c r="I111" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
     </row>
     <row r="114" spans="6:9">
       <c r="H114" s="1" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
     </row>
     <row r="115" spans="6:9">
       <c r="H115" s="1" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="I115" s="1" t="s">
         <v>134</v>
@@ -11227,23 +11316,23 @@
     </row>
     <row r="116" spans="6:9">
       <c r="I116" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
     </row>
     <row r="120" spans="6:9">
       <c r="F120" s="1" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
     </row>
     <row r="121" spans="6:9">
       <c r="F121" s="1" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="I121" s="1" t="s">
         <v>43</v>
@@ -11251,12 +11340,12 @@
     </row>
     <row r="124" spans="6:9">
       <c r="H124" s="1" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
     </row>
     <row r="125" spans="6:9">
       <c r="H125" s="1" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="I125" s="1" t="s">
         <v>47</v>
@@ -11264,12 +11353,12 @@
     </row>
     <row r="128" spans="6:9">
       <c r="H128" s="1" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
     </row>
     <row r="129" spans="8:9">
       <c r="H129" s="1" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="I129" s="1" t="s">
         <v>79</v>
@@ -11277,12 +11366,12 @@
     </row>
     <row r="132" spans="8:9">
       <c r="H132" s="1" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
     </row>
     <row r="133" spans="8:9">
       <c r="H133" s="1" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="I133" s="1" t="s">
         <v>50</v>
@@ -11290,12 +11379,12 @@
     </row>
     <row r="136" spans="8:9">
       <c r="H136" s="1" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
     </row>
     <row r="137" spans="8:9">
       <c r="H137" s="1" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="I137" s="1" t="s">
         <v>24</v>
@@ -11308,7 +11397,7 @@
     </row>
     <row r="158" spans="6:6">
       <c r="F158" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
     </row>
   </sheetData>

--- a/Others/Quant模型设计.xlsx
+++ b/Others/Quant模型设计.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Quant\Backtrader_PJ1\Others\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Quant\Backtrader_PJ1\Quant\Others\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" tabRatio="743" activeTab="7"/>
+    <workbookView windowWidth="23040" windowHeight="10620" tabRatio="743"/>
   </bookViews>
   <sheets>
     <sheet name="T00" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <sheet name="Sheet2" sheetId="7" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">T00!$A$1:$L$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">T00!$A$1:$L$51</definedName>
     <definedName name="ods_akshare_stock_value_em">Takshare!$C$7</definedName>
     <definedName name="ods_akshare_stock_zh_a_gdhs_detail_em">Takshare!$H$7</definedName>
     <definedName name="ods_akshare_stock_cyq_em">Takshare!$M$7</definedName>
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1561" uniqueCount="743">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1509" uniqueCount="726">
   <si>
     <t>序号</t>
   </si>
@@ -499,31 +499,6 @@
   </si>
   <si>
     <t>DMART 层</t>
-  </si>
-  <si>
-    <t>DMART</t>
-  </si>
-  <si>
-    <t>dmart_stock_zt_details</t>
-  </si>
-  <si>
-    <t>股票涨停明细（所属板块）</t>
-  </si>
-  <si>
-    <t>更新至20250319</t>
-  </si>
-  <si>
-    <t>dwd_ashare_stock_base_info
-dwd_stock_ZT_list</t>
-  </si>
-  <si>
-    <t>dmart_stock_zt_details_expanded</t>
-  </si>
-  <si>
-    <t>股票涨停明细拆分</t>
-  </si>
-  <si>
-    <t>更新至20250318</t>
   </si>
   <si>
     <t>字段英文名称</t>
@@ -2118,39 +2093,6 @@
       </rPr>
       <t>层</t>
     </r>
-  </si>
-  <si>
-    <t>股票涨停明细</t>
-  </si>
-  <si>
-    <t>concept_plate</t>
-  </si>
-  <si>
-    <t>概念板块</t>
-  </si>
-  <si>
-    <t>index_plate</t>
-  </si>
-  <si>
-    <t>指数板块</t>
-  </si>
-  <si>
-    <t>industry_plate</t>
-  </si>
-  <si>
-    <t>行业板块</t>
-  </si>
-  <si>
-    <t>style_plate</t>
-  </si>
-  <si>
-    <t>风格板块</t>
-  </si>
-  <si>
-    <t>out_plate</t>
-  </si>
-  <si>
-    <t>外部数据板块</t>
   </si>
   <si>
     <t>数据准备模块</t>
@@ -2404,6 +2346,9 @@
     <t>cal_zt_details</t>
   </si>
   <si>
+    <t>dmart_stock_zt_details</t>
+  </si>
+  <si>
     <t>ymd,stock_code,stock_name,concept_plate,index_plate,industry_plate,style_plate,out_plate</t>
   </si>
   <si>
@@ -2411,6 +2356,9 @@
   </si>
   <si>
     <t>cal_zt_details_explode</t>
+  </si>
+  <si>
+    <t>dmart_stock_zt_details_expanded</t>
   </si>
   <si>
     <t>补数：下载历史数据</t>
@@ -3622,7 +3570,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J79"/>
+  <dimension ref="A1:J77"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="9" style="14"/>
@@ -4300,7 +4248,7 @@
       <c r="H37" s="25"/>
       <c r="I37" s="25"/>
     </row>
-    <row r="38" ht="124" customHeight="1" spans="1:9">
+    <row r="38" ht="80" customHeight="1" spans="1:9">
       <c r="A38" s="14">
         <v>1</v>
       </c>
@@ -4540,43 +4488,8 @@
       <c r="H51" s="25"/>
       <c r="I51" s="25"/>
     </row>
-    <row r="52" ht="39" customHeight="1" spans="1:9">
-      <c r="B52" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F52" s="17" t="s">
-        <v>130</v>
-      </c>
-      <c r="G52" t="s">
-        <v>131</v>
-      </c>
-      <c r="H52" t="s">
-        <v>132</v>
-      </c>
-      <c r="I52" s="27" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="53" ht="24" customHeight="1" spans="1:9">
-      <c r="B53" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F53" s="17" t="s">
-        <v>134</v>
-      </c>
-      <c r="G53" t="s">
-        <v>135</v>
-      </c>
-      <c r="H53" t="s">
-        <v>136</v>
-      </c>
-      <c r="I53" t="s">
-        <v>130</v>
-      </c>
-    </row>
+    <row r="52" ht="19.95" customHeight="1"/>
+    <row r="53" ht="19.95" customHeight="1"/>
     <row r="54" ht="19.95" customHeight="1"/>
     <row r="55" ht="19.95" customHeight="1"/>
     <row r="56" ht="19.95" customHeight="1"/>
@@ -4601,10 +4514,8 @@
     <row r="75" ht="19.95" customHeight="1"/>
     <row r="76" ht="19.95" customHeight="1"/>
     <row r="77" ht="19.95" customHeight="1"/>
-    <row r="78" ht="19.95" customHeight="1"/>
-    <row r="79" ht="19.95" customHeight="1"/>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L53" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L51" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <mergeCells count="2">
@@ -4635,8 +4546,6 @@
     <hyperlink ref="F42" location="dwd_ashare_stock_base_info" display="dwd_ashare_stock_base_info"/>
     <hyperlink ref="F43" location="dwd_stock_ZT_list" display="dwd_stock_zt_list"/>
     <hyperlink ref="F44" location="dwd_stock_DT_list" display="dwd_stock_dt_list"/>
-    <hyperlink ref="F52" location="dmart_stock_zt_details" display="dmart_stock_zt_details"/>
-    <hyperlink ref="F53" location="dmart_stock_zt_details_expanded" display="dmart_stock_zt_details_expanded"/>
     <hyperlink ref="F19" location="ods_stock_kline_daily_ts" display="ods_stock_kline_daily_ts"/>
     <hyperlink ref="F23" location="ods_tushare_board_concept_name_ths" display="ods_tushare_board_concept_name_ths"/>
     <hyperlink ref="F45" location="dwd_stock_technical_indicators" display="dwd_stock_technical_indicators"/>
@@ -4696,19 +4605,19 @@
         <v>0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>0</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:13">
@@ -4716,19 +4625,19 @@
         <v>1</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="C7" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="F7" s="3">
         <v>1</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="H7" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:13">
@@ -4736,19 +4645,19 @@
         <v>2</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="C8" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="F8" s="3">
         <v>2</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="H8" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:13">
@@ -4756,10 +4665,10 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="C9" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="F9" s="3"/>
     </row>
@@ -4768,10 +4677,10 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="C10" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="F10" s="3"/>
     </row>
@@ -4802,28 +4711,28 @@
         <v>0</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>0</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="K15" s="6" t="s">
         <v>0</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:13">
@@ -4831,28 +4740,28 @@
         <v>1</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="C16" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="F16" s="3">
         <v>1</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="H16" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="K16" s="3">
         <v>1</v>
       </c>
       <c r="L16" s="12" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="M16" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:18">
@@ -4860,28 +4769,28 @@
         <v>2</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="C17" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="F17" s="3">
         <v>2</v>
       </c>
       <c r="G17" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="H17" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="K17" s="3">
         <v>2</v>
       </c>
       <c r="L17" s="12" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="M17" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:18">
@@ -4889,28 +4798,28 @@
         <v>3</v>
       </c>
       <c r="B18" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="C18" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="F18" s="3">
         <v>3</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="H18" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="K18" s="3">
         <v>3</v>
       </c>
       <c r="L18" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="M18" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:18">
@@ -4918,28 +4827,28 @@
         <v>4</v>
       </c>
       <c r="B19" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="C19" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="F19" s="3">
         <v>4</v>
       </c>
       <c r="G19" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="H19" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="K19" s="3">
         <v>4</v>
       </c>
       <c r="L19" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="M19" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:18">
@@ -4947,28 +4856,28 @@
         <v>5</v>
       </c>
       <c r="B20" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C20" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="F20" s="3">
         <v>5</v>
       </c>
       <c r="G20" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="H20" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="K20" s="3">
         <v>5</v>
       </c>
       <c r="L20" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="M20" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:18">
@@ -4976,28 +4885,28 @@
         <v>6</v>
       </c>
       <c r="B21" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C21" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="F21" s="3">
         <v>6</v>
       </c>
       <c r="G21" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="H21" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="K21" s="3">
         <v>6</v>
       </c>
       <c r="L21" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="M21" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:18">
@@ -5005,28 +4914,28 @@
         <v>7</v>
       </c>
       <c r="B22" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="C22" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="F22" s="3">
         <v>7</v>
       </c>
       <c r="G22" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="H22" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="K22" s="3">
         <v>7</v>
       </c>
       <c r="L22" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="M22" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:18">
@@ -5034,19 +4943,19 @@
         <v>8</v>
       </c>
       <c r="B23" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="C23" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="F23" s="3">
         <v>8</v>
       </c>
       <c r="G23" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="H23" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:18">
@@ -5082,37 +4991,37 @@
         <v>0</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="F29" s="6" t="s">
         <v>0</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="K29" s="6" t="s">
         <v>0</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="P29" s="6" t="s">
         <v>0</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:18">
@@ -5120,37 +5029,37 @@
         <v>1</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="C30" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="F30" s="3">
         <v>1</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="H30" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="K30" s="3">
         <v>1</v>
       </c>
       <c r="L30" s="12" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="M30" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="P30" s="3">
         <v>1</v>
       </c>
       <c r="Q30" s="12" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="R30" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:18">
@@ -5158,37 +5067,37 @@
         <v>2</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="C31" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="F31" s="3">
         <v>2</v>
       </c>
       <c r="G31" s="12" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="H31" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="K31" s="3">
         <v>2</v>
       </c>
       <c r="L31" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="M31" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="P31" s="3">
         <v>2</v>
       </c>
       <c r="Q31" s="12" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="R31" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="1:18">
@@ -5196,37 +5105,37 @@
         <v>3</v>
       </c>
       <c r="B32" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="C32" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="F32" s="3">
         <v>3</v>
       </c>
       <c r="G32" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="H32" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="K32" s="3">
         <v>3</v>
       </c>
       <c r="L32" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="M32" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="P32" s="3">
         <v>3</v>
       </c>
       <c r="Q32" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="R32" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="1:18">
@@ -5234,37 +5143,37 @@
         <v>4</v>
       </c>
       <c r="B33" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="C33" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="F33" s="3">
         <v>4</v>
       </c>
       <c r="G33" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="H33" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="K33" s="3">
         <v>4</v>
       </c>
       <c r="L33" s="12" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="M33" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="P33" s="3">
         <v>4</v>
       </c>
       <c r="Q33" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="R33" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="1:18">
@@ -5272,37 +5181,37 @@
         <v>5</v>
       </c>
       <c r="B34" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C34" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="F34" s="3">
         <v>5</v>
       </c>
       <c r="G34" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="H34" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="K34" s="3">
         <v>5</v>
       </c>
       <c r="L34" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="M34" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="P34" s="3">
         <v>5</v>
       </c>
       <c r="Q34" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="R34" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="1:18">
@@ -5310,37 +5219,37 @@
         <v>6</v>
       </c>
       <c r="B35" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C35" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="F35" s="3">
         <v>6</v>
       </c>
       <c r="G35" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="H35" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="K35" s="3">
         <v>6</v>
       </c>
       <c r="L35" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="M35" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="P35" s="3">
         <v>6</v>
       </c>
       <c r="Q35" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="R35" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="1:18">
@@ -5348,37 +5257,37 @@
         <v>7</v>
       </c>
       <c r="B36" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="C36" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="F36" s="3">
         <v>7</v>
       </c>
       <c r="G36" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="H36" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="K36" s="3">
         <v>7</v>
       </c>
       <c r="L36" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="M36" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="P36" s="3">
         <v>7</v>
       </c>
       <c r="Q36" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="R36" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="1:18">
@@ -5386,37 +5295,37 @@
         <v>8</v>
       </c>
       <c r="B37" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C37" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="F37" s="3">
         <v>8</v>
       </c>
       <c r="G37" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="H37" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="K37" s="3">
         <v>8</v>
       </c>
       <c r="L37" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="M37" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="P37" s="3">
         <v>8</v>
       </c>
       <c r="Q37" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="R37" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="1:18">
@@ -5424,37 +5333,37 @@
         <v>9</v>
       </c>
       <c r="B38" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C38" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="F38" s="3">
         <v>9</v>
       </c>
       <c r="G38" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="H38" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="K38" s="3">
         <v>9</v>
       </c>
       <c r="L38" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="M38" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="P38" s="3">
         <v>9</v>
       </c>
       <c r="Q38" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="R38" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="1:18">
@@ -5462,28 +5371,28 @@
         <v>10</v>
       </c>
       <c r="G39" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="H39" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="K39" s="3">
         <v>10</v>
       </c>
       <c r="L39" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="M39" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="P39" s="3">
         <v>10</v>
       </c>
       <c r="Q39" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="R39" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="1:18">
@@ -5491,19 +5400,19 @@
         <v>11</v>
       </c>
       <c r="G40" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="H40" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="P40" s="3">
         <v>11</v>
       </c>
       <c r="Q40" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="R40" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="1:18">
@@ -5511,10 +5420,10 @@
         <v>12</v>
       </c>
       <c r="G41" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="H41" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="1:18">
@@ -5522,10 +5431,10 @@
         <v>13</v>
       </c>
       <c r="G42" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="H42" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="1:18">
@@ -5536,10 +5445,10 @@
         <v>14</v>
       </c>
       <c r="G43" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="H43" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="1:18">
@@ -5550,10 +5459,10 @@
         <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="H44" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="1:18">
@@ -5561,19 +5470,19 @@
         <v>0</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="F45" s="3">
         <v>16</v>
       </c>
       <c r="G45" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="H45" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="1:18">
@@ -5581,19 +5490,19 @@
         <v>1</v>
       </c>
       <c r="B46" s="12" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="C46" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="F46" s="3">
         <v>17</v>
       </c>
       <c r="G46" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="H46" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="1:18">
@@ -5601,19 +5510,19 @@
         <v>2</v>
       </c>
       <c r="B47" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="C47" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="F47" s="3">
         <v>18</v>
       </c>
       <c r="G47" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="H47" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="1:18">
@@ -5621,19 +5530,19 @@
         <v>3</v>
       </c>
       <c r="B48" s="12" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="C48" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="F48" s="3">
         <v>19</v>
       </c>
       <c r="G48" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="H48" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="1:8">
@@ -5641,19 +5550,19 @@
         <v>4</v>
       </c>
       <c r="B49" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="C49" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="F49" s="3">
         <v>20</v>
       </c>
       <c r="G49" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="H49" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="1:8">
@@ -5661,19 +5570,19 @@
         <v>5</v>
       </c>
       <c r="B50" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="C50" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="F50" s="3">
         <v>21</v>
       </c>
       <c r="G50" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="H50" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="1:8">
@@ -5681,19 +5590,19 @@
         <v>6</v>
       </c>
       <c r="B51" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="C51" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="F51" s="3">
         <v>22</v>
       </c>
       <c r="G51" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="H51" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="1:8">
@@ -5701,19 +5610,19 @@
         <v>7</v>
       </c>
       <c r="B52" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="C52" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="F52" s="3">
         <v>23</v>
       </c>
       <c r="G52" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="H52" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="1:8">
@@ -5721,19 +5630,19 @@
         <v>8</v>
       </c>
       <c r="B53" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="C53" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="F53" s="3">
         <v>24</v>
       </c>
       <c r="G53" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="H53" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="1:8">
@@ -5741,19 +5650,19 @@
         <v>9</v>
       </c>
       <c r="B54" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="C54" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="F54" s="3">
         <v>25</v>
       </c>
       <c r="G54" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="H54" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="1:8">
@@ -5761,10 +5670,10 @@
         <v>26</v>
       </c>
       <c r="G55" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="H55" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="1:8">
@@ -5772,10 +5681,10 @@
         <v>27</v>
       </c>
       <c r="G56" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="H56" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="1:8">
@@ -5783,10 +5692,10 @@
         <v>0</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="F57" s="3"/>
     </row>
@@ -5795,10 +5704,10 @@
         <v>1</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="C58" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="F58" s="3"/>
     </row>
@@ -5807,10 +5716,10 @@
         <v>2</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="C59" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="F59" s="3"/>
     </row>
@@ -5819,10 +5728,10 @@
         <v>3</v>
       </c>
       <c r="B60" s="12" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="C60" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="F60" s="3"/>
     </row>
@@ -5831,20 +5740,20 @@
         <v>4</v>
       </c>
       <c r="B61" s="12" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="C61" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="1:8">
       <c r="B62" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="1:8">
       <c r="B63" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
     </row>
   </sheetData>
@@ -5874,7 +5783,7 @@
   <sheetData>
     <row r="3" customHeight="1" spans="1:14">
       <c r="A3" s="9" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="B3" s="10"/>
       <c r="C3" s="10"/>
@@ -5913,7 +5822,7 @@
       </c>
       <c r="L6" s="3"/>
       <c r="M6" s="1" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:14">
@@ -5925,7 +5834,7 @@
       </c>
       <c r="L7" s="3"/>
       <c r="M7" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:14">
@@ -5933,28 +5842,28 @@
         <v>0</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>0</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:14">
@@ -5962,28 +5871,28 @@
         <v>1</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="G9" s="3">
         <v>1</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="L9" s="3">
         <v>1</v>
       </c>
       <c r="M9" s="13" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="N9" s="13" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:14">
@@ -5991,28 +5900,28 @@
         <v>2</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="G10" s="3">
         <v>2</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L10" s="3">
         <v>2</v>
       </c>
       <c r="M10" s="13" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="N10" s="13" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:14">
@@ -6020,28 +5929,28 @@
         <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="G11" s="3">
         <v>3</v>
       </c>
       <c r="H11" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="I11" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="L11" s="3">
         <v>3</v>
       </c>
       <c r="M11" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="N11" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:14">
@@ -6049,28 +5958,28 @@
         <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="D12" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="G12" s="3">
         <v>4</v>
       </c>
       <c r="H12" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="I12" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="L12" s="3">
         <v>4</v>
       </c>
       <c r="M12" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="N12" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:14">
@@ -6078,28 +5987,28 @@
         <v>5</v>
       </c>
       <c r="C13" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="D13" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="G13" s="3">
         <v>5</v>
       </c>
       <c r="H13" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="I13" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="L13" s="3">
         <v>5</v>
       </c>
       <c r="M13" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="N13" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:14">
@@ -6107,28 +6016,28 @@
         <v>6</v>
       </c>
       <c r="C14" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="D14" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="G14" s="3">
         <v>6</v>
       </c>
       <c r="H14" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="I14" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="L14" s="3">
         <v>6</v>
       </c>
       <c r="M14" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="N14" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:14">
@@ -6136,28 +6045,28 @@
         <v>7</v>
       </c>
       <c r="C15" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="D15" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="G15" s="3">
         <v>7</v>
       </c>
       <c r="H15" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="I15" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="L15" s="3">
         <v>7</v>
       </c>
       <c r="M15" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="N15" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:14">
@@ -6165,28 +6074,28 @@
         <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="D16" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="G16" s="3">
         <v>8</v>
       </c>
       <c r="H16" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="I16" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="L16" s="3">
         <v>8</v>
       </c>
       <c r="M16" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="N16" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="2:14">
@@ -6194,28 +6103,28 @@
         <v>9</v>
       </c>
       <c r="C17" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="D17" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="G17" s="3">
         <v>9</v>
       </c>
       <c r="H17" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="I17" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="L17" s="3">
         <v>9</v>
       </c>
       <c r="M17" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="N17" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="2:14">
@@ -6223,28 +6132,28 @@
         <v>10</v>
       </c>
       <c r="C18" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="D18" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="G18" s="3">
         <v>10</v>
       </c>
       <c r="H18" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="I18" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="L18" s="3">
         <v>10</v>
       </c>
       <c r="M18" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="N18" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="2:14">
@@ -6252,28 +6161,28 @@
         <v>11</v>
       </c>
       <c r="C19" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="D19" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="G19" s="3">
         <v>11</v>
       </c>
       <c r="H19" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="I19" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="L19" s="3">
         <v>11</v>
       </c>
       <c r="M19" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="N19" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="2:14">
@@ -6281,19 +6190,19 @@
         <v>12</v>
       </c>
       <c r="C20" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="D20" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="G20" s="3">
         <v>12</v>
       </c>
       <c r="H20" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="I20" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="2:14">
@@ -6301,19 +6210,19 @@
         <v>13</v>
       </c>
       <c r="C21" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="D21" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="G21" s="3">
         <v>13</v>
       </c>
       <c r="H21" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="I21" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="2:14">
@@ -6321,19 +6230,19 @@
         <v>14</v>
       </c>
       <c r="C22" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="D22" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="G22" s="3">
         <v>14</v>
       </c>
       <c r="H22" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="I22" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="2:14">
@@ -6341,10 +6250,10 @@
         <v>15</v>
       </c>
       <c r="H23" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="I23" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="2:14">
@@ -6374,28 +6283,28 @@
         <v>0</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="G28" s="6" t="s">
         <v>0</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="L28" s="6" t="s">
         <v>0</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="2:14">
@@ -6403,28 +6312,28 @@
         <v>1</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="G29" s="3">
         <v>1</v>
       </c>
       <c r="H29" s="13" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="I29" s="13" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="L29" s="3">
         <v>1</v>
       </c>
       <c r="M29" s="13" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="N29" s="13" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="2:14">
@@ -6432,7 +6341,7 @@
         <v>2</v>
       </c>
       <c r="C30" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="D30" t="s">
         <v>0</v>
@@ -6441,7 +6350,7 @@
         <v>2</v>
       </c>
       <c r="H30" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="I30" t="s">
         <v>0</v>
@@ -6450,10 +6359,10 @@
         <v>2</v>
       </c>
       <c r="M30" s="13" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="N30" s="13" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="2:14">
@@ -6461,28 +6370,28 @@
         <v>3</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="G31" s="3">
         <v>3</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="I31" s="13" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L31" s="3">
         <v>3</v>
       </c>
       <c r="M31" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="N31" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="2:14">
@@ -6490,28 +6399,28 @@
         <v>4</v>
       </c>
       <c r="C32" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="D32" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="G32" s="3">
         <v>4</v>
       </c>
       <c r="H32" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="I32" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="L32" s="3">
         <v>4</v>
       </c>
       <c r="M32" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="N32" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="2:14">
@@ -6519,28 +6428,28 @@
         <v>5</v>
       </c>
       <c r="C33" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="D33" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="G33" s="3">
         <v>5</v>
       </c>
       <c r="H33" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="I33" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="L33" s="3">
         <v>5</v>
       </c>
       <c r="M33" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="N33" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="2:14">
@@ -6548,28 +6457,28 @@
         <v>6</v>
       </c>
       <c r="C34" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="D34" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="G34" s="3">
         <v>6</v>
       </c>
       <c r="H34" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="I34" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="L34" s="3">
         <v>6</v>
       </c>
       <c r="M34" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="N34" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="2:14">
@@ -6577,28 +6486,28 @@
         <v>7</v>
       </c>
       <c r="C35" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="D35" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="G35" s="3">
         <v>7</v>
       </c>
       <c r="H35" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="I35" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="L35" s="3">
         <v>7</v>
       </c>
       <c r="M35" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="N35" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="2:14">
@@ -6606,28 +6515,28 @@
         <v>8</v>
       </c>
       <c r="C36" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="D36" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="G36" s="3">
         <v>8</v>
       </c>
       <c r="H36" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="I36" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="L36" s="3">
         <v>8</v>
       </c>
       <c r="M36" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="N36" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="2:14">
@@ -6635,28 +6544,28 @@
         <v>9</v>
       </c>
       <c r="C37" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="D37" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="G37" s="3">
         <v>9</v>
       </c>
       <c r="H37" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="I37" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="L37" s="3">
         <v>9</v>
       </c>
       <c r="M37" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="N37" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="2:14">
@@ -6664,19 +6573,19 @@
         <v>10</v>
       </c>
       <c r="C38" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="D38" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="G38" s="3">
         <v>10</v>
       </c>
       <c r="H38" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="I38" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="2:14">
@@ -6684,19 +6593,19 @@
         <v>11</v>
       </c>
       <c r="C39" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="D39" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="G39" s="3">
         <v>11</v>
       </c>
       <c r="H39" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="I39" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="2:14">
@@ -6704,10 +6613,10 @@
         <v>12</v>
       </c>
       <c r="C40" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="D40" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="2:14">
@@ -6715,10 +6624,10 @@
         <v>13</v>
       </c>
       <c r="C41" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="D41" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="2:14">
@@ -6726,10 +6635,10 @@
         <v>14</v>
       </c>
       <c r="C42" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="D42" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="2:14">
@@ -6737,10 +6646,10 @@
         <v>15</v>
       </c>
       <c r="C43" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="D43" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="2:14">
@@ -6748,10 +6657,10 @@
         <v>16</v>
       </c>
       <c r="C44" t="s">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="D44" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="2:14">
@@ -6759,10 +6668,10 @@
         <v>17</v>
       </c>
       <c r="C45" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="D45" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="2:14">
@@ -6770,42 +6679,42 @@
         <v>18</v>
       </c>
       <c r="C46" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="D46" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="2:20">
       <c r="B51" s="6" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="2:20">
       <c r="C52" s="1" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="H52" s="1"/>
       <c r="L52" s="3"/>
       <c r="M52" s="1" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="R52" s="3"/>
       <c r="S52" s="1" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="2:20">
       <c r="C53" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="L53" s="3"/>
       <c r="M53" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="R53" s="3"/>
       <c r="S53" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="2:20">
@@ -6813,10 +6722,10 @@
         <v>0</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="G54" s="6"/>
       <c r="H54" s="1"/>
@@ -6825,19 +6734,19 @@
         <v>0</v>
       </c>
       <c r="M54" s="1" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="N54" s="1" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="R54" s="6" t="s">
         <v>0</v>
       </c>
       <c r="S54" s="1" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="T54" s="1" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="2:20">
@@ -6845,10 +6754,10 @@
         <v>1</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="D55" s="13" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="H55" s="13"/>
       <c r="I55" s="13"/>
@@ -6856,19 +6765,19 @@
         <v>1</v>
       </c>
       <c r="M55" s="13" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="N55" s="13" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="R55" s="3">
         <v>1</v>
       </c>
       <c r="S55" s="13" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="T55" s="13" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="2:20">
@@ -6876,7 +6785,7 @@
         <v>2</v>
       </c>
       <c r="C56" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="D56" t="s">
         <v>0</v>
@@ -6885,19 +6794,19 @@
         <v>2</v>
       </c>
       <c r="M56" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="N56" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="R56" s="3">
         <v>2</v>
       </c>
       <c r="S56" s="13" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="T56" s="13" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="2:20">
@@ -6905,28 +6814,28 @@
         <v>3</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="D57" s="13" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="L57" s="3">
         <v>3</v>
       </c>
       <c r="M57" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="N57" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="R57" s="3">
         <v>3</v>
       </c>
       <c r="S57" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="T57" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="2:20">
@@ -6934,10 +6843,10 @@
         <v>4</v>
       </c>
       <c r="C58" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="D58" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="H58" s="13"/>
       <c r="I58" s="13"/>
@@ -6945,7 +6854,7 @@
         <v>4</v>
       </c>
       <c r="M58" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="N58" t="s">
         <v>0</v>
@@ -6954,10 +6863,10 @@
         <v>4</v>
       </c>
       <c r="S58" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="T58" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="2:20">
@@ -6965,28 +6874,28 @@
         <v>5</v>
       </c>
       <c r="C59" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="D59" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="L59" s="3">
         <v>5</v>
       </c>
       <c r="M59" s="13" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="N59" s="13" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="R59" s="3">
         <v>5</v>
       </c>
       <c r="S59" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="T59" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="2:20">
@@ -6994,28 +6903,28 @@
         <v>6</v>
       </c>
       <c r="C60" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="D60" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="L60" s="3">
         <v>6</v>
       </c>
       <c r="M60" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="N60" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="R60" s="3">
         <v>6</v>
       </c>
       <c r="S60" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="T60" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="2:20">
@@ -7023,28 +6932,28 @@
         <v>7</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="D61" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="L61" s="3">
         <v>7</v>
       </c>
       <c r="M61" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="N61" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="R61" s="3">
         <v>7</v>
       </c>
       <c r="S61" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="T61" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="2:20">
@@ -7052,28 +6961,28 @@
         <v>8</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="D62" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="L62" s="3">
         <v>8</v>
       </c>
       <c r="M62" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="N62" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="R62" s="3">
         <v>8</v>
       </c>
       <c r="S62" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="T62" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="2:20">
@@ -7081,28 +6990,28 @@
         <v>9</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="D63" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="L63" s="3">
         <v>9</v>
       </c>
       <c r="M63" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="N63" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="R63" s="3">
         <v>9</v>
       </c>
       <c r="S63" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="T63" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="2:20">
@@ -7110,28 +7019,28 @@
         <v>10</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="D64" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="L64" s="3">
         <v>10</v>
       </c>
       <c r="M64" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="N64" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="R64" s="3">
         <v>10</v>
       </c>
       <c r="S64" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="T64" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="2:20">
@@ -7139,28 +7048,28 @@
         <v>11</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="L65" s="3">
         <v>11</v>
       </c>
       <c r="M65" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="N65" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="R65" s="3">
         <v>11</v>
       </c>
       <c r="S65" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="T65" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="2:20">
@@ -7168,28 +7077,28 @@
         <v>12</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="D66" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="L66" s="3">
         <v>12</v>
       </c>
       <c r="M66" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="N66" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="R66" s="3">
         <v>12</v>
       </c>
       <c r="S66" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="T66" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="2:20">
@@ -7197,19 +7106,19 @@
         <v>13</v>
       </c>
       <c r="C67" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="D67" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="L67" s="3">
         <v>13</v>
       </c>
       <c r="M67" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="N67" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="2:20">
@@ -7217,19 +7126,19 @@
         <v>14</v>
       </c>
       <c r="C68" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="D68" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="L68" s="3">
         <v>14</v>
       </c>
       <c r="M68" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="N68" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="2:20">
@@ -7237,19 +7146,19 @@
         <v>15</v>
       </c>
       <c r="C69" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="D69" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="L69" s="3">
         <v>15</v>
       </c>
       <c r="M69" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="N69" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="2:20">
@@ -7257,19 +7166,19 @@
         <v>16</v>
       </c>
       <c r="C70" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="D70" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="L70" s="3">
         <v>16</v>
       </c>
       <c r="M70" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="N70" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="2:20">
@@ -7277,19 +7186,19 @@
         <v>17</v>
       </c>
       <c r="C71" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="D71" t="s">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="L71" s="3">
         <v>17</v>
       </c>
       <c r="M71" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="N71" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="2:20">
@@ -7297,19 +7206,19 @@
         <v>18</v>
       </c>
       <c r="C72" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="D72" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="L72" s="3">
         <v>18</v>
       </c>
       <c r="M72" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="N72" t="s">
-        <v>433</v>
+        <v>425</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="2:20">
@@ -7317,19 +7226,19 @@
         <v>19</v>
       </c>
       <c r="C73" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="D73" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="L73" s="3">
         <v>19</v>
       </c>
       <c r="M73" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="N73" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="2:20">
@@ -7337,10 +7246,10 @@
         <v>20</v>
       </c>
       <c r="C74" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="D74" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="2:20">
@@ -7348,10 +7257,10 @@
         <v>21</v>
       </c>
       <c r="C75" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="D75" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="2:20">
@@ -7359,10 +7268,10 @@
         <v>22</v>
       </c>
       <c r="C76" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="D76" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="2:20">
@@ -7370,10 +7279,10 @@
         <v>23</v>
       </c>
       <c r="C77" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="D77" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="2:20">
@@ -7381,10 +7290,10 @@
         <v>24</v>
       </c>
       <c r="C78" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="D78" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
     </row>
   </sheetData>
@@ -7416,7 +7325,7 @@
   <sheetData>
     <row r="3" customHeight="1" spans="1:14">
       <c r="A3" s="9" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="B3" s="10"/>
       <c r="C3" s="10"/>
@@ -7451,11 +7360,11 @@
         <v>67</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="L6" s="3"/>
       <c r="M6" s="1" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:14">
@@ -7463,11 +7372,11 @@
         <v>66</v>
       </c>
       <c r="H7" t="s">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="L7" s="3"/>
       <c r="M7" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:14">
@@ -7475,28 +7384,28 @@
         <v>0</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>0</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:14">
@@ -7504,10 +7413,10 @@
         <v>1</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="G9" s="3">
         <v>1</v>
@@ -7525,10 +7434,10 @@
         <v>2</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="G10" s="3">
         <v>2</v>
@@ -7546,10 +7455,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="D11" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="G11" s="3">
         <v>3</v>
@@ -7563,10 +7472,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="D12" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="G12" s="3">
         <v>4</v>
@@ -7580,10 +7489,10 @@
         <v>5</v>
       </c>
       <c r="C13" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="D13" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="G13" s="3">
         <v>5</v>
@@ -7597,10 +7506,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="D14" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="G14" s="3">
         <v>6</v>
@@ -7614,10 +7523,10 @@
         <v>7</v>
       </c>
       <c r="C15" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="D15" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="G15" s="3">
         <v>7</v>
@@ -7631,10 +7540,10 @@
         <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="D16" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="G16" s="3">
         <v>8</v>
@@ -7648,10 +7557,10 @@
         <v>9</v>
       </c>
       <c r="C17" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="D17" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="G17" s="3">
         <v>9</v>
@@ -7665,10 +7574,10 @@
         <v>10</v>
       </c>
       <c r="C18" t="s">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="D18" t="s">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="G18" s="3">
         <v>10</v>
@@ -7682,10 +7591,10 @@
         <v>11</v>
       </c>
       <c r="C19" t="s">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="D19" t="s">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="G19" s="3">
         <v>11</v>
@@ -7716,7 +7625,7 @@
     </row>
     <row r="26" customHeight="1" spans="1:14">
       <c r="A26" s="9" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="B26" s="10"/>
       <c r="C26" s="10"/>
@@ -7751,10 +7660,10 @@
         <v>72</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:14">
@@ -7773,28 +7682,28 @@
         <v>0</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="G32" s="6" t="s">
         <v>0</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="L32" s="6" t="s">
         <v>0</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="2:14">
@@ -7802,28 +7711,28 @@
         <v>1</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="G33" s="3">
         <v>1</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="I33" s="13" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="L33" s="3">
         <v>1</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="2:14">
@@ -7831,28 +7740,28 @@
         <v>2</v>
       </c>
       <c r="C34" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="D34" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="G34" s="3">
         <v>2</v>
       </c>
       <c r="H34" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="I34" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="L34" s="3">
         <v>2</v>
       </c>
       <c r="M34" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="N34" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="2:14">
@@ -7860,28 +7769,28 @@
         <v>3</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="G35" s="3">
         <v>3</v>
       </c>
       <c r="H35" s="13" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="I35" s="13" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="L35" s="3">
         <v>3</v>
       </c>
       <c r="M35" s="13" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="N35" s="13" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="2:14">
@@ -7889,28 +7798,28 @@
         <v>4</v>
       </c>
       <c r="C36" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="D36" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="G36" s="3">
         <v>4</v>
       </c>
       <c r="H36" s="13" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="I36" s="13" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L36" s="3">
         <v>4</v>
       </c>
       <c r="M36" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="N36" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="2:14">
@@ -7918,28 +7827,28 @@
         <v>5</v>
       </c>
       <c r="C37" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="D37" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="G37" s="3">
         <v>5</v>
       </c>
       <c r="H37" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="I37" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="L37" s="3">
         <v>5</v>
       </c>
       <c r="M37" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="N37" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="2:14">
@@ -7947,28 +7856,28 @@
         <v>6</v>
       </c>
       <c r="C38" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="D38" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
       <c r="G38" s="3">
         <v>6</v>
       </c>
       <c r="H38" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="I38" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="L38" s="3">
         <v>6</v>
       </c>
       <c r="M38" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="N38" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="2:14">
@@ -7976,19 +7885,19 @@
         <v>7</v>
       </c>
       <c r="H39" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="I39" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="L39" s="3">
         <v>7</v>
       </c>
       <c r="M39" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="N39" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="2:14">
@@ -7996,19 +7905,19 @@
         <v>8</v>
       </c>
       <c r="H40" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="I40" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="L40" s="3">
         <v>8</v>
       </c>
       <c r="M40" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="N40" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="2:14">
@@ -8016,19 +7925,19 @@
         <v>9</v>
       </c>
       <c r="H41" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="I41" t="s">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="L41" s="3">
         <v>9</v>
       </c>
       <c r="M41" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="N41" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="2:14">
@@ -8036,26 +7945,26 @@
     </row>
     <row r="50" customHeight="1" spans="2:15">
       <c r="C50" s="1" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="L50" s="3"/>
       <c r="M50" s="1" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="2:15">
       <c r="C51" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="H51" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="L51" s="3"/>
       <c r="M51" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="2:15">
@@ -8063,28 +7972,28 @@
         <v>0</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="G52" s="6" t="s">
         <v>0</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="L52" s="6" t="s">
         <v>0</v>
       </c>
       <c r="M52" s="1" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="N52" s="1" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="2:15">
@@ -8092,28 +8001,28 @@
         <v>1</v>
       </c>
       <c r="C53" s="13" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="D53" s="13" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="G53" s="3">
         <v>1</v>
       </c>
       <c r="H53" s="13" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="I53" s="13" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="L53" s="3">
         <v>1</v>
       </c>
       <c r="M53" s="13" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="N53" s="13" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="O53" s="13"/>
     </row>
@@ -8122,28 +8031,28 @@
         <v>2</v>
       </c>
       <c r="C54" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="D54" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="G54" s="3">
         <v>2</v>
       </c>
       <c r="H54" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="I54" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="L54" s="3">
         <v>2</v>
       </c>
       <c r="M54" s="13" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="N54" s="13" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="O54" s="13"/>
     </row>
@@ -8152,28 +8061,28 @@
         <v>3</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="D55" s="13" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="G55" s="3">
         <v>3</v>
       </c>
       <c r="H55" s="13" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="I55" s="13" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="L55" s="3">
         <v>3</v>
       </c>
       <c r="M55" s="13" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="N55" s="13" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="O55" s="13"/>
     </row>
@@ -8182,28 +8091,28 @@
         <v>4</v>
       </c>
       <c r="C56" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="D56" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="G56" s="3">
         <v>4</v>
       </c>
       <c r="H56" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="I56" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="L56" s="3">
         <v>4</v>
       </c>
       <c r="M56" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="N56" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="2:15">
@@ -8211,28 +8120,28 @@
         <v>5</v>
       </c>
       <c r="C57" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="D57" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="G57" s="3">
         <v>5</v>
       </c>
       <c r="H57" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I57" t="s">
-        <v>478</v>
+        <v>470</v>
       </c>
       <c r="L57" s="3">
         <v>5</v>
       </c>
       <c r="M57" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="N57" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="2:15">
@@ -8240,19 +8149,19 @@
         <v>6</v>
       </c>
       <c r="C58" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="D58" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="G58" s="3">
         <v>6</v>
       </c>
       <c r="H58" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="I58" t="s">
-        <v>480</v>
+        <v>472</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="2:15">
@@ -8260,19 +8169,19 @@
         <v>7</v>
       </c>
       <c r="C59" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="D59" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="G59" s="3">
         <v>7</v>
       </c>
       <c r="H59" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="I59" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="2:15">
@@ -8280,19 +8189,19 @@
         <v>8</v>
       </c>
       <c r="C60" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
       <c r="D60" t="s">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="G60" s="3">
         <v>8</v>
       </c>
       <c r="H60" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="I60" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="2:15">
@@ -8300,19 +8209,19 @@
         <v>9</v>
       </c>
       <c r="C61" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="D61" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="G61" s="3">
         <v>9</v>
       </c>
       <c r="H61" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="I61" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="2:15">
@@ -8320,19 +8229,19 @@
         <v>10</v>
       </c>
       <c r="C62" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="D62" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="G62" s="3">
         <v>10</v>
       </c>
       <c r="H62" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="I62" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="2:15">
@@ -8340,19 +8249,19 @@
         <v>11</v>
       </c>
       <c r="C63" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="D63" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="G63" s="3">
         <v>11</v>
       </c>
       <c r="H63" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="I63" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="2:15">
@@ -8360,10 +8269,10 @@
         <v>12</v>
       </c>
       <c r="H64" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="I64" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="7:9">
@@ -8371,10 +8280,10 @@
         <v>13</v>
       </c>
       <c r="H65" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="I65" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="7:9">
@@ -8382,10 +8291,10 @@
         <v>14</v>
       </c>
       <c r="H66" t="s">
-        <v>492</v>
+        <v>484</v>
       </c>
       <c r="I66" t="s">
-        <v>493</v>
+        <v>485</v>
       </c>
     </row>
   </sheetData>
@@ -8418,7 +8327,7 @@
   <sheetData>
     <row r="3" customHeight="1" spans="1:13">
       <c r="A3" s="9" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="B3" s="10"/>
       <c r="C3" s="10"/>
@@ -8450,7 +8359,7 @@
     </row>
     <row r="7" customHeight="1" spans="1:13">
       <c r="B7" s="6" t="s">
-        <v>495</v>
+        <v>487</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:13">
@@ -8474,19 +8383,19 @@
         <v>0</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>0</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:13">
@@ -8494,19 +8403,19 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="D11" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="G11" s="3">
         <v>1</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:13">
@@ -8514,19 +8423,19 @@
         <v>2</v>
       </c>
       <c r="C12" t="s">
-        <v>496</v>
+        <v>488</v>
       </c>
       <c r="D12" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="G12" s="3">
         <v>2</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>497</v>
+        <v>489</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:13">
@@ -8534,19 +8443,19 @@
         <v>3</v>
       </c>
       <c r="C13" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="D13" t="s">
-        <v>497</v>
+        <v>489</v>
       </c>
       <c r="G13" s="3">
         <v>3</v>
       </c>
       <c r="H13" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="I13" t="s">
-        <v>498</v>
+        <v>490</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:13">
@@ -8554,19 +8463,19 @@
         <v>4</v>
       </c>
       <c r="C14" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="D14" t="s">
-        <v>498</v>
+        <v>490</v>
       </c>
       <c r="G14" s="3">
         <v>4</v>
       </c>
       <c r="H14" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I14" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:13">
@@ -8574,15 +8483,15 @@
         <v>5</v>
       </c>
       <c r="C15" t="s">
-        <v>500</v>
+        <v>492</v>
       </c>
       <c r="D15" t="s">
-        <v>501</v>
+        <v>493</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:13">
       <c r="A22" s="9" t="s">
-        <v>502</v>
+        <v>494</v>
       </c>
       <c r="B22" s="10"/>
       <c r="C22" s="10"/>
@@ -8650,10 +8559,10 @@
         <v>0</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="2:4">
@@ -8661,10 +8570,10 @@
         <v>1</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>503</v>
+        <v>495</v>
       </c>
       <c r="D7" t="s">
-        <v>498</v>
+        <v>490</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="2:4">
@@ -8672,10 +8581,10 @@
         <v>2</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>504</v>
+        <v>496</v>
       </c>
       <c r="D8" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="2:4">
@@ -8683,10 +8592,10 @@
         <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>505</v>
+        <v>497</v>
       </c>
       <c r="D9" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="2:4">
@@ -8694,10 +8603,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>506</v>
+        <v>498</v>
       </c>
       <c r="D10" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="2:4">
@@ -8705,10 +8614,10 @@
         <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="D11" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="2:4">
@@ -8716,10 +8625,10 @@
         <v>6</v>
       </c>
       <c r="C12" t="s">
-        <v>508</v>
+        <v>500</v>
       </c>
       <c r="D12" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="2:4">
@@ -8727,10 +8636,10 @@
         <v>7</v>
       </c>
       <c r="C13" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="D13" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="2:9">
@@ -8756,19 +8665,19 @@
         <v>0</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="G20" s="6" t="s">
         <v>0</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="2:9">
@@ -8776,19 +8685,19 @@
         <v>1</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="D21" t="s">
-        <v>509</v>
+        <v>501</v>
       </c>
       <c r="G21" s="3">
         <v>1</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="I21" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="2:9">
@@ -8796,19 +8705,19 @@
         <v>2</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="D22" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="G22" s="3">
         <v>2</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="I22" t="s">
-        <v>510</v>
+        <v>502</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="2:9">
@@ -8816,10 +8725,10 @@
         <v>3</v>
       </c>
       <c r="C23" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="D23" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="G23" s="3"/>
     </row>
@@ -8828,10 +8737,10 @@
         <v>4</v>
       </c>
       <c r="C24" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="D24" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="G24" s="3"/>
     </row>
@@ -8840,10 +8749,10 @@
         <v>5</v>
       </c>
       <c r="C25" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="D25" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="G25" s="3"/>
     </row>
@@ -8852,10 +8761,10 @@
         <v>6</v>
       </c>
       <c r="C26" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="D26" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="G26" s="3"/>
     </row>
@@ -8884,7 +8793,7 @@
   <sheetData>
     <row r="3" customHeight="1" spans="1:13">
       <c r="A3" s="9" t="s">
-        <v>511</v>
+        <v>503</v>
       </c>
       <c r="B3" s="10"/>
       <c r="C3" s="10"/>
@@ -8953,7 +8862,7 @@
   <sheetData>
     <row r="2" customHeight="1" spans="1:14">
       <c r="A2" s="4" t="s">
-        <v>512</v>
+        <v>504</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -8988,7 +8897,7 @@
     </row>
     <row r="15" customHeight="1" spans="1:14">
       <c r="A15" s="7" t="s">
-        <v>513</v>
+        <v>505</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
@@ -9032,7 +8941,7 @@
       </c>
       <c r="L18" s="3"/>
       <c r="M18" s="1" t="s">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="Q18" s="3"/>
       <c r="R18" s="1" t="s">
@@ -9060,37 +8969,37 @@
         <v>0</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="G20" s="6" t="s">
         <v>0</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="L20" s="6" t="s">
         <v>0</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="Q20" s="6" t="s">
         <v>0</v>
       </c>
       <c r="R20" s="1" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="S20" s="1" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="2:19">
@@ -9098,37 +9007,37 @@
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="D21" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="G21" s="3">
         <v>1</v>
       </c>
       <c r="H21" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="I21" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="L21" s="3">
         <v>1</v>
       </c>
       <c r="M21" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="N21" t="s">
-        <v>515</v>
+        <v>507</v>
       </c>
       <c r="Q21" s="3">
         <v>1</v>
       </c>
       <c r="R21" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="S21" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="2:19">
@@ -9136,34 +9045,34 @@
         <v>2</v>
       </c>
       <c r="C22" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="D22" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="G22" s="3">
         <v>2</v>
       </c>
       <c r="H22" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="I22" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="L22" s="3">
         <v>2</v>
       </c>
       <c r="M22" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="Q22" s="3">
         <v>2</v>
       </c>
       <c r="R22" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="S22" t="s">
-        <v>515</v>
+        <v>507</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="2:19">
@@ -9171,37 +9080,37 @@
         <v>3</v>
       </c>
       <c r="C23" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="D23" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="G23" s="3">
         <v>3</v>
       </c>
       <c r="H23" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="I23" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="L23" s="3">
         <v>3</v>
       </c>
       <c r="M23" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="N23" t="s">
-        <v>516</v>
+        <v>508</v>
       </c>
       <c r="Q23" s="3">
         <v>3</v>
       </c>
       <c r="R23" t="s">
-        <v>517</v>
+        <v>509</v>
       </c>
       <c r="S23" t="s">
-        <v>518</v>
+        <v>510</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="2:19">
@@ -9209,37 +9118,37 @@
         <v>4</v>
       </c>
       <c r="C24" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="D24" t="s">
-        <v>519</v>
+        <v>511</v>
       </c>
       <c r="G24" s="3">
         <v>4</v>
       </c>
       <c r="H24" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="I24" t="s">
-        <v>497</v>
+        <v>489</v>
       </c>
       <c r="L24" s="3">
         <v>4</v>
       </c>
       <c r="M24" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="N24" t="s">
-        <v>520</v>
+        <v>512</v>
       </c>
       <c r="Q24" s="3">
         <v>4</v>
       </c>
       <c r="R24" t="s">
-        <v>521</v>
+        <v>513</v>
       </c>
       <c r="S24" t="s">
-        <v>522</v>
+        <v>514</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="2:19">
@@ -9247,37 +9156,37 @@
         <v>5</v>
       </c>
       <c r="C25" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="D25" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="G25" s="3">
         <v>5</v>
       </c>
       <c r="H25" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="I25" t="s">
-        <v>498</v>
+        <v>490</v>
       </c>
       <c r="L25" s="3">
         <v>5</v>
       </c>
       <c r="M25" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="N25" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="Q25" s="3">
         <v>5</v>
       </c>
       <c r="R25" t="s">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="S25" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="2:19">
@@ -9285,37 +9194,37 @@
         <v>6</v>
       </c>
       <c r="C26" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="D26" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="G26" s="3">
         <v>6</v>
       </c>
       <c r="H26" t="s">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="I26" t="s">
-        <v>526</v>
+        <v>518</v>
       </c>
       <c r="L26" s="3">
         <v>6</v>
       </c>
       <c r="M26" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="N26" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="Q26" s="3">
         <v>6</v>
       </c>
       <c r="R26" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="S26" t="s">
-        <v>528</v>
+        <v>520</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="2:19">
@@ -9323,37 +9232,37 @@
         <v>7</v>
       </c>
       <c r="C27" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="D27" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="G27" s="3">
         <v>7</v>
       </c>
       <c r="H27" t="s">
-        <v>500</v>
+        <v>492</v>
       </c>
       <c r="I27" t="s">
-        <v>501</v>
+        <v>493</v>
       </c>
       <c r="L27" s="3">
         <v>7</v>
       </c>
       <c r="M27" t="s">
-        <v>529</v>
+        <v>521</v>
       </c>
       <c r="N27" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="Q27" s="3">
         <v>7</v>
       </c>
       <c r="R27" t="s">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="S27" t="s">
-        <v>532</v>
+        <v>524</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="2:19">
@@ -9361,29 +9270,29 @@
         <v>8</v>
       </c>
       <c r="C28" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="D28" t="s">
-        <v>534</v>
+        <v>526</v>
       </c>
       <c r="G28"/>
       <c r="L28" s="3">
         <v>8</v>
       </c>
       <c r="M28" t="s">
-        <v>535</v>
+        <v>527</v>
       </c>
       <c r="N28" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="Q28" s="3">
         <v>8</v>
       </c>
       <c r="R28" t="s">
-        <v>537</v>
+        <v>529</v>
       </c>
       <c r="S28" t="s">
-        <v>538</v>
+        <v>530</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="2:19">
@@ -9391,29 +9300,29 @@
         <v>9</v>
       </c>
       <c r="C29" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="D29" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="G29"/>
       <c r="L29" s="3">
         <v>9</v>
       </c>
       <c r="M29" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="N29" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="Q29" s="3">
         <v>9</v>
       </c>
       <c r="R29" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="S29" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="2:19">
@@ -9421,32 +9330,32 @@
         <v>10</v>
       </c>
       <c r="C30" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="D30" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="G30"/>
       <c r="H30" s="1" t="s">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="L30" s="3">
         <v>10</v>
       </c>
       <c r="M30" t="s">
-        <v>548</v>
+        <v>540</v>
       </c>
       <c r="N30" t="s">
-        <v>549</v>
+        <v>541</v>
       </c>
       <c r="Q30" s="3">
         <v>10</v>
       </c>
       <c r="R30" t="s">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="S30" t="s">
-        <v>551</v>
+        <v>543</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="2:19">
@@ -9454,10 +9363,10 @@
         <v>11</v>
       </c>
       <c r="C31" t="s">
-        <v>552</v>
+        <v>544</v>
       </c>
       <c r="D31" t="s">
-        <v>553</v>
+        <v>545</v>
       </c>
       <c r="G31"/>
       <c r="H31" s="1" t="s">
@@ -9467,19 +9376,19 @@
         <v>11</v>
       </c>
       <c r="M31" t="s">
-        <v>554</v>
+        <v>546</v>
       </c>
       <c r="N31" t="s">
-        <v>555</v>
+        <v>547</v>
       </c>
       <c r="Q31" s="3">
         <v>11</v>
       </c>
       <c r="R31" t="s">
-        <v>556</v>
+        <v>548</v>
       </c>
       <c r="S31" t="s">
-        <v>557</v>
+        <v>549</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="2:19">
@@ -9487,28 +9396,28 @@
         <v>12</v>
       </c>
       <c r="C32" t="s">
-        <v>558</v>
+        <v>550</v>
       </c>
       <c r="D32" t="s">
-        <v>559</v>
+        <v>551</v>
       </c>
       <c r="G32" s="6" t="s">
         <v>0</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="L32" s="3">
         <v>12</v>
       </c>
       <c r="M32" t="s">
-        <v>560</v>
+        <v>552</v>
       </c>
       <c r="N32" t="s">
-        <v>561</v>
+        <v>553</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="2:14">
@@ -9516,25 +9425,25 @@
         <v>13</v>
       </c>
       <c r="C33" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="D33" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="G33" s="3">
         <v>1</v>
       </c>
       <c r="H33" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="L33" s="3">
         <v>13</v>
       </c>
       <c r="M33" t="s">
-        <v>562</v>
+        <v>554</v>
       </c>
       <c r="N33" t="s">
-        <v>563</v>
+        <v>555</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="2:14">
@@ -9542,25 +9451,25 @@
         <v>14</v>
       </c>
       <c r="C34" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="D34" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="G34" s="3">
         <v>2</v>
       </c>
       <c r="H34" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="L34" s="3">
         <v>14</v>
       </c>
       <c r="M34" t="s">
-        <v>564</v>
+        <v>556</v>
       </c>
       <c r="N34" t="s">
-        <v>565</v>
+        <v>557</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="2:14">
@@ -9568,25 +9477,25 @@
         <v>15</v>
       </c>
       <c r="C35" t="s">
-        <v>566</v>
+        <v>558</v>
       </c>
       <c r="D35" t="s">
-        <v>567</v>
+        <v>559</v>
       </c>
       <c r="G35" s="3">
         <v>3</v>
       </c>
       <c r="H35" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="L35" s="3">
         <v>15</v>
       </c>
       <c r="M35" t="s">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="N35" t="s">
-        <v>569</v>
+        <v>561</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="2:14">
@@ -9594,19 +9503,19 @@
         <v>16</v>
       </c>
       <c r="C36" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="D36" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="G36" s="3">
         <v>4</v>
       </c>
       <c r="H36" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I36" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="2:14">
@@ -9614,10 +9523,10 @@
         <v>17</v>
       </c>
       <c r="C37" t="s">
-        <v>571</v>
+        <v>563</v>
       </c>
       <c r="D37" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="G37"/>
     </row>
@@ -9650,28 +9559,28 @@
         <v>0</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="G44" s="6" t="s">
         <v>0</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="L44" s="6" t="s">
         <v>0</v>
       </c>
       <c r="M44" s="1" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="2:14">
@@ -9679,28 +9588,28 @@
         <v>1</v>
       </c>
       <c r="C45" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="D45" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="G45" s="3">
         <v>1</v>
       </c>
       <c r="H45" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="I45" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="L45" s="3">
         <v>1</v>
       </c>
       <c r="M45" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="N45" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="2:14">
@@ -9708,28 +9617,28 @@
         <v>2</v>
       </c>
       <c r="C46" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="D46" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="G46" s="3">
         <v>2</v>
       </c>
       <c r="H46" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="I46" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L46" s="3">
         <v>2</v>
       </c>
       <c r="M46" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="N46" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="2:14">
@@ -9737,28 +9646,28 @@
         <v>3</v>
       </c>
       <c r="C47" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="D47" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="G47" s="3">
         <v>3</v>
       </c>
       <c r="H47" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="I47" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="L47" s="3">
         <v>3</v>
       </c>
       <c r="M47" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="N47" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="2:14">
@@ -9766,28 +9675,28 @@
         <v>4</v>
       </c>
       <c r="C48" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="D48" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="G48" s="3">
         <v>4</v>
       </c>
       <c r="H48" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="I48" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="L48" s="3">
         <v>4</v>
       </c>
       <c r="M48" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="N48" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="2:14">
@@ -9795,28 +9704,28 @@
         <v>5</v>
       </c>
       <c r="C49" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="D49" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="G49" s="3">
         <v>5</v>
       </c>
       <c r="H49" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I49" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="L49" s="3">
         <v>5</v>
       </c>
       <c r="M49" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="N49" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="2:14">
@@ -9824,28 +9733,28 @@
         <v>6</v>
       </c>
       <c r="C50" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="D50" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="G50" s="3">
         <v>6</v>
       </c>
       <c r="H50" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="I50" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="L50" s="3">
         <v>6</v>
       </c>
       <c r="M50" t="s">
-        <v>572</v>
+        <v>564</v>
       </c>
       <c r="N50" t="s">
-        <v>573</v>
+        <v>565</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="2:14">
@@ -9853,28 +9762,28 @@
         <v>7</v>
       </c>
       <c r="C51" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="D51" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="G51" s="3">
         <v>7</v>
       </c>
       <c r="H51" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="I51" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="L51" s="3">
         <v>7</v>
       </c>
       <c r="M51" t="s">
-        <v>574</v>
+        <v>566</v>
       </c>
       <c r="N51" t="s">
-        <v>575</v>
+        <v>567</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="2:14">
@@ -9882,28 +9791,28 @@
         <v>8</v>
       </c>
       <c r="C52" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="D52" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="G52" s="3">
         <v>8</v>
       </c>
       <c r="H52" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="I52" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="L52" s="3">
         <v>8</v>
       </c>
       <c r="M52" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="N52" t="s">
-        <v>577</v>
+        <v>569</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="2:14">
@@ -9911,28 +9820,28 @@
         <v>9</v>
       </c>
       <c r="C53" t="s">
-        <v>578</v>
+        <v>570</v>
       </c>
       <c r="D53" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="G53" s="3">
         <v>9</v>
       </c>
       <c r="H53" t="s">
-        <v>578</v>
+        <v>570</v>
       </c>
       <c r="I53" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="L53" s="3">
         <v>9</v>
       </c>
       <c r="M53" t="s">
-        <v>580</v>
+        <v>572</v>
       </c>
       <c r="N53" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="2:14">
@@ -9940,28 +9849,28 @@
         <v>10</v>
       </c>
       <c r="C54" t="s">
-        <v>582</v>
+        <v>574</v>
       </c>
       <c r="D54" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
       <c r="G54" s="3">
         <v>10</v>
       </c>
       <c r="H54" t="s">
-        <v>582</v>
+        <v>574</v>
       </c>
       <c r="I54" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
       <c r="L54" s="3">
         <v>10</v>
       </c>
       <c r="M54" t="s">
-        <v>584</v>
+        <v>576</v>
       </c>
       <c r="N54" t="s">
-        <v>585</v>
+        <v>577</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="2:14">
@@ -9969,28 +9878,28 @@
         <v>11</v>
       </c>
       <c r="C55" t="s">
-        <v>586</v>
+        <v>578</v>
       </c>
       <c r="D55" t="s">
-        <v>587</v>
+        <v>579</v>
       </c>
       <c r="G55" s="3">
         <v>11</v>
       </c>
       <c r="H55" t="s">
-        <v>588</v>
+        <v>580</v>
       </c>
       <c r="I55" t="s">
-        <v>589</v>
+        <v>581</v>
       </c>
       <c r="L55" s="3">
         <v>11</v>
       </c>
       <c r="M55" t="s">
-        <v>590</v>
+        <v>582</v>
       </c>
       <c r="N55" t="s">
-        <v>591</v>
+        <v>583</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="2:14">
@@ -9998,28 +9907,28 @@
         <v>12</v>
       </c>
       <c r="C56" t="s">
-        <v>588</v>
+        <v>580</v>
       </c>
       <c r="D56" t="s">
-        <v>592</v>
+        <v>584</v>
       </c>
       <c r="G56" s="3">
         <v>12</v>
       </c>
       <c r="H56" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="I56" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
       <c r="L56" s="3">
         <v>12</v>
       </c>
       <c r="M56" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="N56" t="s">
-        <v>595</v>
+        <v>587</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="2:14">
@@ -10027,28 +9936,28 @@
         <v>13</v>
       </c>
       <c r="C57" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="D57" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
       <c r="G57" s="3">
         <v>13</v>
       </c>
       <c r="H57" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="I57" t="s">
-        <v>534</v>
+        <v>526</v>
       </c>
       <c r="L57" s="3">
         <v>13</v>
       </c>
       <c r="M57" t="s">
-        <v>596</v>
+        <v>588</v>
       </c>
       <c r="N57" t="s">
-        <v>597</v>
+        <v>589</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="2:14">
@@ -10056,28 +9965,28 @@
         <v>14</v>
       </c>
       <c r="C58" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="D58" t="s">
-        <v>534</v>
+        <v>526</v>
       </c>
       <c r="G58" s="3">
         <v>14</v>
       </c>
       <c r="H58" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="I58" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="L58" s="3">
         <v>14</v>
       </c>
       <c r="M58" t="s">
-        <v>598</v>
+        <v>590</v>
       </c>
       <c r="N58" t="s">
-        <v>599</v>
+        <v>591</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="2:14">
@@ -10085,28 +9994,28 @@
         <v>15</v>
       </c>
       <c r="C59" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="D59" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="G59" s="3">
         <v>15</v>
       </c>
       <c r="H59" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="I59" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="L59" s="3">
         <v>15</v>
       </c>
       <c r="M59" t="s">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="N59" t="s">
-        <v>601</v>
+        <v>593</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="2:14">
@@ -10114,28 +10023,28 @@
         <v>16</v>
       </c>
       <c r="C60" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="D60" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="G60" s="3">
         <v>16</v>
       </c>
       <c r="H60" t="s">
-        <v>552</v>
+        <v>544</v>
       </c>
       <c r="I60" t="s">
-        <v>553</v>
+        <v>545</v>
       </c>
       <c r="L60" s="3">
         <v>16</v>
       </c>
       <c r="M60" t="s">
-        <v>602</v>
+        <v>594</v>
       </c>
       <c r="N60" t="s">
-        <v>603</v>
+        <v>595</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="2:14">
@@ -10143,28 +10052,28 @@
         <v>17</v>
       </c>
       <c r="C61" t="s">
-        <v>552</v>
+        <v>544</v>
       </c>
       <c r="D61" t="s">
-        <v>553</v>
+        <v>545</v>
       </c>
       <c r="G61" s="3">
         <v>17</v>
       </c>
       <c r="H61" t="s">
-        <v>558</v>
+        <v>550</v>
       </c>
       <c r="I61" t="s">
-        <v>559</v>
+        <v>551</v>
       </c>
       <c r="L61" s="3">
         <v>17</v>
       </c>
       <c r="M61" t="s">
-        <v>604</v>
+        <v>596</v>
       </c>
       <c r="N61" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="2:14">
@@ -10172,28 +10081,28 @@
         <v>18</v>
       </c>
       <c r="C62" t="s">
-        <v>558</v>
+        <v>550</v>
       </c>
       <c r="D62" t="s">
-        <v>559</v>
+        <v>551</v>
       </c>
       <c r="G62" s="3">
         <v>18</v>
       </c>
       <c r="H62" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="I62" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="L62" s="3">
         <v>18</v>
       </c>
       <c r="M62" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="N62" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="2:14">
@@ -10201,28 +10110,28 @@
         <v>19</v>
       </c>
       <c r="C63" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="D63" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="G63" s="3">
         <v>19</v>
       </c>
       <c r="H63" t="s">
-        <v>566</v>
+        <v>558</v>
       </c>
       <c r="I63" t="s">
-        <v>567</v>
+        <v>559</v>
       </c>
       <c r="L63" s="3">
         <v>19</v>
       </c>
       <c r="M63" t="s">
-        <v>608</v>
+        <v>600</v>
       </c>
       <c r="N63" t="s">
-        <v>609</v>
+        <v>601</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="2:14">
@@ -10230,28 +10139,28 @@
         <v>20</v>
       </c>
       <c r="C64" t="s">
-        <v>566</v>
+        <v>558</v>
       </c>
       <c r="D64" t="s">
-        <v>567</v>
+        <v>559</v>
       </c>
       <c r="G64" s="3">
         <v>20</v>
       </c>
       <c r="H64" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I64" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="L64" s="3">
         <v>20</v>
       </c>
       <c r="M64" t="s">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="N64" t="s">
-        <v>611</v>
+        <v>603</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="2:14">
@@ -10259,28 +10168,28 @@
         <v>21</v>
       </c>
       <c r="C65" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="D65" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="G65" s="3">
         <v>21</v>
       </c>
       <c r="H65" t="s">
-        <v>571</v>
+        <v>563</v>
       </c>
       <c r="I65" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="L65" s="3">
         <v>21</v>
       </c>
       <c r="M65" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="N65" t="s">
-        <v>613</v>
+        <v>605</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="2:14">
@@ -10288,40 +10197,40 @@
         <v>22</v>
       </c>
       <c r="C66" t="s">
-        <v>571</v>
+        <v>563</v>
       </c>
       <c r="D66" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="L66" s="3">
         <v>22</v>
       </c>
       <c r="M66" t="s">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="N66" t="s">
-        <v>615</v>
+        <v>607</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="2:14">
       <c r="B77" s="3" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="C77" t="s">
         <v>17</v>
       </c>
       <c r="D77" t="s">
-        <v>617</v>
+        <v>609</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="2:14">
       <c r="C79" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="1:14">
       <c r="A81" s="7" t="s">
-        <v>619</v>
+        <v>611</v>
       </c>
       <c r="B81" s="7"/>
       <c r="C81" s="7"/>
@@ -10374,19 +10283,19 @@
         <v>0</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="G86" s="6" t="s">
         <v>0</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="87" customHeight="1" spans="1:14">
@@ -10394,19 +10303,19 @@
         <v>1</v>
       </c>
       <c r="C87" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="D87" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="G87" s="3">
         <v>1</v>
       </c>
       <c r="H87" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="I87" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
     </row>
     <row r="88" customHeight="1" spans="1:14">
@@ -10414,19 +10323,19 @@
         <v>2</v>
       </c>
       <c r="C88" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="D88" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="G88" s="3">
         <v>2</v>
       </c>
       <c r="H88" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="I88" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="89" customHeight="1" spans="1:14">
@@ -10434,19 +10343,19 @@
         <v>3</v>
       </c>
       <c r="C89" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="D89" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="G89" s="3">
         <v>3</v>
       </c>
       <c r="H89" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="I89" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
     </row>
     <row r="90" customHeight="1" spans="1:14">
@@ -10454,19 +10363,19 @@
         <v>4</v>
       </c>
       <c r="C90" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="D90" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="G90" s="3">
         <v>4</v>
       </c>
       <c r="H90" t="s">
-        <v>620</v>
+        <v>612</v>
       </c>
       <c r="I90" t="s">
-        <v>621</v>
+        <v>613</v>
       </c>
     </row>
     <row r="91" customHeight="1" spans="1:14">
@@ -10474,19 +10383,19 @@
         <v>5</v>
       </c>
       <c r="C91" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="D91" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="G91" s="3">
         <v>5</v>
       </c>
       <c r="H91" t="s">
-        <v>622</v>
+        <v>614</v>
       </c>
       <c r="I91" t="s">
-        <v>623</v>
+        <v>615</v>
       </c>
     </row>
     <row r="92" customHeight="1" spans="1:14">
@@ -10494,19 +10403,19 @@
         <v>6</v>
       </c>
       <c r="C92" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="D92" t="s">
-        <v>595</v>
+        <v>587</v>
       </c>
       <c r="G92" s="3">
         <v>6</v>
       </c>
       <c r="H92" t="s">
-        <v>624</v>
+        <v>616</v>
       </c>
       <c r="I92" t="s">
-        <v>625</v>
+        <v>617</v>
       </c>
     </row>
     <row r="93" customHeight="1" spans="1:14">
@@ -10514,19 +10423,19 @@
         <v>7</v>
       </c>
       <c r="C93" t="s">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="D93" t="s">
-        <v>601</v>
+        <v>593</v>
       </c>
       <c r="G93" s="3">
         <v>7</v>
       </c>
       <c r="H93" t="s">
-        <v>626</v>
+        <v>618</v>
       </c>
       <c r="I93" t="s">
-        <v>627</v>
+        <v>619</v>
       </c>
     </row>
     <row r="94" customHeight="1" spans="1:14">
@@ -10534,19 +10443,19 @@
         <v>8</v>
       </c>
       <c r="C94" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="D94" t="s">
-        <v>613</v>
+        <v>605</v>
       </c>
       <c r="G94" s="3">
         <v>8</v>
       </c>
       <c r="H94" t="s">
-        <v>628</v>
+        <v>620</v>
       </c>
       <c r="I94" t="s">
-        <v>629</v>
+        <v>621</v>
       </c>
     </row>
     <row r="95" customHeight="1" spans="1:14">
@@ -10554,19 +10463,19 @@
         <v>9</v>
       </c>
       <c r="C95" t="s">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="D95" t="s">
-        <v>631</v>
+        <v>623</v>
       </c>
       <c r="G95" s="3">
         <v>9</v>
       </c>
       <c r="H95" t="s">
-        <v>632</v>
+        <v>624</v>
       </c>
       <c r="I95" t="s">
-        <v>633</v>
+        <v>625</v>
       </c>
     </row>
     <row r="96" customHeight="1" spans="1:14">
@@ -10574,19 +10483,19 @@
         <v>10</v>
       </c>
       <c r="C96" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="D96" t="s">
-        <v>635</v>
+        <v>627</v>
       </c>
       <c r="G96" s="3">
         <v>10</v>
       </c>
       <c r="H96" t="s">
-        <v>636</v>
+        <v>628</v>
       </c>
       <c r="I96" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
     </row>
     <row r="97" customHeight="1" spans="1:9">
@@ -10594,10 +10503,10 @@
         <v>11</v>
       </c>
       <c r="C97" t="s">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="D97" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
     </row>
     <row r="98" customHeight="1" spans="1:9">
@@ -10605,10 +10514,10 @@
         <v>12</v>
       </c>
       <c r="C98" t="s">
-        <v>639</v>
+        <v>631</v>
       </c>
       <c r="D98" t="s">
-        <v>640</v>
+        <v>632</v>
       </c>
     </row>
     <row r="99" customHeight="1" spans="1:9">
@@ -10616,10 +10525,10 @@
         <v>13</v>
       </c>
       <c r="C99" t="s">
-        <v>626</v>
+        <v>618</v>
       </c>
       <c r="D99" t="s">
-        <v>627</v>
+        <v>619</v>
       </c>
     </row>
     <row r="100" customHeight="1" spans="1:9">
@@ -10627,10 +10536,10 @@
         <v>14</v>
       </c>
       <c r="C100" t="s">
-        <v>628</v>
+        <v>620</v>
       </c>
       <c r="D100" t="s">
-        <v>629</v>
+        <v>621</v>
       </c>
     </row>
     <row r="101" customHeight="1" spans="1:9">
@@ -10638,10 +10547,10 @@
         <v>15</v>
       </c>
       <c r="C101" t="s">
-        <v>632</v>
+        <v>624</v>
       </c>
       <c r="D101" t="s">
-        <v>633</v>
+        <v>625</v>
       </c>
     </row>
     <row r="102" customHeight="1" spans="1:9">
@@ -10649,15 +10558,15 @@
         <v>16</v>
       </c>
       <c r="C102" t="s">
-        <v>636</v>
+        <v>628</v>
       </c>
       <c r="D102" t="s">
-        <v>641</v>
+        <v>633</v>
       </c>
     </row>
     <row r="106" customHeight="1" spans="1:9">
       <c r="A106" s="7" t="s">
-        <v>642</v>
+        <v>634</v>
       </c>
       <c r="B106" s="7"/>
       <c r="C106" s="7"/>
@@ -10680,199 +10589,61 @@
       <c r="I107" s="7"/>
     </row>
     <row r="110" customHeight="1" spans="1:9">
-      <c r="C110" s="1" t="s">
-        <v>643</v>
-      </c>
-      <c r="H110" s="1" t="s">
-        <v>643</v>
-      </c>
+      <c r="C110" s="1"/>
+      <c r="H110" s="1"/>
     </row>
     <row r="111" customHeight="1" spans="1:9">
-      <c r="C111" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="H111" s="1" t="s">
-        <v>134</v>
-      </c>
+      <c r="C111" s="1"/>
+      <c r="H111" s="1"/>
     </row>
     <row r="112" customHeight="1" spans="1:9">
       <c r="B112" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C112" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="G112" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="H112" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="I112" s="1" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="113" customHeight="1" spans="2:9">
+      <c r="C112" s="1"/>
+      <c r="D112" s="1"/>
+      <c r="G112" s="6"/>
+      <c r="H112" s="1"/>
+      <c r="I112" s="1"/>
+    </row>
+    <row r="113" customHeight="1" spans="2:2">
       <c r="B113" s="3">
         <v>1</v>
       </c>
-      <c r="C113" t="s">
-        <v>139</v>
-      </c>
-      <c r="D113" t="s">
-        <v>140</v>
-      </c>
-      <c r="G113" s="3">
-        <v>1</v>
-      </c>
-      <c r="H113" t="s">
-        <v>139</v>
-      </c>
-      <c r="I113" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="114" customHeight="1" spans="2:9">
+    </row>
+    <row r="114" customHeight="1" spans="2:2">
       <c r="B114" s="3">
         <v>2</v>
       </c>
-      <c r="C114" t="s">
-        <v>141</v>
-      </c>
-      <c r="D114" t="s">
-        <v>142</v>
-      </c>
-      <c r="G114" s="3">
-        <v>2</v>
-      </c>
-      <c r="H114" t="s">
-        <v>141</v>
-      </c>
-      <c r="I114" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="115" customHeight="1" spans="2:9">
+    </row>
+    <row r="115" customHeight="1" spans="2:2">
       <c r="B115" s="3">
         <v>3</v>
       </c>
-      <c r="C115" t="s">
-        <v>145</v>
-      </c>
-      <c r="D115" t="s">
-        <v>184</v>
-      </c>
-      <c r="G115" s="3">
-        <v>3</v>
-      </c>
-      <c r="H115" t="s">
-        <v>145</v>
-      </c>
-      <c r="I115" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="116" customHeight="1" spans="2:9">
+    </row>
+    <row r="116" customHeight="1" spans="2:2">
       <c r="B116" s="3">
         <v>4</v>
       </c>
-      <c r="C116" t="s">
-        <v>644</v>
-      </c>
-      <c r="D116" t="s">
-        <v>645</v>
-      </c>
-      <c r="G116" s="3">
-        <v>4</v>
-      </c>
-      <c r="H116" t="s">
-        <v>644</v>
-      </c>
-      <c r="I116" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="117" customHeight="1" spans="2:9">
+    </row>
+    <row r="117" customHeight="1" spans="2:2">
       <c r="B117" s="3">
         <v>5</v>
       </c>
-      <c r="C117" t="s">
-        <v>646</v>
-      </c>
-      <c r="D117" t="s">
-        <v>647</v>
-      </c>
-      <c r="G117" s="3">
-        <v>5</v>
-      </c>
-      <c r="H117" t="s">
-        <v>646</v>
-      </c>
-      <c r="I117" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="118" customHeight="1" spans="2:9">
+    </row>
+    <row r="118" customHeight="1" spans="2:2">
       <c r="B118" s="3">
         <v>6</v>
       </c>
-      <c r="C118" t="s">
-        <v>648</v>
-      </c>
-      <c r="D118" t="s">
-        <v>649</v>
-      </c>
-      <c r="G118" s="3">
-        <v>6</v>
-      </c>
-      <c r="H118" t="s">
-        <v>648</v>
-      </c>
-      <c r="I118" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="119" customHeight="1" spans="2:9">
+    </row>
+    <row r="119" customHeight="1" spans="2:2">
       <c r="B119" s="3">
         <v>7</v>
       </c>
-      <c r="C119" t="s">
-        <v>650</v>
-      </c>
-      <c r="D119" t="s">
-        <v>651</v>
-      </c>
-      <c r="G119" s="3">
-        <v>7</v>
-      </c>
-      <c r="H119" t="s">
-        <v>650</v>
-      </c>
-      <c r="I119" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="120" customHeight="1" spans="2:9">
+    </row>
+    <row r="120" customHeight="1" spans="2:2">
       <c r="B120" s="3">
         <v>8</v>
-      </c>
-      <c r="C120" t="s">
-        <v>652</v>
-      </c>
-      <c r="D120" t="s">
-        <v>653</v>
-      </c>
-      <c r="G120" s="3">
-        <v>8</v>
-      </c>
-      <c r="H120" t="s">
-        <v>652</v>
-      </c>
-      <c r="I120" t="s">
-        <v>653</v>
       </c>
     </row>
   </sheetData>
@@ -10903,29 +10674,29 @@
   <sheetData>
     <row r="5" spans="3:9">
       <c r="C5" s="1" t="s">
-        <v>654</v>
+        <v>635</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>655</v>
+        <v>636</v>
       </c>
     </row>
     <row r="7" spans="3:9">
       <c r="F7" s="1" t="s">
-        <v>656</v>
+        <v>637</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>657</v>
+        <v>638</v>
       </c>
     </row>
     <row r="8" spans="3:9">
       <c r="D8" s="1" t="s">
-        <v>658</v>
+        <v>639</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>659</v>
+        <v>640</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>660</v>
+        <v>641</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>17</v>
@@ -10933,89 +10704,89 @@
     </row>
     <row r="9" spans="3:9">
       <c r="I9" t="s">
-        <v>661</v>
+        <v>642</v>
       </c>
     </row>
     <row r="13" spans="3:9">
       <c r="H13" s="1" t="s">
-        <v>662</v>
+        <v>643</v>
       </c>
     </row>
     <row r="14" spans="3:9">
       <c r="H14" s="1" t="s">
-        <v>663</v>
+        <v>644</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>664</v>
+        <v>645</v>
       </c>
     </row>
     <row r="15" spans="3:9">
       <c r="I15" t="s">
-        <v>665</v>
+        <v>646</v>
       </c>
     </row>
     <row r="19" spans="8:9">
       <c r="H19" s="1" t="s">
-        <v>666</v>
+        <v>647</v>
       </c>
     </row>
     <row r="20" spans="8:9">
       <c r="H20" s="1" t="s">
-        <v>667</v>
+        <v>648</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>668</v>
+        <v>649</v>
       </c>
     </row>
     <row r="21" spans="8:9">
       <c r="I21" t="s">
-        <v>669</v>
+        <v>650</v>
       </c>
     </row>
     <row r="25" spans="8:9">
       <c r="H25" s="1" t="s">
-        <v>670</v>
+        <v>651</v>
       </c>
     </row>
     <row r="26" spans="8:9">
       <c r="H26" s="1" t="s">
-        <v>671</v>
+        <v>652</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>672</v>
+        <v>653</v>
       </c>
     </row>
     <row r="27" spans="8:9">
       <c r="I27" t="s">
-        <v>673</v>
+        <v>654</v>
       </c>
     </row>
     <row r="31" spans="8:9">
       <c r="H31" s="1" t="s">
-        <v>674</v>
+        <v>655</v>
       </c>
     </row>
     <row r="32" spans="8:9">
       <c r="H32" s="1" t="s">
-        <v>675</v>
+        <v>656</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>676</v>
+        <v>657</v>
       </c>
     </row>
     <row r="33" spans="8:9">
       <c r="I33" t="s">
-        <v>677</v>
+        <v>658</v>
       </c>
     </row>
     <row r="37" spans="8:9">
       <c r="H37" s="1" t="s">
-        <v>678</v>
+        <v>659</v>
       </c>
     </row>
     <row r="38" spans="8:9">
       <c r="H38" s="1" t="s">
-        <v>679</v>
+        <v>660</v>
       </c>
       <c r="I38" s="1" t="s">
         <v>21</v>
@@ -11023,12 +10794,12 @@
     </row>
     <row r="43" spans="8:9">
       <c r="H43" s="1" t="s">
-        <v>680</v>
+        <v>661</v>
       </c>
     </row>
     <row r="44" spans="8:9">
       <c r="H44" s="1" t="s">
-        <v>681</v>
+        <v>662</v>
       </c>
       <c r="I44" s="1" t="s">
         <v>86</v>
@@ -11036,17 +10807,17 @@
     </row>
     <row r="45" spans="8:9">
       <c r="I45" t="s">
-        <v>682</v>
+        <v>663</v>
       </c>
     </row>
     <row r="49" ht="13" customHeight="1" spans="6:9">
       <c r="H49" s="1" t="s">
-        <v>683</v>
+        <v>664</v>
       </c>
     </row>
     <row r="50" spans="6:9">
       <c r="H50" s="1" t="s">
-        <v>684</v>
+        <v>665</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>89</v>
@@ -11054,41 +10825,41 @@
     </row>
     <row r="51" spans="6:9">
       <c r="I51" t="s">
-        <v>685</v>
+        <v>666</v>
       </c>
     </row>
     <row r="55" spans="6:9">
       <c r="H55" s="1" t="s">
-        <v>686</v>
+        <v>667</v>
       </c>
     </row>
     <row r="56" spans="6:9">
       <c r="H56" s="1" t="s">
-        <v>687</v>
+        <v>668</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>688</v>
+        <v>669</v>
       </c>
     </row>
     <row r="57" spans="6:9">
       <c r="I57" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
     </row>
     <row r="61" spans="6:9">
       <c r="F61" s="1" t="s">
-        <v>690</v>
+        <v>671</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>691</v>
+        <v>672</v>
       </c>
     </row>
     <row r="62" spans="6:9">
       <c r="F62" s="1" t="s">
-        <v>692</v>
+        <v>673</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>693</v>
+        <v>674</v>
       </c>
       <c r="I62" s="1" t="s">
         <v>43</v>
@@ -11096,17 +10867,17 @@
     </row>
     <row r="63" spans="6:9">
       <c r="I63" t="s">
-        <v>665</v>
+        <v>646</v>
       </c>
     </row>
     <row r="65" spans="8:9">
       <c r="H65" s="1" t="s">
-        <v>694</v>
+        <v>675</v>
       </c>
     </row>
     <row r="66" spans="8:9">
       <c r="H66" s="1" t="s">
-        <v>695</v>
+        <v>676</v>
       </c>
       <c r="I66" s="1" t="s">
         <v>47</v>
@@ -11114,17 +10885,17 @@
     </row>
     <row r="67" spans="8:9">
       <c r="I67" t="s">
-        <v>669</v>
+        <v>650</v>
       </c>
     </row>
     <row r="69" spans="8:9">
       <c r="H69" s="1" t="s">
-        <v>696</v>
+        <v>677</v>
       </c>
     </row>
     <row r="70" spans="8:9">
       <c r="H70" s="1" t="s">
-        <v>697</v>
+        <v>678</v>
       </c>
       <c r="I70" s="1" t="s">
         <v>79</v>
@@ -11132,35 +10903,35 @@
     </row>
     <row r="71" spans="8:9">
       <c r="I71" t="s">
-        <v>673</v>
+        <v>654</v>
       </c>
     </row>
     <row r="73" spans="8:9">
       <c r="H73" s="1" t="s">
-        <v>698</v>
+        <v>679</v>
       </c>
     </row>
     <row r="74" spans="8:9">
       <c r="H74" s="1" t="s">
-        <v>699</v>
+        <v>680</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>700</v>
+        <v>681</v>
       </c>
     </row>
     <row r="75" spans="8:9">
       <c r="I75" t="s">
-        <v>701</v>
+        <v>682</v>
       </c>
     </row>
     <row r="77" spans="8:9">
       <c r="H77" s="1" t="s">
-        <v>702</v>
+        <v>683</v>
       </c>
     </row>
     <row r="78" spans="8:9">
       <c r="H78" s="1" t="s">
-        <v>703</v>
+        <v>684</v>
       </c>
       <c r="I78" s="1" t="s">
         <v>24</v>
@@ -11168,59 +10939,59 @@
     </row>
     <row r="79" spans="8:9">
       <c r="I79" t="s">
-        <v>704</v>
+        <v>685</v>
       </c>
     </row>
     <row r="81" spans="6:9">
       <c r="H81" s="1" t="s">
-        <v>705</v>
+        <v>686</v>
       </c>
     </row>
     <row r="82" spans="6:9">
       <c r="H82" s="1" t="s">
-        <v>706</v>
+        <v>687</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
     </row>
     <row r="83" spans="6:9">
       <c r="I83" t="s">
-        <v>707</v>
+        <v>688</v>
       </c>
     </row>
     <row r="87" spans="6:9">
       <c r="F87" s="1" t="s">
-        <v>708</v>
+        <v>689</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>709</v>
+        <v>690</v>
       </c>
     </row>
     <row r="88" spans="6:9">
       <c r="F88" s="1" t="s">
-        <v>710</v>
+        <v>691</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>711</v>
+        <v>692</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>712</v>
+        <v>693</v>
       </c>
     </row>
     <row r="89" spans="6:9">
       <c r="I89" t="s">
-        <v>713</v>
+        <v>694</v>
       </c>
     </row>
     <row r="92" spans="6:9">
       <c r="H92" s="1" t="s">
-        <v>714</v>
+        <v>695</v>
       </c>
     </row>
     <row r="93" spans="6:9">
       <c r="H93" s="1" t="s">
-        <v>715</v>
+        <v>696</v>
       </c>
       <c r="I93" s="1" t="s">
         <v>102</v>
@@ -11228,17 +10999,17 @@
     </row>
     <row r="94" spans="6:9">
       <c r="I94" t="s">
-        <v>716</v>
+        <v>697</v>
       </c>
     </row>
     <row r="97" spans="6:9">
       <c r="H97" s="1" t="s">
-        <v>717</v>
+        <v>698</v>
       </c>
     </row>
     <row r="98" spans="6:9">
       <c r="H98" s="1" t="s">
-        <v>718</v>
+        <v>699</v>
       </c>
       <c r="I98" s="1" t="s">
         <v>109</v>
@@ -11246,17 +11017,17 @@
     </row>
     <row r="99" spans="6:9">
       <c r="I99" t="s">
-        <v>719</v>
+        <v>700</v>
       </c>
     </row>
     <row r="101" spans="6:9">
       <c r="H101" s="1" t="s">
-        <v>720</v>
+        <v>701</v>
       </c>
     </row>
     <row r="102" spans="6:9">
       <c r="H102" s="1" t="s">
-        <v>721</v>
+        <v>702</v>
       </c>
       <c r="I102" s="1" t="s">
         <v>113</v>
@@ -11264,7 +11035,7 @@
     </row>
     <row r="103" spans="6:9">
       <c r="I103" t="s">
-        <v>722</v>
+        <v>703</v>
       </c>
     </row>
     <row r="105" spans="6:9">
@@ -11274,65 +11045,65 @@
     </row>
     <row r="106" spans="6:9">
       <c r="I106" t="s">
-        <v>722</v>
+        <v>703</v>
       </c>
     </row>
     <row r="109" spans="6:9">
       <c r="F109" s="1" t="s">
-        <v>723</v>
+        <v>704</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>724</v>
+        <v>705</v>
       </c>
     </row>
     <row r="110" spans="6:9">
       <c r="F110" s="1" t="s">
-        <v>725</v>
+        <v>706</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>726</v>
+        <v>707</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>130</v>
+        <v>708</v>
       </c>
     </row>
     <row r="111" spans="6:9">
       <c r="I111" t="s">
-        <v>727</v>
+        <v>709</v>
       </c>
     </row>
     <row r="114" spans="6:9">
       <c r="H114" s="1" t="s">
-        <v>728</v>
+        <v>710</v>
       </c>
     </row>
     <row r="115" spans="6:9">
       <c r="H115" s="1" t="s">
-        <v>729</v>
+        <v>711</v>
       </c>
       <c r="I115" s="1" t="s">
-        <v>134</v>
+        <v>712</v>
       </c>
     </row>
     <row r="116" spans="6:9">
       <c r="I116" t="s">
-        <v>727</v>
+        <v>709</v>
       </c>
     </row>
     <row r="120" spans="6:9">
       <c r="F120" s="1" t="s">
-        <v>730</v>
+        <v>713</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>731</v>
+        <v>714</v>
       </c>
     </row>
     <row r="121" spans="6:9">
       <c r="F121" s="1" t="s">
-        <v>732</v>
+        <v>715</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>733</v>
+        <v>716</v>
       </c>
       <c r="I121" s="1" t="s">
         <v>43</v>
@@ -11340,12 +11111,12 @@
     </row>
     <row r="124" spans="6:9">
       <c r="H124" s="1" t="s">
-        <v>734</v>
+        <v>717</v>
       </c>
     </row>
     <row r="125" spans="6:9">
       <c r="H125" s="1" t="s">
-        <v>735</v>
+        <v>718</v>
       </c>
       <c r="I125" s="1" t="s">
         <v>47</v>
@@ -11353,12 +11124,12 @@
     </row>
     <row r="128" spans="6:9">
       <c r="H128" s="1" t="s">
-        <v>736</v>
+        <v>719</v>
       </c>
     </row>
     <row r="129" spans="8:9">
       <c r="H129" s="1" t="s">
-        <v>737</v>
+        <v>720</v>
       </c>
       <c r="I129" s="1" t="s">
         <v>79</v>
@@ -11366,12 +11137,12 @@
     </row>
     <row r="132" spans="8:9">
       <c r="H132" s="1" t="s">
-        <v>738</v>
+        <v>721</v>
       </c>
     </row>
     <row r="133" spans="8:9">
       <c r="H133" s="1" t="s">
-        <v>739</v>
+        <v>722</v>
       </c>
       <c r="I133" s="1" t="s">
         <v>50</v>
@@ -11379,12 +11150,12 @@
     </row>
     <row r="136" spans="8:9">
       <c r="H136" s="1" t="s">
-        <v>740</v>
+        <v>723</v>
       </c>
     </row>
     <row r="137" spans="8:9">
       <c r="H137" s="1" t="s">
-        <v>741</v>
+        <v>724</v>
       </c>
       <c r="I137" s="1" t="s">
         <v>24</v>
@@ -11392,12 +11163,12 @@
     </row>
     <row r="141" spans="8:9">
       <c r="I141" s="1" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
     </row>
     <row r="158" spans="6:6">
       <c r="F158" t="s">
-        <v>742</v>
+        <v>725</v>
       </c>
     </row>
   </sheetData>
